--- a/Results/Phase 2/Hydrogen/hydrogen particulate matter results.xlsx
+++ b/Results/Phase 2/Hydrogen/hydrogen particulate matter results.xlsx
@@ -886,7 +886,7 @@
         <v>5.716161884475068e-08</v>
       </c>
       <c r="N5" t="n">
-        <v>1.752249074064535e-06</v>
+        <v>5.716161884475072e-08</v>
       </c>
       <c r="O5" t="n">
         <v>5.716161884475072e-08</v>
@@ -974,7 +974,7 @@
         <v>1.022854255717844e-07</v>
       </c>
       <c r="N6" t="n">
-        <v>1.752249074064535e-06</v>
+        <v>4.827542423601023e-08</v>
       </c>
       <c r="O6" t="n">
         <v>4.827525561211562e-08</v>
@@ -1062,7 +1062,7 @@
         <v>9.658209423484999e-08</v>
       </c>
       <c r="N7" t="n">
-        <v>1.752249074064535e-06</v>
+        <v>9.658209423484999e-08</v>
       </c>
       <c r="O7" t="n">
         <v>9.657382279994106e-08</v>
@@ -1150,7 +1150,7 @@
         <v>2.398803713311602e-07</v>
       </c>
       <c r="N8" t="n">
-        <v>1.752249074064535e-06</v>
+        <v>1.756899728045787e-07</v>
       </c>
       <c r="O8" t="n">
         <v>1.93330051673279e-07</v>
@@ -1238,7 +1238,7 @@
         <v>3.114960688532038e-07</v>
       </c>
       <c r="N9" t="n">
-        <v>1.752249074064535e-06</v>
+        <v>3.114960688532038e-07</v>
       </c>
       <c r="O9" t="n">
         <v>3.319398121583917e-07</v>
@@ -1922,7 +1922,7 @@
         <v>4.854415333814749e-08</v>
       </c>
       <c r="N5" t="n">
-        <v>2.158581586407831e-07</v>
+        <v>4.854415333814746e-08</v>
       </c>
       <c r="O5" t="n">
         <v>4.854415333814746e-08</v>
@@ -2010,7 +2010,7 @@
         <v>4.105174568552714e-08</v>
       </c>
       <c r="N6" t="n">
-        <v>2.158581586407831e-07</v>
+        <v>4.111812229989229e-08</v>
       </c>
       <c r="O6" t="n">
         <v>7.741215552505223e-08</v>
@@ -2098,7 +2098,7 @@
         <v>7.530848006687787e-08</v>
       </c>
       <c r="N7" t="n">
-        <v>2.158581586407831e-07</v>
+        <v>7.530848006687787e-08</v>
       </c>
       <c r="O7" t="n">
         <v>7.530130986713382e-08</v>
@@ -2122,7 +2122,7 @@
         <v>7.531141675261313e-08</v>
       </c>
       <c r="V7" t="n">
-        <v>7.363784795213155e-08</v>
+        <v>7.363784795213154e-08</v>
       </c>
       <c r="W7" t="n">
         <v>7.530848006687787e-08</v>
@@ -2186,7 +2186,7 @@
         <v>1.827533267185232e-07</v>
       </c>
       <c r="N8" t="n">
-        <v>2.158581586407831e-07</v>
+        <v>1.352855078557957e-07</v>
       </c>
       <c r="O8" t="n">
         <v>1.483300766345605e-07</v>
@@ -2274,7 +2274,7 @@
         <v>1.682583932833118e-07</v>
       </c>
       <c r="N9" t="n">
-        <v>2.158581586407831e-07</v>
+        <v>1.682583932833118e-07</v>
       </c>
       <c r="O9" t="n">
         <v>1.785333986975147e-07</v>
@@ -2958,7 +2958,7 @@
         <v>5.24461720781899e-08</v>
       </c>
       <c r="N5" t="n">
-        <v>8.255242855591031e-07</v>
+        <v>5.244617207818986e-08</v>
       </c>
       <c r="O5" t="n">
         <v>5.244617207818986e-08</v>
@@ -3046,7 +3046,7 @@
         <v>9.03035095533053e-08</v>
       </c>
       <c r="N6" t="n">
-        <v>8.255242855591031e-07</v>
+        <v>4.376097836206093e-08</v>
       </c>
       <c r="O6" t="n">
         <v>4.375620885257943e-08</v>
@@ -3134,7 +3134,7 @@
         <v>8.605576946037153e-08</v>
       </c>
       <c r="N7" t="n">
-        <v>8.255242855591031e-07</v>
+        <v>8.605576946037153e-08</v>
       </c>
       <c r="O7" t="n">
         <v>8.604812618778106e-08</v>
@@ -3222,7 +3222,7 @@
         <v>2.138531979776167e-07</v>
       </c>
       <c r="N8" t="n">
-        <v>8.255242855591031e-07</v>
+        <v>1.570294583955723e-07</v>
       </c>
       <c r="O8" t="n">
         <v>1.726451154229814e-07</v>
@@ -3310,7 +3310,7 @@
         <v>2.430366336398585e-07</v>
       </c>
       <c r="N9" t="n">
-        <v>8.255242855591031e-07</v>
+        <v>2.430366336398585e-07</v>
       </c>
       <c r="O9" t="n">
         <v>2.586778513871342e-07</v>
@@ -3694,82 +3694,82 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.041460073180114e-08</v>
+        <v>6.041460073180103e-08</v>
       </c>
       <c r="C2" t="n">
-        <v>6.042689049366798e-08</v>
+        <v>6.042689049366794e-08</v>
       </c>
       <c r="D2" t="n">
-        <v>6.168638751102342e-08</v>
+        <v>6.168638751102341e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>9.678230771063313e-08</v>
+        <v>9.678230771063309e-08</v>
       </c>
       <c r="F2" t="n">
-        <v>6.132856361632346e-08</v>
+        <v>6.132856361632343e-08</v>
       </c>
       <c r="G2" t="n">
-        <v>6.832545991995061e-08</v>
+        <v>6.832545991995055e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>6.040737709176332e-08</v>
+        <v>6.040737709176327e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>6.169102304112436e-08</v>
+        <v>6.169102304112429e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>6.356228056392216e-08</v>
+        <v>6.356228056392208e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>6.151709348435777e-08</v>
+        <v>6.151709348435774e-08</v>
       </c>
       <c r="L2" t="n">
-        <v>7.188288015063028e-08</v>
+        <v>7.188288015063025e-08</v>
       </c>
       <c r="M2" t="n">
-        <v>6.230763760020287e-08</v>
+        <v>6.230763760020275e-08</v>
       </c>
       <c r="N2" t="n">
-        <v>6.104238189779259e-08</v>
+        <v>6.104238189779257e-08</v>
       </c>
       <c r="O2" t="n">
-        <v>6.052081179464993e-08</v>
+        <v>6.052081179464985e-08</v>
       </c>
       <c r="P2" t="n">
-        <v>6.13133009937979e-08</v>
+        <v>6.131330099379785e-08</v>
       </c>
       <c r="Q2" t="n">
         <v>6.10394859598614e-08</v>
       </c>
       <c r="R2" t="n">
-        <v>6.05531423933474e-08</v>
+        <v>6.055314239334737e-08</v>
       </c>
       <c r="S2" t="n">
-        <v>6.103988039248493e-08</v>
+        <v>6.103988039248484e-08</v>
       </c>
       <c r="T2" t="n">
-        <v>6.072486324680022e-08</v>
+        <v>6.072486324680011e-08</v>
       </c>
       <c r="U2" t="n">
-        <v>6.163612952961029e-08</v>
+        <v>6.163612952961026e-08</v>
       </c>
       <c r="V2" t="n">
-        <v>4.542766044370603e-08</v>
+        <v>4.542766044370608e-08</v>
       </c>
       <c r="W2" t="n">
-        <v>6.285542516899421e-08</v>
+        <v>6.285542516899419e-08</v>
       </c>
       <c r="X2" t="n">
-        <v>6.77776567475512e-08</v>
+        <v>6.777765674755121e-08</v>
       </c>
       <c r="Y2" t="n">
-        <v>6.225055363076841e-08</v>
+        <v>6.22505536307684e-08</v>
       </c>
       <c r="Z2" t="n">
-        <v>6.148220209728095e-08</v>
+        <v>6.148220209728093e-08</v>
       </c>
       <c r="AA2" t="n">
-        <v>6.144751797072712e-08</v>
+        <v>6.144751797072709e-08</v>
       </c>
       <c r="AB2" t="n">
         <v>6.477848250746631e-08</v>
@@ -3782,85 +3782,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.070714674854106e-08</v>
+        <v>6.0707146748541e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>6.051276591762133e-08</v>
+        <v>6.051276591762127e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>6.070714674854106e-08</v>
+        <v>6.0707146748541e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>9.743530613724273e-08</v>
+        <v>9.743530613724283e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>6.060981220289547e-08</v>
+        <v>6.060981220289542e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>6.044706134274069e-08</v>
+        <v>6.044706134274063e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>6.070714674854106e-08</v>
+        <v>6.0707146748541e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>6.070714674854106e-08</v>
+        <v>6.0707146748541e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>6.030898095407336e-08</v>
+        <v>6.030898095407334e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>6.064996611384869e-08</v>
+        <v>6.064996611384864e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>6.070714674854106e-08</v>
+        <v>6.0707146748541e-08</v>
       </c>
       <c r="M3" t="n">
-        <v>6.054767051316373e-08</v>
+        <v>6.054767051316366e-08</v>
       </c>
       <c r="N3" t="n">
-        <v>6.070714674854106e-08</v>
+        <v>6.0707146748541e-08</v>
       </c>
       <c r="O3" t="n">
-        <v>6.051413432864414e-08</v>
+        <v>6.051413432864409e-08</v>
       </c>
       <c r="P3" t="n">
-        <v>6.068650905753617e-08</v>
+        <v>6.068650905753611e-08</v>
       </c>
       <c r="Q3" t="n">
-        <v>6.07049769802326e-08</v>
+        <v>6.070497698023255e-08</v>
       </c>
       <c r="R3" t="n">
-        <v>6.092218945037036e-08</v>
+        <v>6.092218945037031e-08</v>
       </c>
       <c r="S3" t="n">
-        <v>6.070714674854106e-08</v>
+        <v>6.0707146748541e-08</v>
       </c>
       <c r="T3" t="n">
-        <v>6.050016954970799e-08</v>
+        <v>6.050016954970794e-08</v>
       </c>
       <c r="U3" t="n">
-        <v>6.089698609045791e-08</v>
+        <v>6.089698609045786e-08</v>
       </c>
       <c r="V3" t="n">
-        <v>4.5320434458176e-08</v>
+        <v>4.532043445817603e-08</v>
       </c>
       <c r="W3" t="n">
-        <v>6.070714674854106e-08</v>
+        <v>6.0707146748541e-08</v>
       </c>
       <c r="X3" t="n">
-        <v>6.200082125239634e-08</v>
+        <v>6.200082125239627e-08</v>
       </c>
       <c r="Y3" t="n">
-        <v>6.021650395826623e-08</v>
+        <v>6.021650395826616e-08</v>
       </c>
       <c r="Z3" t="n">
-        <v>6.06900291196161e-08</v>
+        <v>6.069002911961604e-08</v>
       </c>
       <c r="AA3" t="n">
-        <v>6.070714674854106e-08</v>
+        <v>6.0707146748541e-08</v>
       </c>
       <c r="AB3" t="n">
-        <v>6.26385513442939e-08</v>
+        <v>6.263855134429383e-08</v>
       </c>
     </row>
     <row r="4">
@@ -3870,85 +3870,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.051281992843496e-07</v>
+        <v>2.051281992843509e-07</v>
       </c>
       <c r="C4" t="n">
-        <v>2.653689317970485e-07</v>
+        <v>2.65368931797048e-07</v>
       </c>
       <c r="D4" t="n">
-        <v>5.551783826670672e-07</v>
+        <v>5.551783826670678e-07</v>
       </c>
       <c r="E4" t="n">
-        <v>2.497614913536243e-07</v>
+        <v>2.497614913536237e-07</v>
       </c>
       <c r="F4" t="n">
-        <v>4.839410678432638e-07</v>
+        <v>4.839410678432634e-07</v>
       </c>
       <c r="G4" t="n">
-        <v>2.120513563447681e-06</v>
+        <v>2.120513563447682e-06</v>
       </c>
       <c r="H4" t="n">
-        <v>2.279994284974735e-07</v>
+        <v>2.279994284974731e-07</v>
       </c>
       <c r="I4" t="n">
-        <v>5.642344987425304e-07</v>
+        <v>5.642344987425285e-07</v>
       </c>
       <c r="J4" t="n">
-        <v>1.060354062833745e-06</v>
+        <v>1.060354062833744e-06</v>
       </c>
       <c r="K4" t="n">
-        <v>4.851898156903503e-07</v>
+        <v>4.851898156903495e-07</v>
       </c>
       <c r="L4" t="n">
         <v>3.083313903430098e-06</v>
       </c>
       <c r="M4" t="n">
-        <v>7.688434376867456e-07</v>
+        <v>7.688434376867434e-07</v>
       </c>
       <c r="N4" t="n">
-        <v>3.793172318309576e-07</v>
+        <v>3.793172318309572e-07</v>
       </c>
       <c r="O4" t="n">
-        <v>2.670685849295804e-07</v>
+        <v>2.670685849295817e-07</v>
       </c>
       <c r="P4" t="n">
-        <v>4.198767540722988e-07</v>
+        <v>4.198767540722987e-07</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.744441627685871e-07</v>
+        <v>3.74444162768586e-07</v>
       </c>
       <c r="R4" t="n">
-        <v>2.101655040225521e-07</v>
+        <v>2.101655040225519e-07</v>
       </c>
       <c r="S4" t="n">
-        <v>3.549554024831625e-07</v>
+        <v>3.549554024831617e-07</v>
       </c>
       <c r="T4" t="n">
-        <v>3.547072712497086e-07</v>
+        <v>3.54707271249709e-07</v>
       </c>
       <c r="U4" t="n">
-        <v>4.650884545468979e-07</v>
+        <v>4.650884545469112e-07</v>
       </c>
       <c r="V4" t="n">
-        <v>2.308804759409908e-07</v>
+        <v>2.308804759409929e-07</v>
       </c>
       <c r="W4" t="n">
-        <v>8.331093764243229e-07</v>
+        <v>8.33109376424322e-07</v>
       </c>
       <c r="X4" t="n">
-        <v>1.819040770516288e-06</v>
+        <v>1.81904077051629e-06</v>
       </c>
       <c r="Y4" t="n">
-        <v>7.882461316131374e-07</v>
+        <v>7.882461316131376e-07</v>
       </c>
       <c r="Z4" t="n">
-        <v>4.449989414653665e-07</v>
+        <v>4.449989414653649e-07</v>
       </c>
       <c r="AA4" t="n">
-        <v>4.766150396851644e-07</v>
+        <v>4.766150396851636e-07</v>
       </c>
       <c r="AB4" t="n">
-        <v>9.580756408591482e-07</v>
+        <v>9.580756408591471e-07</v>
       </c>
     </row>
     <row r="5">
@@ -3958,85 +3958,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.979256023243691e-08</v>
+        <v>4.979256023243684e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>4.979256023243696e-08</v>
+        <v>4.979256023243676e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>4.979256023243696e-08</v>
+        <v>4.979256023243676e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>4.979256023243696e-08</v>
+        <v>4.979256023243676e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>4.979256023243692e-08</v>
+        <v>4.979256023243681e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>4.979256023243696e-08</v>
+        <v>4.979256023243676e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>4.979256023243696e-08</v>
+        <v>4.979256023243676e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>4.979256023243696e-08</v>
+        <v>4.979256023243676e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>4.947621093798652e-08</v>
+        <v>4.947621093798639e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>4.979256023243696e-08</v>
+        <v>4.979256023243676e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>4.979256023243696e-08</v>
+        <v>4.979256023243678e-08</v>
       </c>
       <c r="M5" t="n">
-        <v>4.979256023243696e-08</v>
+        <v>4.979256023243676e-08</v>
       </c>
       <c r="N5" t="n">
-        <v>3.793172318309576e-07</v>
+        <v>4.979256023243681e-08</v>
       </c>
       <c r="O5" t="n">
-        <v>4.979256023243692e-08</v>
+        <v>4.979256023243681e-08</v>
       </c>
       <c r="P5" t="n">
-        <v>4.979256023243692e-08</v>
+        <v>4.979256023243681e-08</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.979256023243692e-08</v>
+        <v>4.979256023243681e-08</v>
       </c>
       <c r="R5" t="n">
-        <v>4.979256023243696e-08</v>
+        <v>4.979256023243676e-08</v>
       </c>
       <c r="S5" t="n">
-        <v>4.979256023243696e-08</v>
+        <v>4.979256023243676e-08</v>
       </c>
       <c r="T5" t="n">
-        <v>4.979256023243696e-08</v>
+        <v>4.979256023243676e-08</v>
       </c>
       <c r="U5" t="n">
-        <v>4.880059034033598e-08</v>
+        <v>4.88005903403358e-08</v>
       </c>
       <c r="V5" t="n">
         <v>4.766813436854802e-08</v>
       </c>
       <c r="W5" t="n">
-        <v>4.979256023243692e-08</v>
+        <v>4.979256023243681e-08</v>
       </c>
       <c r="X5" t="n">
-        <v>4.979256023243691e-08</v>
+        <v>4.979256023243684e-08</v>
       </c>
       <c r="Y5" t="n">
-        <v>4.880059034033598e-08</v>
+        <v>4.88005903403358e-08</v>
       </c>
       <c r="Z5" t="n">
-        <v>4.979256023243696e-08</v>
+        <v>4.979256023243676e-08</v>
       </c>
       <c r="AA5" t="n">
-        <v>4.979256023243696e-08</v>
+        <v>4.979256023243676e-08</v>
       </c>
       <c r="AB5" t="n">
-        <v>4.979256023243692e-08</v>
+        <v>4.979256023243681e-08</v>
       </c>
     </row>
     <row r="6">
@@ -4046,85 +4046,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>8.383380913092938e-08</v>
+        <v>8.383380913092912e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>4.172937394486655e-08</v>
+        <v>4.172937394486626e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>8.383380913092938e-08</v>
+        <v>8.383380913092914e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>8.383380913092938e-08</v>
+        <v>8.383380913092914e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>4.172937394486655e-08</v>
+        <v>4.172937394486626e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>4.172937394486655e-08</v>
+        <v>4.172937394486626e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>4.172937394486655e-08</v>
+        <v>4.172937394486626e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>4.172937394486655e-08</v>
+        <v>4.172937394486626e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>8.351745983647884e-08</v>
+        <v>8.351745983647877e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>8.383380913092938e-08</v>
+        <v>8.383380913092914e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>8.383380913092938e-08</v>
+        <v>8.383380913092912e-08</v>
       </c>
       <c r="M6" t="n">
-        <v>4.172937394486655e-08</v>
+        <v>4.172937394486626e-08</v>
       </c>
       <c r="N6" t="n">
-        <v>3.793172318309576e-07</v>
+        <v>4.175850752366421e-08</v>
       </c>
       <c r="O6" t="n">
-        <v>8.469922390186853e-08</v>
+        <v>8.469922390186811e-08</v>
       </c>
       <c r="P6" t="n">
-        <v>8.470539089437746e-08</v>
+        <v>8.470539089437715e-08</v>
       </c>
       <c r="Q6" t="n">
-        <v>8.383380913092938e-08</v>
+        <v>8.383380913092914e-08</v>
       </c>
       <c r="R6" t="n">
-        <v>4.172937394486655e-08</v>
+        <v>4.172937394486626e-08</v>
       </c>
       <c r="S6" t="n">
-        <v>8.383380913092938e-08</v>
+        <v>8.383380913092914e-08</v>
       </c>
       <c r="T6" t="n">
-        <v>4.172937394486655e-08</v>
+        <v>4.172937394486626e-08</v>
       </c>
       <c r="U6" t="n">
-        <v>4.172937394486655e-08</v>
+        <v>4.172937394486626e-08</v>
       </c>
       <c r="V6" t="n">
         <v>8.170938326704048e-08</v>
       </c>
       <c r="W6" t="n">
-        <v>8.469830144732343e-08</v>
+        <v>8.469830144732314e-08</v>
       </c>
       <c r="X6" t="n">
-        <v>4.172937394486655e-08</v>
+        <v>4.172937394486626e-08</v>
       </c>
       <c r="Y6" t="n">
-        <v>4.226130557436316e-08</v>
+        <v>4.226130557436313e-08</v>
       </c>
       <c r="Z6" t="n">
-        <v>8.383380913092938e-08</v>
+        <v>8.383380913092914e-08</v>
       </c>
       <c r="AA6" t="n">
-        <v>8.383380913092938e-08</v>
+        <v>8.383380913092914e-08</v>
       </c>
       <c r="AB6" t="n">
-        <v>4.209295767993665e-08</v>
+        <v>4.209295767993653e-08</v>
       </c>
     </row>
     <row r="7">
@@ -4134,85 +4134,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>7.957448372830347e-08</v>
+        <v>7.957448372830344e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>7.957448372830341e-08</v>
+        <v>7.957448372830343e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>7.957448372830341e-08</v>
+        <v>7.957448372830343e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>7.957448372830341e-08</v>
+        <v>7.957448372830343e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>7.957448372830341e-08</v>
+        <v>7.957448372830343e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>7.957448372830341e-08</v>
+        <v>7.957448372830343e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>7.957448372830341e-08</v>
+        <v>7.957448372830343e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>7.957448372830341e-08</v>
+        <v>7.957448372830343e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>7.925813443385322e-08</v>
+        <v>7.925813443385298e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>7.957448372830341e-08</v>
+        <v>7.957448372830343e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>7.957448372830347e-08</v>
+        <v>7.957448372830344e-08</v>
       </c>
       <c r="M7" t="n">
-        <v>7.957448372830341e-08</v>
+        <v>7.957448372830343e-08</v>
       </c>
       <c r="N7" t="n">
-        <v>3.793172318309576e-07</v>
+        <v>7.957448372830343e-08</v>
       </c>
       <c r="O7" t="n">
-        <v>7.956732355797941e-08</v>
+        <v>7.956732355797931e-08</v>
       </c>
       <c r="P7" t="n">
-        <v>7.956732355797941e-08</v>
+        <v>7.956732355797931e-08</v>
       </c>
       <c r="Q7" t="n">
-        <v>7.957448372830341e-08</v>
+        <v>7.957448372830343e-08</v>
       </c>
       <c r="R7" t="n">
-        <v>7.957448372830341e-08</v>
+        <v>7.957448372830343e-08</v>
       </c>
       <c r="S7" t="n">
-        <v>7.957448372830341e-08</v>
+        <v>7.957448372830343e-08</v>
       </c>
       <c r="T7" t="n">
-        <v>7.957448372830341e-08</v>
+        <v>7.957448372830343e-08</v>
       </c>
       <c r="U7" t="n">
-        <v>7.953060284467762e-08</v>
+        <v>7.953060284467752e-08</v>
       </c>
       <c r="V7" t="n">
-        <v>7.745005786441466e-08</v>
+        <v>7.74500578644147e-08</v>
       </c>
       <c r="W7" t="n">
-        <v>7.957448372830341e-08</v>
+        <v>7.957448372830343e-08</v>
       </c>
       <c r="X7" t="n">
-        <v>7.957448372830347e-08</v>
+        <v>7.957448372830344e-08</v>
       </c>
       <c r="Y7" t="n">
-        <v>7.957448372830341e-08</v>
+        <v>7.957448372830343e-08</v>
       </c>
       <c r="Z7" t="n">
-        <v>7.957448372830341e-08</v>
+        <v>7.957448372830343e-08</v>
       </c>
       <c r="AA7" t="n">
-        <v>7.957448372830341e-08</v>
+        <v>7.957448372830343e-08</v>
       </c>
       <c r="AB7" t="n">
-        <v>7.957448372830341e-08</v>
+        <v>7.957448372830343e-08</v>
       </c>
     </row>
     <row r="8">
@@ -4222,73 +4222,73 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.2908364528203e-07</v>
+        <v>1.290836452820301e-07</v>
       </c>
       <c r="C8" t="n">
-        <v>1.952410735721799e-07</v>
+        <v>1.9524107357218e-07</v>
       </c>
       <c r="D8" t="n">
-        <v>1.952410735721799e-07</v>
+        <v>1.9524107357218e-07</v>
       </c>
       <c r="E8" t="n">
         <v>1.600141945291696e-07</v>
       </c>
       <c r="F8" t="n">
-        <v>1.393901994089577e-07</v>
+        <v>1.393901994089575e-07</v>
       </c>
       <c r="G8" t="n">
-        <v>2.08959247304075e-07</v>
+        <v>2.089592473040747e-07</v>
       </c>
       <c r="H8" t="n">
-        <v>1.952410735721799e-07</v>
+        <v>1.9524107357218e-07</v>
       </c>
       <c r="I8" t="n">
-        <v>1.952410735721799e-07</v>
+        <v>1.9524107357218e-07</v>
       </c>
       <c r="J8" t="n">
         <v>1.949247242777294e-07</v>
       </c>
       <c r="K8" t="n">
-        <v>1.952410735721799e-07</v>
+        <v>1.9524107357218e-07</v>
       </c>
       <c r="L8" t="n">
-        <v>1.952410735721801e-07</v>
+        <v>1.9524107357218e-07</v>
       </c>
       <c r="M8" t="n">
         <v>1.952410735721696e-07</v>
       </c>
       <c r="N8" t="n">
-        <v>3.793172318309576e-07</v>
+        <v>1.439579987478343e-07</v>
       </c>
       <c r="O8" t="n">
         <v>1.580510329912132e-07</v>
       </c>
       <c r="P8" t="n">
-        <v>1.545964897629098e-07</v>
+        <v>1.545964897629096e-07</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.160822006516195e-07</v>
+        <v>1.160822006516194e-07</v>
       </c>
       <c r="R8" t="n">
-        <v>1.952410735721799e-07</v>
+        <v>1.9524107357218e-07</v>
       </c>
       <c r="S8" t="n">
-        <v>1.952410735721799e-07</v>
+        <v>1.9524107357218e-07</v>
       </c>
       <c r="T8" t="n">
-        <v>1.952410735721799e-07</v>
+        <v>1.9524107357218e-07</v>
       </c>
       <c r="U8" t="n">
-        <v>1.6292205816231e-07</v>
+        <v>1.629220581623101e-07</v>
       </c>
       <c r="V8" t="n">
-        <v>1.750034370638809e-07</v>
+        <v>1.75003437063881e-07</v>
       </c>
       <c r="W8" t="n">
-        <v>1.952540753972396e-07</v>
+        <v>1.952540753972395e-07</v>
       </c>
       <c r="X8" t="n">
-        <v>1.221456604091963e-07</v>
+        <v>1.221456604091965e-07</v>
       </c>
       <c r="Y8" t="n">
         <v>2.609712159206085e-07</v>
@@ -4297,10 +4297,10 @@
         <v>1.278547370841564e-07</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.952410735721799e-07</v>
+        <v>1.9524107357218e-07</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.643480394150368e-07</v>
+        <v>2.64348039415037e-07</v>
       </c>
     </row>
     <row r="9">
@@ -4310,85 +4310,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.661809457425435e-07</v>
+        <v>1.661809457425431e-07</v>
       </c>
       <c r="C9" t="n">
-        <v>2.052355916008363e-07</v>
+        <v>2.052355916008359e-07</v>
       </c>
       <c r="D9" t="n">
-        <v>2.052355916008363e-07</v>
+        <v>2.052355916008359e-07</v>
       </c>
       <c r="E9" t="n">
-        <v>1.962219824218044e-07</v>
+        <v>1.96221982421804e-07</v>
       </c>
       <c r="F9" t="n">
-        <v>1.152038995755563e-07</v>
+        <v>1.152038995755559e-07</v>
       </c>
       <c r="G9" t="n">
-        <v>2.052356485220936e-07</v>
+        <v>2.052356485220931e-07</v>
       </c>
       <c r="H9" t="n">
-        <v>2.052355916008363e-07</v>
+        <v>2.052355916008359e-07</v>
       </c>
       <c r="I9" t="n">
-        <v>2.052355916008363e-07</v>
+        <v>2.052355916008359e-07</v>
       </c>
       <c r="J9" t="n">
-        <v>2.04919242306386e-07</v>
+        <v>2.049192423063857e-07</v>
       </c>
       <c r="K9" t="n">
-        <v>2.052355916008363e-07</v>
+        <v>2.052355916008359e-07</v>
       </c>
       <c r="L9" t="n">
-        <v>2.052355916008363e-07</v>
+        <v>2.052355916008359e-07</v>
       </c>
       <c r="M9" t="n">
-        <v>2.052355916008363e-07</v>
+        <v>2.052355916008359e-07</v>
       </c>
       <c r="N9" t="n">
-        <v>3.793172318309576e-07</v>
+        <v>2.052355916008359e-07</v>
       </c>
       <c r="O9" t="n">
-        <v>2.181783258854711e-07</v>
+        <v>2.181783258854707e-07</v>
       </c>
       <c r="P9" t="n">
-        <v>2.209931361530566e-07</v>
+        <v>2.209931361530563e-07</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.052356485220936e-07</v>
+        <v>2.052356485220931e-07</v>
       </c>
       <c r="R9" t="n">
-        <v>2.052355916008363e-07</v>
+        <v>2.052355916008359e-07</v>
       </c>
       <c r="S9" t="n">
-        <v>2.052355916008363e-07</v>
+        <v>2.052355916008359e-07</v>
       </c>
       <c r="T9" t="n">
-        <v>2.052355916008363e-07</v>
+        <v>2.052355916008359e-07</v>
       </c>
       <c r="U9" t="n">
-        <v>2.052355916008363e-07</v>
+        <v>2.052355916008359e-07</v>
       </c>
       <c r="V9" t="n">
         <v>2.481794599531115e-07</v>
       </c>
       <c r="W9" t="n">
-        <v>2.052355916008363e-07</v>
+        <v>2.052355916008359e-07</v>
       </c>
       <c r="X9" t="n">
-        <v>2.052355916008363e-07</v>
+        <v>2.052355916008359e-07</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.052355916008363e-07</v>
+        <v>2.052355916008359e-07</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.816891356256987e-07</v>
+        <v>1.816891356256983e-07</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.052355916008363e-07</v>
+        <v>2.052355916008359e-07</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.052355916008363e-07</v>
+        <v>2.052355916008359e-07</v>
       </c>
     </row>
     <row r="10">
@@ -4398,85 +4398,85 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>5.699909740770727e-08</v>
+        <v>5.699909740770717e-08</v>
       </c>
       <c r="C10" t="n">
-        <v>5.574439997197269e-08</v>
+        <v>5.57443999719727e-08</v>
       </c>
       <c r="D10" t="n">
-        <v>4.960727590272329e-08</v>
+        <v>4.960727590272319e-08</v>
       </c>
       <c r="E10" t="n">
-        <v>9.239816373850406e-08</v>
+        <v>9.239816373850412e-08</v>
       </c>
       <c r="F10" t="n">
-        <v>5.113156817547682e-08</v>
+        <v>5.113156817547679e-08</v>
       </c>
       <c r="G10" t="n">
-        <v>8.291017854424886e-09</v>
+        <v>8.291017854424721e-09</v>
       </c>
       <c r="H10" t="n">
-        <v>5.712372328146519e-08</v>
+        <v>5.712372328146517e-08</v>
       </c>
       <c r="I10" t="n">
-        <v>4.960102367335304e-08</v>
+        <v>4.960102367335297e-08</v>
       </c>
       <c r="J10" t="n">
-        <v>3.559758657893394e-08</v>
+        <v>3.559758657893398e-08</v>
       </c>
       <c r="K10" t="n">
-        <v>5.022084952322022e-08</v>
+        <v>5.022084952322018e-08</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.077601471262198e-08</v>
+        <v>-1.077601471262196e-08</v>
       </c>
       <c r="M10" t="n">
-        <v>4.501448750034782e-08</v>
+        <v>4.501448750034779e-08</v>
       </c>
       <c r="N10" t="n">
-        <v>5.334839822359943e-08</v>
+        <v>5.334839822359939e-08</v>
       </c>
       <c r="O10" t="n">
-        <v>5.511899184906433e-08</v>
+        <v>5.511899184906428e-08</v>
       </c>
       <c r="P10" t="n">
-        <v>5.150152956269882e-08</v>
+        <v>5.150152956269873e-08</v>
       </c>
       <c r="Q10" t="n">
-        <v>5.336391540313984e-08</v>
+        <v>5.33639154031398e-08</v>
       </c>
       <c r="R10" t="n">
-        <v>5.762460808724328e-08</v>
+        <v>5.76246080872432e-08</v>
       </c>
       <c r="S10" t="n">
-        <v>5.330225192897943e-08</v>
+        <v>5.330225192897936e-08</v>
       </c>
       <c r="T10" t="n">
-        <v>5.392875850791565e-08</v>
+        <v>5.392875850791549e-08</v>
       </c>
       <c r="U10" t="n">
-        <v>5.100664966191132e-08</v>
+        <v>5.100664966191121e-08</v>
       </c>
       <c r="V10" t="n">
-        <v>4.05189375926754e-08</v>
+        <v>4.051893759267544e-08</v>
       </c>
       <c r="W10" t="n">
-        <v>4.262313174654306e-08</v>
+        <v>4.26231317465431e-08</v>
       </c>
       <c r="X10" t="n">
-        <v>2.210749238886951e-08</v>
+        <v>2.21074923888695e-08</v>
       </c>
       <c r="Y10" t="n">
-        <v>4.308397876355908e-08</v>
+        <v>4.308397876355899e-08</v>
       </c>
       <c r="Z10" t="n">
-        <v>5.054886472595075e-08</v>
+        <v>5.054886472595073e-08</v>
       </c>
       <c r="AA10" t="n">
-        <v>5.094054573751954e-08</v>
+        <v>5.094054573751951e-08</v>
       </c>
       <c r="AB10" t="n">
-        <v>4.376928484933357e-08</v>
+        <v>4.376928484933354e-08</v>
       </c>
     </row>
     <row r="11">
@@ -4486,85 +4486,85 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>5.872742646486961e-08</v>
+        <v>5.872742646486957e-08</v>
       </c>
       <c r="C11" t="n">
-        <v>5.82572687925173e-08</v>
+        <v>5.825726879251729e-08</v>
       </c>
       <c r="D11" t="n">
-        <v>5.663591090298678e-08</v>
+        <v>5.663591090298674e-08</v>
       </c>
       <c r="E11" t="n">
-        <v>9.449039186678672e-08</v>
+        <v>9.449039186678665e-08</v>
       </c>
       <c r="F11" t="n">
-        <v>5.701593237847643e-08</v>
+        <v>5.701593237847644e-08</v>
       </c>
       <c r="G11" t="n">
-        <v>4.459429392131835e-08</v>
+        <v>4.459429392131834e-08</v>
       </c>
       <c r="H11" t="n">
-        <v>5.877690799455082e-08</v>
+        <v>5.877690799455078e-08</v>
       </c>
       <c r="I11" t="n">
-        <v>5.663770164879954e-08</v>
+        <v>5.663770164879951e-08</v>
       </c>
       <c r="J11" t="n">
-        <v>5.231851737269242e-08</v>
+        <v>5.231851737269237e-08</v>
       </c>
       <c r="K11" t="n">
-        <v>5.677181219999933e-08</v>
+        <v>5.677181219999926e-08</v>
       </c>
       <c r="L11" t="n">
-        <v>3.935781388248208e-08</v>
+        <v>3.935781388248209e-08</v>
       </c>
       <c r="M11" t="n">
-        <v>5.523998982805448e-08</v>
+        <v>5.523998982805436e-08</v>
       </c>
       <c r="N11" t="n">
         <v>5.769412786800407e-08</v>
       </c>
       <c r="O11" t="n">
-        <v>5.806600477314214e-08</v>
+        <v>5.806600477314217e-08</v>
       </c>
       <c r="P11" t="n">
-        <v>5.713410605285399e-08</v>
+        <v>5.713410605285389e-08</v>
       </c>
       <c r="Q11" t="n">
-        <v>5.769927954770907e-08</v>
+        <v>5.769927954770904e-08</v>
       </c>
       <c r="R11" t="n">
-        <v>5.905273236435629e-08</v>
+        <v>5.905273236435623e-08</v>
       </c>
       <c r="S11" t="n">
-        <v>5.767062965158478e-08</v>
+        <v>5.767062965158472e-08</v>
       </c>
       <c r="T11" t="n">
-        <v>5.773485028094014e-08</v>
+        <v>5.77348502809401e-08</v>
       </c>
       <c r="U11" t="n">
         <v>5.713599493598951e-08</v>
       </c>
       <c r="V11" t="n">
-        <v>4.324296406844065e-08</v>
+        <v>4.324296406844071e-08</v>
       </c>
       <c r="W11" t="n">
-        <v>5.462714071274883e-08</v>
+        <v>5.462714071274875e-08</v>
       </c>
       <c r="X11" t="n">
-        <v>4.962606498215067e-08</v>
+        <v>4.962606498215068e-08</v>
       </c>
       <c r="Y11" t="n">
-        <v>5.445520006905846e-08</v>
+        <v>5.445520006905838e-08</v>
       </c>
       <c r="Z11" t="n">
-        <v>5.686793998018984e-08</v>
+        <v>5.686793998018986e-08</v>
       </c>
       <c r="AA11" t="n">
         <v>5.700368338640159e-08</v>
       </c>
       <c r="AB11" t="n">
-        <v>5.619290611947501e-08</v>
+        <v>5.619290611947496e-08</v>
       </c>
     </row>
   </sheetData>
@@ -4730,85 +4730,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.938846833171938e-08</v>
+        <v>5.938846833171948e-08</v>
       </c>
       <c r="C2" t="n">
-        <v>5.930096098305842e-08</v>
+        <v>5.930096098305843e-08</v>
       </c>
       <c r="D2" t="n">
-        <v>5.984526530615188e-08</v>
+        <v>5.984526530615198e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>9.610413712348218e-08</v>
+        <v>9.610413712348219e-08</v>
       </c>
       <c r="F2" t="n">
         <v>6.03611370436754e-08</v>
       </c>
       <c r="G2" t="n">
-        <v>6.60420340396741e-08</v>
+        <v>6.604203403967426e-08</v>
       </c>
       <c r="H2" t="n">
         <v>5.947359343971207e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>6.034173874372e-08</v>
+        <v>6.034173874372011e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>6.19304346703059e-08</v>
+        <v>6.193043467030594e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>6.064133147489808e-08</v>
+        <v>6.064133147489816e-08</v>
       </c>
       <c r="L2" t="n">
-        <v>6.840435140119206e-08</v>
+        <v>6.840435140119208e-08</v>
       </c>
       <c r="M2" t="n">
-        <v>6.068518375960609e-08</v>
+        <v>6.068518375960613e-08</v>
       </c>
       <c r="N2" t="n">
-        <v>5.935547953763847e-08</v>
+        <v>5.935547953763859e-08</v>
       </c>
       <c r="O2" t="n">
-        <v>5.958074068505775e-08</v>
+        <v>5.958074068505779e-08</v>
       </c>
       <c r="P2" t="n">
-        <v>5.957099824416277e-08</v>
+        <v>5.957099824416278e-08</v>
       </c>
       <c r="Q2" t="n">
-        <v>5.997922623379025e-08</v>
+        <v>5.997922623379026e-08</v>
       </c>
       <c r="R2" t="n">
-        <v>6.011628917965306e-08</v>
+        <v>6.011628917965302e-08</v>
       </c>
       <c r="S2" t="n">
-        <v>6.011265548847862e-08</v>
+        <v>6.011265548847878e-08</v>
       </c>
       <c r="T2" t="n">
-        <v>5.98508426256259e-08</v>
+        <v>5.985084262562593e-08</v>
       </c>
       <c r="U2" t="n">
-        <v>6.126837140713599e-08</v>
+        <v>6.126837140713609e-08</v>
       </c>
       <c r="V2" t="n">
-        <v>4.459332823468517e-08</v>
+        <v>4.459332823468526e-08</v>
       </c>
       <c r="W2" t="n">
-        <v>6.083746410132882e-08</v>
+        <v>6.083746410132885e-08</v>
       </c>
       <c r="X2" t="n">
-        <v>6.676010022273429e-08</v>
+        <v>6.676010022273432e-08</v>
       </c>
       <c r="Y2" t="n">
-        <v>6.214030948160568e-08</v>
+        <v>6.214030948160566e-08</v>
       </c>
       <c r="Z2" t="n">
-        <v>6.031737441113925e-08</v>
+        <v>6.031737441113926e-08</v>
       </c>
       <c r="AA2" t="n">
-        <v>6.052389638446837e-08</v>
+        <v>6.052389638446844e-08</v>
       </c>
       <c r="AB2" t="n">
-        <v>6.342982070549254e-08</v>
+        <v>6.342982070549266e-08</v>
       </c>
     </row>
     <row r="3">
@@ -4818,85 +4818,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.974165783764199e-08</v>
+        <v>5.974165783764211e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>5.954803736596674e-08</v>
+        <v>5.954803736596685e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>5.974165783764199e-08</v>
+        <v>5.974165783764211e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>9.697328361798548e-08</v>
+        <v>9.697328361798567e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>5.961246733297429e-08</v>
+        <v>5.961246733297441e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>5.935340485075362e-08</v>
+        <v>5.935340485075374e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>5.974165783764199e-08</v>
+        <v>5.974165783764211e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>5.974165783764199e-08</v>
+        <v>5.974165783764211e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>5.938723322706439e-08</v>
+        <v>5.938723322706442e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>5.966835458757968e-08</v>
+        <v>5.966835458757978e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>5.974165783764199e-08</v>
+        <v>5.974165783764211e-08</v>
       </c>
       <c r="M3" t="n">
-        <v>5.93283095998817e-08</v>
+        <v>5.932830959988181e-08</v>
       </c>
       <c r="N3" t="n">
-        <v>5.974165783764199e-08</v>
+        <v>5.974165783764211e-08</v>
       </c>
       <c r="O3" t="n">
-        <v>5.952085414111808e-08</v>
+        <v>5.952085414111819e-08</v>
       </c>
       <c r="P3" t="n">
-        <v>5.931328666752005e-08</v>
+        <v>5.931328666752016e-08</v>
       </c>
       <c r="Q3" t="n">
-        <v>5.973948806933354e-08</v>
+        <v>5.973948806933366e-08</v>
       </c>
       <c r="R3" t="n">
-        <v>6.015619210818503e-08</v>
+        <v>6.015619210818513e-08</v>
       </c>
       <c r="S3" t="n">
-        <v>5.974165783764199e-08</v>
+        <v>5.974165783764211e-08</v>
       </c>
       <c r="T3" t="n">
-        <v>5.944441432938325e-08</v>
+        <v>5.944441432938337e-08</v>
       </c>
       <c r="U3" t="n">
-        <v>6.035672838081666e-08</v>
+        <v>6.035672838081678e-08</v>
       </c>
       <c r="V3" t="n">
-        <v>4.435474133265363e-08</v>
+        <v>4.435474133265334e-08</v>
       </c>
       <c r="W3" t="n">
-        <v>5.974165783764199e-08</v>
+        <v>5.974165783764211e-08</v>
       </c>
       <c r="X3" t="n">
-        <v>6.033474250959059e-08</v>
+        <v>6.033474250959071e-08</v>
       </c>
       <c r="Y3" t="n">
-        <v>5.888082059030623e-08</v>
+        <v>5.888082059030635e-08</v>
       </c>
       <c r="Z3" t="n">
-        <v>5.97248151153364e-08</v>
+        <v>5.972481511533651e-08</v>
       </c>
       <c r="AA3" t="n">
-        <v>5.974165783764199e-08</v>
+        <v>5.974165783764211e-08</v>
       </c>
       <c r="AB3" t="n">
-        <v>6.167306243339484e-08</v>
+        <v>6.167306243339494e-08</v>
       </c>
     </row>
     <row r="4">
@@ -4906,85 +4906,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.863538115972263e-07</v>
+        <v>1.863538115972281e-07</v>
       </c>
       <c r="C4" t="n">
-        <v>2.215320545739495e-07</v>
+        <v>2.215320545739494e-07</v>
       </c>
       <c r="D4" t="n">
-        <v>3.157325290316862e-07</v>
+        <v>3.157325290316916e-07</v>
       </c>
       <c r="E4" t="n">
-        <v>1.91064385073643e-07</v>
+        <v>1.910643850736437e-07</v>
       </c>
       <c r="F4" t="n">
-        <v>4.841258328476709e-07</v>
+        <v>4.841258328476686e-07</v>
       </c>
       <c r="G4" t="n">
-        <v>1.774183762748788e-06</v>
+        <v>1.774183762748785e-06</v>
       </c>
       <c r="H4" t="n">
-        <v>2.333771388672597e-07</v>
+        <v>2.333771388672599e-07</v>
       </c>
       <c r="I4" t="n">
-        <v>4.529523305570279e-07</v>
+        <v>4.529523305570278e-07</v>
       </c>
       <c r="J4" t="n">
-        <v>8.638245557907867e-07</v>
+        <v>8.638245557907842e-07</v>
       </c>
       <c r="K4" t="n">
-        <v>5.054753385807424e-07</v>
+        <v>5.054753385807426e-07</v>
       </c>
       <c r="L4" t="n">
-        <v>2.354757086765475e-06</v>
+        <v>2.354757086765474e-06</v>
       </c>
       <c r="M4" t="n">
-        <v>6.309123274257616e-07</v>
+        <v>6.309123274257596e-07</v>
       </c>
       <c r="N4" t="n">
-        <v>1.898413458756115e-07</v>
+        <v>1.898413458756118e-07</v>
       </c>
       <c r="O4" t="n">
-        <v>2.748881179692095e-07</v>
+        <v>2.748881179692099e-07</v>
       </c>
       <c r="P4" t="n">
-        <v>3.156452709270247e-07</v>
+        <v>3.156452709270223e-07</v>
       </c>
       <c r="Q4" t="n">
         <v>3.412521513353915e-07</v>
       </c>
       <c r="R4" t="n">
-        <v>3.007516536547509e-07</v>
+        <v>3.007516536547511e-07</v>
       </c>
       <c r="S4" t="n">
-        <v>3.574444086294014e-07</v>
+        <v>3.574444086294044e-07</v>
       </c>
       <c r="T4" t="n">
-        <v>3.977573791153215e-07</v>
+        <v>3.977573791153225e-07</v>
       </c>
       <c r="U4" t="n">
-        <v>4.995677684804548e-07</v>
+        <v>4.995677684804541e-07</v>
       </c>
       <c r="V4" t="n">
-        <v>2.543172608393396e-07</v>
+        <v>2.543172608393383e-07</v>
       </c>
       <c r="W4" t="n">
-        <v>5.635640626585422e-07</v>
+        <v>5.635640626585419e-07</v>
       </c>
       <c r="X4" t="n">
-        <v>1.907524916064125e-06</v>
+        <v>1.907524916064118e-06</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.104117098641403e-06</v>
+        <v>1.1041170986414e-06</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.818694750702645e-07</v>
+        <v>3.818694750702654e-07</v>
       </c>
       <c r="AA4" t="n">
-        <v>4.858595546330122e-07</v>
+        <v>4.858595546330118e-07</v>
       </c>
       <c r="AB4" t="n">
-        <v>8.366467315103157e-07</v>
+        <v>8.366467315103143e-07</v>
       </c>
     </row>
     <row r="5">
@@ -4994,85 +4994,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.957394603221324e-08</v>
+        <v>4.957394603221362e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>4.957394603221317e-08</v>
+        <v>4.957394603221369e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>4.957394603221317e-08</v>
+        <v>4.957394603221369e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>4.957394603221317e-08</v>
+        <v>4.957394603221369e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>4.957394603221317e-08</v>
+        <v>4.957394603221341e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>4.957394603221317e-08</v>
+        <v>4.957394603221369e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>4.957394603221317e-08</v>
+        <v>4.957394603221369e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>4.957394603221317e-08</v>
+        <v>4.957394603221369e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>4.928371835348926e-08</v>
+        <v>4.928371835348941e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>4.957394603221317e-08</v>
+        <v>4.957394603221369e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>4.957394603221323e-08</v>
+        <v>4.957394603221371e-08</v>
       </c>
       <c r="M5" t="n">
-        <v>4.957394603221317e-08</v>
+        <v>4.957394603221369e-08</v>
       </c>
       <c r="N5" t="n">
-        <v>1.898413458756115e-07</v>
+        <v>4.957394603221341e-08</v>
       </c>
       <c r="O5" t="n">
-        <v>4.957394603221317e-08</v>
+        <v>4.957394603221341e-08</v>
       </c>
       <c r="P5" t="n">
-        <v>4.957394603221317e-08</v>
+        <v>4.957394603221341e-08</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.957394603221317e-08</v>
+        <v>4.957394603221341e-08</v>
       </c>
       <c r="R5" t="n">
-        <v>4.957394603221317e-08</v>
+        <v>4.957394603221369e-08</v>
       </c>
       <c r="S5" t="n">
-        <v>4.957394603221317e-08</v>
+        <v>4.957394603221369e-08</v>
       </c>
       <c r="T5" t="n">
-        <v>4.957394603221317e-08</v>
+        <v>4.957394603221369e-08</v>
       </c>
       <c r="U5" t="n">
-        <v>4.938464694321675e-08</v>
+        <v>4.938464694321709e-08</v>
       </c>
       <c r="V5" t="n">
-        <v>4.762132743114029e-08</v>
+        <v>4.762132743113988e-08</v>
       </c>
       <c r="W5" t="n">
-        <v>4.957394603221317e-08</v>
+        <v>4.957394603221341e-08</v>
       </c>
       <c r="X5" t="n">
-        <v>4.957394603221324e-08</v>
+        <v>4.957394603221342e-08</v>
       </c>
       <c r="Y5" t="n">
-        <v>4.938464694321675e-08</v>
+        <v>4.938464694321709e-08</v>
       </c>
       <c r="Z5" t="n">
-        <v>4.957394603221317e-08</v>
+        <v>4.957394603221369e-08</v>
       </c>
       <c r="AA5" t="n">
-        <v>4.957394603221317e-08</v>
+        <v>4.957394603221369e-08</v>
       </c>
       <c r="AB5" t="n">
-        <v>4.957394603221317e-08</v>
+        <v>4.957394603221341e-08</v>
       </c>
     </row>
     <row r="6">
@@ -5082,85 +5082,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.144986681519964e-08</v>
+        <v>4.144986681519969e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>4.144986681519964e-08</v>
+        <v>4.144986681519969e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>8.229910835858037e-08</v>
+        <v>8.229910835858095e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>8.229910835858037e-08</v>
+        <v>8.229910835858095e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>4.144986681519964e-08</v>
+        <v>4.144986681519969e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>4.144986681519964e-08</v>
+        <v>4.144986681519969e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>8.229910835858037e-08</v>
+        <v>8.229910835858095e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>4.144986681519964e-08</v>
+        <v>4.144986681519969e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>8.200888067985628e-08</v>
+        <v>8.200888067985638e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>8.229910835858037e-08</v>
+        <v>8.229910835858095e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>4.144986681519964e-08</v>
+        <v>4.144986681519969e-08</v>
       </c>
       <c r="M6" t="n">
-        <v>4.144986681519964e-08</v>
+        <v>4.144986681519969e-08</v>
       </c>
       <c r="N6" t="n">
-        <v>1.898413458756115e-07</v>
+        <v>4.150994514636533e-08</v>
       </c>
       <c r="O6" t="n">
-        <v>4.165273518284587e-08</v>
+        <v>4.165273518284615e-08</v>
       </c>
       <c r="P6" t="n">
-        <v>8.306769760558074e-08</v>
+        <v>8.306769760558124e-08</v>
       </c>
       <c r="Q6" t="n">
-        <v>8.229910835858037e-08</v>
+        <v>8.229910835858095e-08</v>
       </c>
       <c r="R6" t="n">
-        <v>8.229910835858037e-08</v>
+        <v>8.229910835858095e-08</v>
       </c>
       <c r="S6" t="n">
-        <v>4.144986681519964e-08</v>
+        <v>4.144986681519969e-08</v>
       </c>
       <c r="T6" t="n">
-        <v>8.229910835858037e-08</v>
+        <v>8.229910835858095e-08</v>
       </c>
       <c r="U6" t="n">
-        <v>8.229910835858037e-08</v>
+        <v>8.229910835858095e-08</v>
       </c>
       <c r="V6" t="n">
-        <v>3.949724821412693e-08</v>
+        <v>3.949724821412598e-08</v>
       </c>
       <c r="W6" t="n">
-        <v>4.238596305831377e-08</v>
+        <v>4.238596305831393e-08</v>
       </c>
       <c r="X6" t="n">
-        <v>4.144986681519964e-08</v>
+        <v>4.144986681519969e-08</v>
       </c>
       <c r="Y6" t="n">
-        <v>4.205598034593067e-08</v>
+        <v>4.205598034593058e-08</v>
       </c>
       <c r="Z6" t="n">
-        <v>4.144986681519964e-08</v>
+        <v>4.144986681519969e-08</v>
       </c>
       <c r="AA6" t="n">
-        <v>8.229910835858037e-08</v>
+        <v>8.229910835858095e-08</v>
       </c>
       <c r="AB6" t="n">
-        <v>4.162905547641083e-08</v>
+        <v>4.162905547641124e-08</v>
       </c>
     </row>
     <row r="7">
@@ -5170,85 +5170,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>7.867087638161042e-08</v>
+        <v>7.867087638161061e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>7.867087638161034e-08</v>
+        <v>7.867087638161061e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>7.867087638161034e-08</v>
+        <v>7.867087638161061e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>7.867087638161034e-08</v>
+        <v>7.867087638161061e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>7.867087638161034e-08</v>
+        <v>7.867087638161061e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>7.867087638161034e-08</v>
+        <v>7.867087638161061e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>7.867087638161034e-08</v>
+        <v>7.867087638161061e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>7.867087638161034e-08</v>
+        <v>7.867087638161061e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>7.838064870288635e-08</v>
+        <v>7.838064870288643e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>7.867087638161034e-08</v>
+        <v>7.867087638161061e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>7.867087638161044e-08</v>
+        <v>7.867087638161061e-08</v>
       </c>
       <c r="M7" t="n">
-        <v>7.867087638161034e-08</v>
+        <v>7.867087638161061e-08</v>
       </c>
       <c r="N7" t="n">
-        <v>1.898413458756115e-07</v>
+        <v>7.867087638161061e-08</v>
       </c>
       <c r="O7" t="n">
-        <v>7.866370661264113e-08</v>
+        <v>7.866370661264133e-08</v>
       </c>
       <c r="P7" t="n">
-        <v>7.866370661264113e-08</v>
+        <v>7.866370661264133e-08</v>
       </c>
       <c r="Q7" t="n">
-        <v>7.867087638161034e-08</v>
+        <v>7.867087638161061e-08</v>
       </c>
       <c r="R7" t="n">
-        <v>7.867087638161034e-08</v>
+        <v>7.867087638161061e-08</v>
       </c>
       <c r="S7" t="n">
-        <v>7.867087638161034e-08</v>
+        <v>7.867087638161061e-08</v>
       </c>
       <c r="T7" t="n">
-        <v>7.867087638161034e-08</v>
+        <v>7.867087638161061e-08</v>
       </c>
       <c r="U7" t="n">
         <v>7.863162560122311e-08</v>
       </c>
       <c r="V7" t="n">
-        <v>7.671825778053762e-08</v>
+        <v>7.671825778053688e-08</v>
       </c>
       <c r="W7" t="n">
-        <v>7.867087638161034e-08</v>
+        <v>7.867087638161061e-08</v>
       </c>
       <c r="X7" t="n">
-        <v>7.867087638161044e-08</v>
+        <v>7.867087638161061e-08</v>
       </c>
       <c r="Y7" t="n">
-        <v>7.867087638161034e-08</v>
+        <v>7.867087638161061e-08</v>
       </c>
       <c r="Z7" t="n">
-        <v>7.867087638161034e-08</v>
+        <v>7.867087638161061e-08</v>
       </c>
       <c r="AA7" t="n">
-        <v>7.867087638161034e-08</v>
+        <v>7.867087638161061e-08</v>
       </c>
       <c r="AB7" t="n">
-        <v>7.867087638161034e-08</v>
+        <v>7.867087638161061e-08</v>
       </c>
     </row>
     <row r="8">
@@ -5258,34 +5258,34 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.273895140393008e-07</v>
+        <v>1.273895140393007e-07</v>
       </c>
       <c r="C8" t="n">
-        <v>1.924367102011793e-07</v>
+        <v>1.924367102011792e-07</v>
       </c>
       <c r="D8" t="n">
-        <v>1.924367102011793e-07</v>
+        <v>1.924367102011792e-07</v>
       </c>
       <c r="E8" t="n">
-        <v>1.57800997016619e-07</v>
+        <v>1.578009970166191e-07</v>
       </c>
       <c r="F8" t="n">
         <v>1.375231069762116e-07</v>
       </c>
       <c r="G8" t="n">
-        <v>2.059246700688019e-07</v>
+        <v>2.059246700688017e-07</v>
       </c>
       <c r="H8" t="n">
-        <v>1.924367102011793e-07</v>
+        <v>1.924367102011792e-07</v>
       </c>
       <c r="I8" t="n">
-        <v>1.924367102011793e-07</v>
+        <v>1.924367102011792e-07</v>
       </c>
       <c r="J8" t="n">
-        <v>1.921464825224551e-07</v>
+        <v>1.92146482522455e-07</v>
       </c>
       <c r="K8" t="n">
-        <v>1.924367102011793e-07</v>
+        <v>1.924367102011792e-07</v>
       </c>
       <c r="L8" t="n">
         <v>1.924367102011793e-07</v>
@@ -5294,46 +5294,46 @@
         <v>1.924367102011743e-07</v>
       </c>
       <c r="N8" t="n">
-        <v>1.898413458756115e-07</v>
+        <v>1.420142510140674e-07</v>
       </c>
       <c r="O8" t="n">
-        <v>1.5587078060785e-07</v>
+        <v>1.558707806078499e-07</v>
       </c>
       <c r="P8" t="n">
         <v>1.524742103839013e-07</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.146062553618259e-07</v>
+        <v>1.146062553618262e-07</v>
       </c>
       <c r="R8" t="n">
-        <v>1.924367102011793e-07</v>
+        <v>1.924367102011792e-07</v>
       </c>
       <c r="S8" t="n">
-        <v>1.924367102011793e-07</v>
+        <v>1.924367102011792e-07</v>
       </c>
       <c r="T8" t="n">
-        <v>1.924367102011793e-07</v>
+        <v>1.924367102011792e-07</v>
       </c>
       <c r="U8" t="n">
-        <v>1.606631799301994e-07</v>
+        <v>1.606631799301993e-07</v>
       </c>
       <c r="V8" t="n">
-        <v>1.726782900390505e-07</v>
+        <v>1.726782900390503e-07</v>
       </c>
       <c r="W8" t="n">
         <v>1.924494938340238e-07</v>
       </c>
       <c r="X8" t="n">
-        <v>1.205679601389174e-07</v>
+        <v>1.205679601389176e-07</v>
       </c>
       <c r="Y8" t="n">
         <v>2.570691251347594e-07</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.261812289731666e-07</v>
+        <v>1.261812289731669e-07</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.924367102011793e-07</v>
+        <v>1.924367102011792e-07</v>
       </c>
       <c r="AB8" t="n">
         <v>2.603839457501857e-07</v>
@@ -5346,85 +5346,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.545858787604029e-07</v>
+        <v>1.54585878760403e-07</v>
       </c>
       <c r="C9" t="n">
-        <v>1.904191408422627e-07</v>
+        <v>1.904191408422631e-07</v>
       </c>
       <c r="D9" t="n">
-        <v>1.904191408422627e-07</v>
+        <v>1.904191408422631e-07</v>
       </c>
       <c r="E9" t="n">
         <v>1.821490117838977e-07</v>
       </c>
       <c r="F9" t="n">
-        <v>1.07813621209933e-07</v>
+        <v>1.078136212099332e-07</v>
       </c>
       <c r="G9" t="n">
-        <v>1.904191950137311e-07</v>
+        <v>1.90419195013731e-07</v>
       </c>
       <c r="H9" t="n">
-        <v>1.904191408422627e-07</v>
+        <v>1.904191408422631e-07</v>
       </c>
       <c r="I9" t="n">
-        <v>1.904191408422627e-07</v>
+        <v>1.904191408422631e-07</v>
       </c>
       <c r="J9" t="n">
-        <v>1.901289131635387e-07</v>
+        <v>1.901289131635385e-07</v>
       </c>
       <c r="K9" t="n">
-        <v>1.904191408422627e-07</v>
+        <v>1.904191408422631e-07</v>
       </c>
       <c r="L9" t="n">
-        <v>1.904191408422627e-07</v>
+        <v>1.904191408422632e-07</v>
       </c>
       <c r="M9" t="n">
-        <v>1.904191408422627e-07</v>
+        <v>1.904191408422631e-07</v>
       </c>
       <c r="N9" t="n">
-        <v>1.898413458756115e-07</v>
+        <v>1.904191408422631e-07</v>
       </c>
       <c r="O9" t="n">
-        <v>2.022943091003646e-07</v>
+        <v>2.022943091003645e-07</v>
       </c>
       <c r="P9" t="n">
-        <v>2.048769426715594e-07</v>
+        <v>2.048769426715592e-07</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.904191950137311e-07</v>
+        <v>1.90419195013731e-07</v>
       </c>
       <c r="R9" t="n">
-        <v>1.904191408422627e-07</v>
+        <v>1.904191408422631e-07</v>
       </c>
       <c r="S9" t="n">
-        <v>1.904191408422627e-07</v>
+        <v>1.904191408422631e-07</v>
       </c>
       <c r="T9" t="n">
-        <v>1.904191408422627e-07</v>
+        <v>1.904191408422631e-07</v>
       </c>
       <c r="U9" t="n">
-        <v>1.904191408422627e-07</v>
+        <v>1.904191408422631e-07</v>
       </c>
       <c r="V9" t="n">
-        <v>2.298174068610301e-07</v>
+        <v>2.298174068610289e-07</v>
       </c>
       <c r="W9" t="n">
-        <v>1.904191408422627e-07</v>
+        <v>1.904191408422631e-07</v>
       </c>
       <c r="X9" t="n">
-        <v>1.904191408422627e-07</v>
+        <v>1.904191408422632e-07</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.904191408422627e-07</v>
+        <v>1.904191408422631e-07</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.688148917357812e-07</v>
+        <v>1.688148917357813e-07</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.904191408422627e-07</v>
+        <v>1.904191408422631e-07</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.904191408422627e-07</v>
+        <v>1.904191408422631e-07</v>
       </c>
     </row>
     <row r="10">
@@ -5434,85 +5434,85 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>5.646469992552482e-08</v>
+        <v>5.646469992552499e-08</v>
       </c>
       <c r="C10" t="n">
-        <v>5.579392518358064e-08</v>
+        <v>5.579392518358072e-08</v>
       </c>
       <c r="D10" t="n">
-        <v>5.384005921824752e-08</v>
+        <v>5.384005921824783e-08</v>
       </c>
       <c r="E10" t="n">
-        <v>9.323802572628733e-08</v>
+        <v>9.32380257262875e-08</v>
       </c>
       <c r="F10" t="n">
-        <v>5.004471509864026e-08</v>
+        <v>5.004471509864045e-08</v>
       </c>
       <c r="G10" t="n">
-        <v>1.440751484525091e-08</v>
+        <v>1.440751484525111e-08</v>
       </c>
       <c r="H10" t="n">
-        <v>5.604252474729204e-08</v>
+        <v>5.604252474729211e-08</v>
       </c>
       <c r="I10" t="n">
-        <v>5.094851227476353e-08</v>
+        <v>5.094851227476356e-08</v>
       </c>
       <c r="J10" t="n">
-        <v>3.896640345408875e-08</v>
+        <v>3.896640345408894e-08</v>
       </c>
       <c r="K10" t="n">
-        <v>4.869581326258395e-08</v>
+        <v>4.869581326258408e-08</v>
       </c>
       <c r="L10" t="n">
-        <v>3.185052088109061e-09</v>
+        <v>3.185052088109172e-09</v>
       </c>
       <c r="M10" t="n">
-        <v>4.6343914559137e-08</v>
+        <v>4.634391455913716e-08</v>
       </c>
       <c r="N10" t="n">
-        <v>5.669600633638344e-08</v>
+        <v>5.66960063363835e-08</v>
       </c>
       <c r="O10" t="n">
-        <v>5.389346950888403e-08</v>
+        <v>5.389346950888409e-08</v>
       </c>
       <c r="P10" t="n">
-        <v>5.260827210895424e-08</v>
+        <v>5.260827210895433e-08</v>
       </c>
       <c r="Q10" t="n">
-        <v>5.302436979309001e-08</v>
+        <v>5.302436979309007e-08</v>
       </c>
       <c r="R10" t="n">
-        <v>5.490688221067889e-08</v>
+        <v>5.490688221067894e-08</v>
       </c>
       <c r="S10" t="n">
-        <v>5.217992092900598e-08</v>
+        <v>5.21799209290061e-08</v>
       </c>
       <c r="T10" t="n">
-        <v>5.192387628716498e-08</v>
+        <v>5.192387628716508e-08</v>
       </c>
       <c r="U10" t="n">
-        <v>4.929867251764393e-08</v>
+        <v>4.929867251764399e-08</v>
       </c>
       <c r="V10" t="n">
-        <v>3.887239002959806e-08</v>
+        <v>3.887239002959772e-08</v>
       </c>
       <c r="W10" t="n">
-        <v>4.793905865460252e-08</v>
+        <v>4.793905865460263e-08</v>
       </c>
       <c r="X10" t="n">
-        <v>1.706228759838596e-08</v>
+        <v>1.706228759838609e-08</v>
       </c>
       <c r="Y10" t="n">
-        <v>3.478507768941829e-08</v>
+        <v>3.478507768941843e-08</v>
       </c>
       <c r="Z10" t="n">
-        <v>5.08399652712553e-08</v>
+        <v>5.083996527125538e-08</v>
       </c>
       <c r="AA10" t="n">
-        <v>4.979785196828525e-08</v>
+        <v>4.979785196828534e-08</v>
       </c>
       <c r="AB10" t="n">
-        <v>4.511693714909611e-08</v>
+        <v>4.511693714909622e-08</v>
       </c>
     </row>
     <row r="11">
@@ -5522,85 +5522,85 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>5.789744203866075e-08</v>
+        <v>5.789744203866086e-08</v>
       </c>
       <c r="C11" t="n">
-        <v>5.759282797642703e-08</v>
+        <v>5.759282797642708e-08</v>
       </c>
       <c r="D11" t="n">
-        <v>5.71600191270485e-08</v>
+        <v>5.716001912704866e-08</v>
       </c>
       <c r="E11" t="n">
-        <v>9.440458287919885e-08</v>
+        <v>9.440458287919901e-08</v>
       </c>
       <c r="F11" t="n">
-        <v>5.600777928643601e-08</v>
+        <v>5.600777928643621e-08</v>
       </c>
       <c r="G11" t="n">
-        <v>4.559151085311769e-08</v>
+        <v>4.559151085311778e-08</v>
       </c>
       <c r="H11" t="n">
-        <v>5.779047609516503e-08</v>
+        <v>5.779047609516509e-08</v>
       </c>
       <c r="I11" t="n">
-        <v>5.634082949051806e-08</v>
+        <v>5.634082949051809e-08</v>
       </c>
       <c r="J11" t="n">
-        <v>5.263889204627886e-08</v>
+        <v>5.26388920462789e-08</v>
       </c>
       <c r="K11" t="n">
-        <v>5.564879020461055e-08</v>
+        <v>5.564879020461063e-08</v>
       </c>
       <c r="L11" t="n">
-        <v>4.267091554994611e-08</v>
+        <v>4.267091554994612e-08</v>
       </c>
       <c r="M11" t="n">
-        <v>5.477724263725532e-08</v>
+        <v>5.477724263725544e-08</v>
       </c>
       <c r="N11" t="n">
-        <v>5.796969839865032e-08</v>
+        <v>5.796969839865039e-08</v>
       </c>
       <c r="O11" t="n">
-        <v>5.702026274398045e-08</v>
+        <v>5.702026274398048e-08</v>
       </c>
       <c r="P11" t="n">
-        <v>5.652019525240175e-08</v>
+        <v>5.652019525240179e-08</v>
       </c>
       <c r="Q11" t="n">
-        <v>5.692382601828722e-08</v>
+        <v>5.692382601828729e-08</v>
       </c>
       <c r="R11" t="n">
-        <v>5.772783644772967e-08</v>
+        <v>5.772783644772977e-08</v>
       </c>
       <c r="S11" t="n">
-        <v>5.667204109722359e-08</v>
+        <v>5.667204109722375e-08</v>
       </c>
       <c r="T11" t="n">
-        <v>5.642897384988396e-08</v>
+        <v>5.642897384988403e-08</v>
       </c>
       <c r="U11" t="n">
-        <v>5.623692074945924e-08</v>
+        <v>5.623692074945934e-08</v>
       </c>
       <c r="V11" t="n">
-        <v>4.209884092057784e-08</v>
+        <v>4.209884092057799e-08</v>
       </c>
       <c r="W11" t="n">
-        <v>5.546724386039397e-08</v>
+        <v>5.546724386039396e-08</v>
       </c>
       <c r="X11" t="n">
-        <v>4.707099533700453e-08</v>
+        <v>4.707099533700471e-08</v>
       </c>
       <c r="Y11" t="n">
-        <v>5.11766696731252e-08</v>
+        <v>5.117666967312529e-08</v>
       </c>
       <c r="Z11" t="n">
-        <v>5.627473941774591e-08</v>
+        <v>5.627473941774599e-08</v>
       </c>
       <c r="AA11" t="n">
-        <v>5.599943302488204e-08</v>
+        <v>5.599943302488211e-08</v>
       </c>
       <c r="AB11" t="n">
-        <v>5.589673093989587e-08</v>
+        <v>5.589673093989607e-08</v>
       </c>
     </row>
   </sheetData>
@@ -6066,7 +6066,7 @@
         <v>4.991941534710248e-08</v>
       </c>
       <c r="N5" t="n">
-        <v>7.415914421012229e-07</v>
+        <v>4.991941534710258e-08</v>
       </c>
       <c r="O5" t="n">
         <v>4.991941534710258e-08</v>
@@ -6154,7 +6154,7 @@
         <v>8.196078999659635e-08</v>
       </c>
       <c r="N6" t="n">
-        <v>7.415914421012229e-07</v>
+        <v>4.085819353682552e-08</v>
       </c>
       <c r="O6" t="n">
         <v>8.303450817734673e-08</v>
@@ -6242,7 +6242,7 @@
         <v>7.961204157813203e-08</v>
       </c>
       <c r="N7" t="n">
-        <v>7.415914421012229e-07</v>
+        <v>7.961204157813203e-08</v>
       </c>
       <c r="O7" t="n">
         <v>7.960443895875453e-08</v>
@@ -6330,7 +6330,7 @@
         <v>1.983407768500698e-07</v>
       </c>
       <c r="N8" t="n">
-        <v>7.415914421012229e-07</v>
+        <v>1.459196884459235e-07</v>
       </c>
       <c r="O8" t="n">
         <v>1.603254587028527e-07</v>
@@ -6418,7 +6418,7 @@
         <v>2.057083497965208e-07</v>
       </c>
       <c r="N9" t="n">
-        <v>7.415914421012229e-07</v>
+        <v>2.057083497965208e-07</v>
       </c>
       <c r="O9" t="n">
         <v>2.187337612361906e-07</v>
@@ -7066,7 +7066,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.767793050769041e-08</v>
+        <v>4.767793050769042e-08</v>
       </c>
       <c r="C5" t="n">
         <v>4.76779305076904e-08</v>
@@ -7102,7 +7102,7 @@
         <v>4.76779305076904e-08</v>
       </c>
       <c r="N5" t="n">
-        <v>4.287540941151468e-07</v>
+        <v>4.767793050769032e-08</v>
       </c>
       <c r="O5" t="n">
         <v>4.767793050769032e-08</v>
@@ -7190,7 +7190,7 @@
         <v>7.579503469512255e-08</v>
       </c>
       <c r="N6" t="n">
-        <v>4.287540941151468e-07</v>
+        <v>3.971345637100876e-08</v>
       </c>
       <c r="O6" t="n">
         <v>7.657676394693675e-08</v>
@@ -7242,43 +7242,43 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>7.415553496610835e-08</v>
+        <v>7.415553496610836e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>7.415553496610835e-08</v>
+        <v>7.415553496610836e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>7.415553496610835e-08</v>
+        <v>7.415553496610836e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>7.415553496610835e-08</v>
+        <v>7.415553496610836e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>7.415553496610835e-08</v>
+        <v>7.415553496610836e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>7.415553496610835e-08</v>
+        <v>7.415553496610836e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>7.415553496610835e-08</v>
+        <v>7.415553496610836e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>7.415553496610835e-08</v>
+        <v>7.415553496610836e-08</v>
       </c>
       <c r="J7" t="n">
         <v>7.388170644741992e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>7.415553496610835e-08</v>
+        <v>7.415553496610836e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>7.415553496610835e-08</v>
+        <v>7.415553496610836e-08</v>
       </c>
       <c r="M7" t="n">
-        <v>7.415553496610835e-08</v>
+        <v>7.415553496610836e-08</v>
       </c>
       <c r="N7" t="n">
-        <v>4.287540941151468e-07</v>
+        <v>7.415553496610836e-08</v>
       </c>
       <c r="O7" t="n">
         <v>7.414840257979381e-08</v>
@@ -7287,16 +7287,16 @@
         <v>7.414840257979381e-08</v>
       </c>
       <c r="Q7" t="n">
-        <v>7.415553496610835e-08</v>
+        <v>7.415553496610836e-08</v>
       </c>
       <c r="R7" t="n">
-        <v>7.415553496610835e-08</v>
+        <v>7.415553496610836e-08</v>
       </c>
       <c r="S7" t="n">
-        <v>7.415553496610835e-08</v>
+        <v>7.415553496610836e-08</v>
       </c>
       <c r="T7" t="n">
-        <v>7.415553496610835e-08</v>
+        <v>7.415553496610836e-08</v>
       </c>
       <c r="U7" t="n">
         <v>7.414600370124936e-08</v>
@@ -7305,22 +7305,22 @@
         <v>7.230293140576748e-08</v>
       </c>
       <c r="W7" t="n">
-        <v>7.415553496610835e-08</v>
+        <v>7.415553496610836e-08</v>
       </c>
       <c r="X7" t="n">
-        <v>7.415553496610835e-08</v>
+        <v>7.415553496610836e-08</v>
       </c>
       <c r="Y7" t="n">
-        <v>7.415553496610835e-08</v>
+        <v>7.415553496610836e-08</v>
       </c>
       <c r="Z7" t="n">
-        <v>7.415553496610835e-08</v>
+        <v>7.415553496610836e-08</v>
       </c>
       <c r="AA7" t="n">
-        <v>7.415553496610835e-08</v>
+        <v>7.415553496610836e-08</v>
       </c>
       <c r="AB7" t="n">
-        <v>7.415553496610835e-08</v>
+        <v>7.415553496610836e-08</v>
       </c>
     </row>
     <row r="8">
@@ -7366,7 +7366,7 @@
         <v>1.813850437020199e-07</v>
       </c>
       <c r="N8" t="n">
-        <v>4.287540941151468e-07</v>
+        <v>1.340828881187512e-07</v>
       </c>
       <c r="O8" t="n">
         <v>1.470819311897345e-07</v>
@@ -7454,7 +7454,7 @@
         <v>1.747649608827057e-07</v>
       </c>
       <c r="N9" t="n">
-        <v>4.287540941151468e-07</v>
+        <v>1.747649608827057e-07</v>
       </c>
       <c r="O9" t="n">
         <v>1.85565853827849e-07</v>
@@ -7524,7 +7524,7 @@
         <v>5.000125500909275e-08</v>
       </c>
       <c r="H10" t="n">
-        <v>5.227430807344497e-08</v>
+        <v>5.227430807344496e-08</v>
       </c>
       <c r="I10" t="n">
         <v>5.102459246946983e-08</v>
@@ -7606,7 +7606,7 @@
         <v>9.257270932230475e-08</v>
       </c>
       <c r="F11" t="n">
-        <v>5.429441037168701e-08</v>
+        <v>5.429441037168702e-08</v>
       </c>
       <c r="G11" t="n">
         <v>5.440558047828003e-08</v>
@@ -7636,7 +7636,7 @@
         <v>5.339336342127166e-08</v>
       </c>
       <c r="P11" t="n">
-        <v>5.521634660794207e-08</v>
+        <v>5.521634660794208e-08</v>
       </c>
       <c r="Q11" t="n">
         <v>5.569810264627085e-08</v>
@@ -8050,7 +8050,7 @@
         <v>1.972136324549675e-07</v>
       </c>
       <c r="N4" t="n">
-        <v>2.669090081682988e-07</v>
+        <v>2.669090081682989e-07</v>
       </c>
       <c r="O4" t="n">
         <v>4.992998613095494e-07</v>
@@ -8138,7 +8138,7 @@
         <v>4.863318065705461e-08</v>
       </c>
       <c r="N5" t="n">
-        <v>2.669090081682989e-07</v>
+        <v>4.863318065705471e-08</v>
       </c>
       <c r="O5" t="n">
         <v>4.863318065705471e-08</v>
@@ -8226,7 +8226,7 @@
         <v>7.699474797236656e-08</v>
       </c>
       <c r="N6" t="n">
-        <v>2.669090081682988e-07</v>
+        <v>4.135556609707551e-08</v>
       </c>
       <c r="O6" t="n">
         <v>4.149848735243407e-08</v>
@@ -8314,7 +8314,7 @@
         <v>7.519519867868795e-08</v>
       </c>
       <c r="N7" t="n">
-        <v>2.669090081682988e-07</v>
+        <v>7.519519867868795e-08</v>
       </c>
       <c r="O7" t="n">
         <v>7.51880287926448e-08</v>
@@ -8402,7 +8402,7 @@
         <v>1.821145014422848e-07</v>
       </c>
       <c r="N8" t="n">
-        <v>2.669090081682989e-07</v>
+        <v>1.348870592275257e-07</v>
       </c>
       <c r="O8" t="n">
         <v>1.47865570416097e-07</v>
@@ -8490,7 +8490,7 @@
         <v>1.68165598567309e-07</v>
       </c>
       <c r="N9" t="n">
-        <v>2.669090081682988e-07</v>
+        <v>1.68165598567309e-07</v>
       </c>
       <c r="O9" t="n">
         <v>1.784225059510242e-07</v>
@@ -9174,7 +9174,7 @@
         <v>5.200068583099393e-08</v>
       </c>
       <c r="N5" t="n">
-        <v>1.244827939993536e-06</v>
+        <v>5.200068583099398e-08</v>
       </c>
       <c r="O5" t="n">
         <v>5.200068583099398e-08</v>
@@ -9262,7 +9262,7 @@
         <v>4.294291491841561e-08</v>
       </c>
       <c r="N6" t="n">
-        <v>1.244827939993536e-06</v>
+        <v>4.300448602569515e-08</v>
       </c>
       <c r="O6" t="n">
         <v>9.029427496591053e-08</v>
@@ -9350,7 +9350,7 @@
         <v>8.463404668406365e-08</v>
       </c>
       <c r="N7" t="n">
-        <v>1.244827939993536e-06</v>
+        <v>8.463404668406365e-08</v>
       </c>
       <c r="O7" t="n">
         <v>8.462641582140197e-08</v>
@@ -9438,7 +9438,7 @@
         <v>2.103950218426432e-07</v>
       </c>
       <c r="N8" t="n">
-        <v>1.244827939993536e-06</v>
+        <v>1.545679235938364e-07</v>
       </c>
       <c r="O8" t="n">
         <v>1.699096949290651e-07</v>
@@ -9526,7 +9526,7 @@
         <v>2.393358667132408e-07</v>
       </c>
       <c r="N9" t="n">
-        <v>1.244827939993536e-06</v>
+        <v>2.393358667132408e-07</v>
       </c>
       <c r="O9" t="n">
         <v>2.547220814353398e-07</v>
@@ -10210,7 +10210,7 @@
         <v>4.962876538430179e-08</v>
       </c>
       <c r="N5" t="n">
-        <v>2.738916618144422e-07</v>
+        <v>4.962876538430178e-08</v>
       </c>
       <c r="O5" t="n">
         <v>4.962876538430178e-08</v>
@@ -10298,7 +10298,7 @@
         <v>4.125915698648749e-08</v>
       </c>
       <c r="N6" t="n">
-        <v>2.738916618144422e-07</v>
+        <v>4.127243375297077e-08</v>
       </c>
       <c r="O6" t="n">
         <v>8.841976064015176e-08</v>
@@ -10386,7 +10386,7 @@
         <v>7.825703363635449e-08</v>
       </c>
       <c r="N7" t="n">
-        <v>2.738916618144422e-07</v>
+        <v>7.825703363635449e-08</v>
       </c>
       <c r="O7" t="n">
         <v>7.824988648033018e-08</v>
@@ -10474,7 +10474,7 @@
         <v>1.921533994444619e-07</v>
       </c>
       <c r="N8" t="n">
-        <v>2.738916618144422e-07</v>
+        <v>1.418706546795911e-07</v>
       </c>
       <c r="O8" t="n">
         <v>1.556887895369657e-07</v>
@@ -10562,7 +10562,7 @@
         <v>1.981449035191111e-07</v>
       </c>
       <c r="N9" t="n">
-        <v>2.738916618144422e-07</v>
+        <v>1.981449035191111e-07</v>
       </c>
       <c r="O9" t="n">
         <v>2.105617545203412e-07</v>

--- a/Results/Phase 2/Hydrogen/hydrogen particulate matter results.xlsx
+++ b/Results/Phase 2/Hydrogen/hydrogen particulate matter results.xlsx
@@ -586,85 +586,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.470587404325463e-08</v>
+        <v>6.47058740432545e-08</v>
       </c>
       <c r="C2" t="n">
-        <v>6.439382085122408e-08</v>
+        <v>6.43938208512239e-08</v>
       </c>
       <c r="D2" t="n">
-        <v>6.710086316714234e-08</v>
+        <v>6.710086316714226e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>9.844466498699423e-08</v>
+        <v>9.844466498699433e-08</v>
       </c>
       <c r="F2" t="n">
-        <v>6.676628668970099e-08</v>
+        <v>6.676628668970087e-08</v>
       </c>
       <c r="G2" t="n">
-        <v>7.67193242728658e-08</v>
+        <v>7.671932427286561e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>6.599662002079543e-08</v>
+        <v>6.599662002079581e-08</v>
       </c>
       <c r="I2" t="n">
         <v>6.825760900795994e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>6.877905992280704e-08</v>
+        <v>6.877905992280694e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>7.163087115925057e-08</v>
+        <v>7.163087115925037e-08</v>
       </c>
       <c r="L2" t="n">
-        <v>8.15414968151307e-08</v>
+        <v>8.154149681513088e-08</v>
       </c>
       <c r="M2" t="n">
-        <v>6.820110731878495e-08</v>
+        <v>6.820110731878481e-08</v>
       </c>
       <c r="N2" t="n">
-        <v>6.913702763897902e-08</v>
+        <v>6.913702763897888e-08</v>
       </c>
       <c r="O2" t="n">
-        <v>6.571179034574771e-08</v>
+        <v>6.571179034574749e-08</v>
       </c>
       <c r="P2" t="n">
-        <v>6.507653212227284e-08</v>
+        <v>6.507653212227282e-08</v>
       </c>
       <c r="Q2" t="n">
-        <v>6.553461691710435e-08</v>
+        <v>6.553461691710417e-08</v>
       </c>
       <c r="R2" t="n">
-        <v>6.577671842966162e-08</v>
+        <v>6.577671842966142e-08</v>
       </c>
       <c r="S2" t="n">
-        <v>6.517915891836672e-08</v>
+        <v>6.517915891836664e-08</v>
       </c>
       <c r="T2" t="n">
-        <v>6.743293240426528e-08</v>
+        <v>6.743293240426504e-08</v>
       </c>
       <c r="U2" t="n">
-        <v>6.653147356006978e-08</v>
+        <v>6.65314735600697e-08</v>
       </c>
       <c r="V2" t="n">
-        <v>4.935940367697307e-08</v>
+        <v>4.935940367697298e-08</v>
       </c>
       <c r="W2" t="n">
-        <v>6.581536868845564e-08</v>
+        <v>6.581536868845544e-08</v>
       </c>
       <c r="X2" t="n">
-        <v>6.763979889401978e-08</v>
+        <v>6.763979889401946e-08</v>
       </c>
       <c r="Y2" t="n">
-        <v>6.508508334448076e-08</v>
+        <v>6.508508334448062e-08</v>
       </c>
       <c r="Z2" t="n">
-        <v>6.565390389812655e-08</v>
+        <v>6.565390389812635e-08</v>
       </c>
       <c r="AA2" t="n">
-        <v>6.836634247073562e-08</v>
+        <v>6.836634247073543e-08</v>
       </c>
       <c r="AB2" t="n">
-        <v>6.701210277509112e-08</v>
+        <v>6.701210277509098e-08</v>
       </c>
     </row>
     <row r="3">
@@ -674,85 +674,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.437801362054353e-08</v>
+        <v>6.437801362054335e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>6.437801362054353e-08</v>
+        <v>6.437801362054335e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>6.437801362054353e-08</v>
+        <v>6.437801362054335e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>9.931399022454616e-08</v>
+        <v>9.931399022454615e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>6.437801362054353e-08</v>
+        <v>6.437801362054335e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>6.437801362054353e-08</v>
+        <v>6.437801362054335e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>6.437801362054353e-08</v>
+        <v>6.437801362054335e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>6.437801362054353e-08</v>
+        <v>6.437801362054335e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>6.38563292636445e-08</v>
+        <v>6.385632926364437e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>6.437801362054353e-08</v>
+        <v>6.437801362054335e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>6.437801362054353e-08</v>
+        <v>6.437801362054335e-08</v>
       </c>
       <c r="M3" t="n">
-        <v>6.437801362054353e-08</v>
+        <v>6.437801362054335e-08</v>
       </c>
       <c r="N3" t="n">
-        <v>6.437801362054353e-08</v>
+        <v>6.437801362054335e-08</v>
       </c>
       <c r="O3" t="n">
-        <v>6.437801362054353e-08</v>
+        <v>6.437801362054335e-08</v>
       </c>
       <c r="P3" t="n">
-        <v>6.437801362054353e-08</v>
+        <v>6.437801362054335e-08</v>
       </c>
       <c r="Q3" t="n">
-        <v>6.437801362054353e-08</v>
+        <v>6.437801362054335e-08</v>
       </c>
       <c r="R3" t="n">
-        <v>6.437801362054353e-08</v>
+        <v>6.437801362054335e-08</v>
       </c>
       <c r="S3" t="n">
-        <v>6.437801362054353e-08</v>
+        <v>6.437801362054335e-08</v>
       </c>
       <c r="T3" t="n">
-        <v>6.437801362054353e-08</v>
+        <v>6.437801362054335e-08</v>
       </c>
       <c r="U3" t="n">
-        <v>6.437801362054353e-08</v>
+        <v>6.437801362054335e-08</v>
       </c>
       <c r="V3" t="n">
-        <v>4.886940846942626e-08</v>
+        <v>4.886940846942621e-08</v>
       </c>
       <c r="W3" t="n">
-        <v>6.437801362054353e-08</v>
+        <v>6.437801362054335e-08</v>
       </c>
       <c r="X3" t="n">
-        <v>6.437801362054353e-08</v>
+        <v>6.437801362054335e-08</v>
       </c>
       <c r="Y3" t="n">
-        <v>6.437801362054353e-08</v>
+        <v>6.437801362054335e-08</v>
       </c>
       <c r="Z3" t="n">
-        <v>6.437801362054353e-08</v>
+        <v>6.437801362054335e-08</v>
       </c>
       <c r="AA3" t="n">
-        <v>6.437801362054353e-08</v>
+        <v>6.437801362054335e-08</v>
       </c>
       <c r="AB3" t="n">
-        <v>6.437801362054353e-08</v>
+        <v>6.437801362054335e-08</v>
       </c>
     </row>
     <row r="4">
@@ -762,85 +762,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.112835048392261e-07</v>
+        <v>4.11283504839211e-07</v>
       </c>
       <c r="C4" t="n">
         <v>3.546852487429447e-07</v>
       </c>
       <c r="D4" t="n">
-        <v>1.181072252792255e-06</v>
+        <v>1.181072252792257e-06</v>
       </c>
       <c r="E4" t="n">
-        <v>2.250952072804744e-07</v>
+        <v>2.25095207280473e-07</v>
       </c>
       <c r="F4" t="n">
-        <v>1.101757400578838e-06</v>
+        <v>1.101757400578837e-06</v>
       </c>
       <c r="G4" t="n">
-        <v>3.747872977822916e-06</v>
+        <v>3.747872977822912e-06</v>
       </c>
       <c r="H4" t="n">
-        <v>8.777968964059582e-07</v>
+        <v>8.777968964059574e-07</v>
       </c>
       <c r="I4" t="n">
-        <v>1.549207138955976e-06</v>
+        <v>1.549207138955975e-06</v>
       </c>
       <c r="J4" t="n">
-        <v>1.717785761199277e-06</v>
+        <v>1.717785761199275e-06</v>
       </c>
       <c r="K4" t="n">
-        <v>2.540569132789352e-06</v>
+        <v>2.540569132789348e-06</v>
       </c>
       <c r="L4" t="n">
-        <v>5.292789127963576e-06</v>
+        <v>5.292789127963462e-06</v>
       </c>
       <c r="M4" t="n">
         <v>1.532140566872968e-06</v>
       </c>
       <c r="N4" t="n">
-        <v>1.752249074064535e-06</v>
+        <v>1.752249074064536e-06</v>
       </c>
       <c r="O4" t="n">
-        <v>6.710485568106633e-07</v>
+        <v>6.710485568106643e-07</v>
       </c>
       <c r="P4" t="n">
-        <v>5.149760644606139e-07</v>
+        <v>5.149760644606128e-07</v>
       </c>
       <c r="Q4" t="n">
-        <v>6.917079349068292e-07</v>
+        <v>6.917079349068257e-07</v>
       </c>
       <c r="R4" t="n">
-        <v>7.952849416108463e-07</v>
+        <v>7.952849416108449e-07</v>
       </c>
       <c r="S4" t="n">
-        <v>5.510829657884011e-07</v>
+        <v>5.510829657883935e-07</v>
       </c>
       <c r="T4" t="n">
-        <v>1.286692261898868e-06</v>
+        <v>1.286692261898869e-06</v>
       </c>
       <c r="U4" t="n">
-        <v>9.432450056987235e-07</v>
+        <v>9.432450056987207e-07</v>
       </c>
       <c r="V4" t="n">
-        <v>3.82242173045033e-07</v>
+        <v>3.822421730450308e-07</v>
       </c>
       <c r="W4" t="n">
-        <v>7.574413060305747e-07</v>
+        <v>7.574413060305719e-07</v>
       </c>
       <c r="X4" t="n">
         <v>1.328366677806134e-06</v>
       </c>
       <c r="Y4" t="n">
-        <v>5.467252589368162e-07</v>
+        <v>5.467252589368159e-07</v>
       </c>
       <c r="Z4" t="n">
-        <v>6.803409510488418e-07</v>
+        <v>6.803409510488514e-07</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.508794890577954e-06</v>
+        <v>1.508794890577951e-06</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.209403258856242e-06</v>
+        <v>1.209403258856241e-06</v>
       </c>
     </row>
     <row r="5">
@@ -850,85 +850,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.570719262058474e-07</v>
+        <v>1.570719262058475e-07</v>
       </c>
       <c r="C5" t="n">
-        <v>2.398803713311698e-07</v>
+        <v>2.398803713311689e-07</v>
       </c>
       <c r="D5" t="n">
-        <v>2.398803713311698e-07</v>
+        <v>2.398803713311689e-07</v>
       </c>
       <c r="E5" t="n">
-        <v>1.957873169976271e-07</v>
+        <v>1.957873169976276e-07</v>
       </c>
       <c r="F5" t="n">
-        <v>1.699725141506873e-07</v>
+        <v>1.69972514150687e-07</v>
       </c>
       <c r="G5" t="n">
-        <v>2.570512418750812e-07</v>
+        <v>2.570512418750809e-07</v>
       </c>
       <c r="H5" t="n">
-        <v>2.398803713311698e-07</v>
+        <v>2.398803713311689e-07</v>
       </c>
       <c r="I5" t="n">
-        <v>2.398803713311698e-07</v>
+        <v>2.398803713311689e-07</v>
       </c>
       <c r="J5" t="n">
-        <v>2.394888627935321e-07</v>
+        <v>2.394888627935316e-07</v>
       </c>
       <c r="K5" t="n">
-        <v>2.398803713311698e-07</v>
+        <v>2.398803713311689e-07</v>
       </c>
       <c r="L5" t="n">
-        <v>2.398803713311698e-07</v>
+        <v>2.398803713311689e-07</v>
       </c>
       <c r="M5" t="n">
-        <v>2.398803713311602e-07</v>
+        <v>2.398803713311593e-07</v>
       </c>
       <c r="N5" t="n">
-        <v>1.752249074064535e-06</v>
+        <v>1.756899728045782e-07</v>
       </c>
       <c r="O5" t="n">
-        <v>1.933300516732791e-07</v>
+        <v>1.933300516732788e-07</v>
       </c>
       <c r="P5" t="n">
-        <v>1.8900604209873e-07</v>
+        <v>1.890060420987303e-07</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.407981767261741e-07</v>
+        <v>1.407981767261736e-07</v>
       </c>
       <c r="R5" t="n">
-        <v>2.398803713311698e-07</v>
+        <v>2.398803713311689e-07</v>
       </c>
       <c r="S5" t="n">
-        <v>2.398803713311698e-07</v>
+        <v>2.398803713311689e-07</v>
       </c>
       <c r="T5" t="n">
-        <v>2.398803713311698e-07</v>
+        <v>2.39880371331169e-07</v>
       </c>
       <c r="U5" t="n">
-        <v>1.994244628871356e-07</v>
+        <v>1.994244628871353e-07</v>
       </c>
       <c r="V5" t="n">
-        <v>2.145873958890463e-07</v>
+        <v>2.145873958890462e-07</v>
       </c>
       <c r="W5" t="n">
-        <v>2.398966455569568e-07</v>
+        <v>2.398966455569565e-07</v>
       </c>
       <c r="X5" t="n">
-        <v>1.483877352622294e-07</v>
+        <v>1.483877352622293e-07</v>
       </c>
       <c r="Y5" t="n">
-        <v>3.221495545386381e-07</v>
+        <v>3.221495545386375e-07</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.55533716821275e-07</v>
+        <v>1.555337168212751e-07</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.398803713311698e-07</v>
+        <v>2.398803713311689e-07</v>
       </c>
       <c r="AB5" t="n">
-        <v>3.263807165934026e-07</v>
+        <v>3.263807165934024e-07</v>
       </c>
     </row>
     <row r="6">
@@ -938,22 +938,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.498070906540158e-07</v>
+        <v>2.498070906540156e-07</v>
       </c>
       <c r="C6" t="n">
         <v>3.114960688532043e-07</v>
       </c>
       <c r="D6" t="n">
-        <v>3.114960688532042e-07</v>
+        <v>3.114960688532043e-07</v>
       </c>
       <c r="E6" t="n">
-        <v>2.972585601799519e-07</v>
+        <v>2.972585601799511e-07</v>
       </c>
       <c r="F6" t="n">
-        <v>1.692860427773668e-07</v>
+        <v>1.692860427773663e-07</v>
       </c>
       <c r="G6" t="n">
-        <v>3.114961414871945e-07</v>
+        <v>3.114961414871939e-07</v>
       </c>
       <c r="H6" t="n">
         <v>3.114960688532043e-07</v>
@@ -962,10 +962,10 @@
         <v>3.114960688532043e-07</v>
       </c>
       <c r="J6" t="n">
-        <v>3.111045603155666e-07</v>
+        <v>3.111045603155658e-07</v>
       </c>
       <c r="K6" t="n">
-        <v>3.114960688532042e-07</v>
+        <v>3.114960688532043e-07</v>
       </c>
       <c r="L6" t="n">
         <v>3.114960688532043e-07</v>
@@ -974,31 +974,31 @@
         <v>3.114960688532043e-07</v>
       </c>
       <c r="N6" t="n">
-        <v>1.752249074064535e-06</v>
+        <v>3.114960688532043e-07</v>
       </c>
       <c r="O6" t="n">
-        <v>3.319398121583922e-07</v>
+        <v>3.319398121583915e-07</v>
       </c>
       <c r="P6" t="n">
-        <v>3.363859597750589e-07</v>
+        <v>3.36385959775058e-07</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.114961414871945e-07</v>
+        <v>3.114961414871939e-07</v>
       </c>
       <c r="R6" t="n">
-        <v>3.114960688532042e-07</v>
+        <v>3.114960688532043e-07</v>
       </c>
       <c r="S6" t="n">
-        <v>3.114960688532042e-07</v>
+        <v>3.114960688532043e-07</v>
       </c>
       <c r="T6" t="n">
-        <v>3.114960688532042e-07</v>
+        <v>3.114960688532043e-07</v>
       </c>
       <c r="U6" t="n">
-        <v>3.114960688532042e-07</v>
+        <v>3.114960688532043e-07</v>
       </c>
       <c r="V6" t="n">
-        <v>3.800658772059399e-07</v>
+        <v>3.800658772059395e-07</v>
       </c>
       <c r="W6" t="n">
         <v>3.114960688532043e-07</v>
@@ -1010,7 +1010,7 @@
         <v>3.114960688532043e-07</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.743031294392207e-07</v>
+        <v>2.743031294392201e-07</v>
       </c>
       <c r="AA6" t="n">
         <v>3.114960688532043e-07</v>
@@ -1026,85 +1026,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5.678930772377847e-08</v>
+        <v>5.678930772377855e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>5.872811461877319e-08</v>
+        <v>5.872811461877318e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>4.287811792659801e-08</v>
+        <v>4.287811792659788e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>9.552670210114702e-08</v>
+        <v>9.55267021011471e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>4.493346703200838e-08</v>
+        <v>4.493346703200816e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.463681567197506e-08</v>
+        <v>-1.463681567197512e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>4.944791840813187e-08</v>
+        <v>4.944791840813138e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>3.615544956697758e-08</v>
+        <v>3.615544956697728e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>2.905094974991944e-08</v>
+        <v>2.905094974991926e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>1.627529646103853e-08</v>
+        <v>1.627529646103833e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>-4.269230218971763e-08</v>
+        <v>-4.269230218971665e-08</v>
       </c>
       <c r="M7" t="n">
-        <v>3.653960755884354e-08</v>
+        <v>3.653960755884343e-08</v>
       </c>
       <c r="N7" t="n">
-        <v>3.080962933940911e-08</v>
+        <v>3.080962933940883e-08</v>
       </c>
       <c r="O7" t="n">
-        <v>5.079011028484632e-08</v>
+        <v>5.079011028484617e-08</v>
       </c>
       <c r="P7" t="n">
-        <v>5.456474263500618e-08</v>
+        <v>5.456474263500594e-08</v>
       </c>
       <c r="Q7" t="n">
-        <v>5.202083065326622e-08</v>
+        <v>5.202083065326619e-08</v>
       </c>
       <c r="R7" t="n">
-        <v>5.068865565373318e-08</v>
+        <v>5.068865565373307e-08</v>
       </c>
       <c r="S7" t="n">
-        <v>5.400590443243261e-08</v>
+        <v>5.400590443243248e-08</v>
       </c>
       <c r="T7" t="n">
-        <v>4.094792493514891e-08</v>
+        <v>4.094792493514877e-08</v>
       </c>
       <c r="U7" t="n">
-        <v>4.602619607027513e-08</v>
+        <v>4.602619607027503e-08</v>
       </c>
       <c r="V7" t="n">
         <v>4.1601175549592e-08</v>
       </c>
       <c r="W7" t="n">
-        <v>5.030162866394397e-08</v>
+        <v>5.030162866394387e-08</v>
       </c>
       <c r="X7" t="n">
-        <v>3.969751767897955e-08</v>
+        <v>3.969751767897981e-08</v>
       </c>
       <c r="Y7" t="n">
-        <v>5.462759228880689e-08</v>
+        <v>5.46275922888067e-08</v>
       </c>
       <c r="Z7" t="n">
-        <v>5.116401578214199e-08</v>
+        <v>5.116401578214229e-08</v>
       </c>
       <c r="AA7" t="n">
-        <v>3.526956049561887e-08</v>
+        <v>3.526956049561877e-08</v>
       </c>
       <c r="AB7" t="n">
-        <v>4.340281756183709e-08</v>
+        <v>4.340281756183697e-08</v>
       </c>
     </row>
     <row r="8">
@@ -1114,85 +1114,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6.125298867645579e-08</v>
+        <v>6.125298867645559e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>6.182309880025879e-08</v>
+        <v>6.182309880025855e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>5.731834211029492e-08</v>
+        <v>5.73183421102945e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>9.672143682147646e-08</v>
+        <v>9.672143682147613e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>5.79189560258242e-08</v>
+        <v>5.791895602582397e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>4.076732513944938e-08</v>
+        <v>4.076732513944928e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>5.920337911975771e-08</v>
+        <v>5.920337911975767e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>5.541625242361229e-08</v>
+        <v>5.54162524236125e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>5.294250132589877e-08</v>
+        <v>5.294250132589835e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>4.974398155741172e-08</v>
+        <v>4.974398155741161e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>3.282416190861089e-08</v>
+        <v>3.282416190861081e-08</v>
       </c>
       <c r="M8" t="n">
-        <v>5.553454384497525e-08</v>
+        <v>5.553454384497506e-08</v>
       </c>
       <c r="N8" t="n">
-        <v>5.386330581496951e-08</v>
+        <v>5.386330581496922e-08</v>
       </c>
       <c r="O8" t="n">
-        <v>5.952925102592683e-08</v>
+        <v>5.952925102592645e-08</v>
       </c>
       <c r="P8" t="n">
-        <v>6.061146255081428e-08</v>
+        <v>6.061146255081427e-08</v>
       </c>
       <c r="Q8" t="n">
-        <v>5.991205928698759e-08</v>
+        <v>5.991205928698743e-08</v>
       </c>
       <c r="R8" t="n">
-        <v>5.954801692936756e-08</v>
+        <v>5.954801692936731e-08</v>
       </c>
       <c r="S8" t="n">
-        <v>6.045981618382551e-08</v>
+        <v>6.045981618382552e-08</v>
       </c>
       <c r="T8" t="n">
-        <v>5.677216738514839e-08</v>
+        <v>5.677216738514827e-08</v>
       </c>
       <c r="U8" t="n">
-        <v>5.818133809092523e-08</v>
+        <v>5.818133809092494e-08</v>
       </c>
       <c r="V8" t="n">
-        <v>4.605233453596449e-08</v>
+        <v>4.605233453596442e-08</v>
       </c>
       <c r="W8" t="n">
-        <v>5.941056867442563e-08</v>
+        <v>5.941056867442538e-08</v>
       </c>
       <c r="X8" t="n">
-        <v>5.641009458853436e-08</v>
+        <v>5.641009458853438e-08</v>
       </c>
       <c r="Y8" t="n">
-        <v>6.064861056579152e-08</v>
+        <v>6.064861056579127e-08</v>
       </c>
       <c r="Z8" t="n">
-        <v>5.964149277114132e-08</v>
+        <v>5.96414927711409e-08</v>
       </c>
       <c r="AA8" t="n">
-        <v>5.51219035357588e-08</v>
+        <v>5.51219035357586e-08</v>
       </c>
       <c r="AB8" t="n">
-        <v>5.746832172439598e-08</v>
+        <v>5.746832172439579e-08</v>
       </c>
     </row>
   </sheetData>
@@ -1358,85 +1358,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.710895823885567e-08</v>
+        <v>5.710895823885566e-08</v>
       </c>
       <c r="C2" t="n">
-        <v>5.71984570900057e-08</v>
+        <v>5.719845709000569e-08</v>
       </c>
       <c r="D2" t="n">
-        <v>5.722718221463906e-08</v>
+        <v>5.722718221463903e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>9.4617297645301e-08</v>
+        <v>9.461729764530091e-08</v>
       </c>
       <c r="F2" t="n">
-        <v>5.763058992927443e-08</v>
+        <v>5.763058992927438e-08</v>
       </c>
       <c r="G2" t="n">
         <v>5.750111255313932e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>5.730457298883523e-08</v>
+        <v>5.730457298883517e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>5.747851836155741e-08</v>
+        <v>5.747851836155737e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>5.761662257131548e-08</v>
+        <v>5.761662257131536e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>5.754735769116033e-08</v>
+        <v>5.754735769116031e-08</v>
       </c>
       <c r="L2" t="n">
-        <v>5.816581257696846e-08</v>
+        <v>5.816581257696842e-08</v>
       </c>
       <c r="M2" t="n">
-        <v>5.695101040172176e-08</v>
+        <v>5.695101040172173e-08</v>
       </c>
       <c r="N2" t="n">
-        <v>5.729843146391036e-08</v>
+        <v>5.729843146391031e-08</v>
       </c>
       <c r="O2" t="n">
-        <v>5.706692429098591e-08</v>
+        <v>5.706692429098593e-08</v>
       </c>
       <c r="P2" t="n">
-        <v>5.719702367982265e-08</v>
+        <v>5.719702367982261e-08</v>
       </c>
       <c r="Q2" t="n">
-        <v>5.729135604011399e-08</v>
+        <v>5.729135604011395e-08</v>
       </c>
       <c r="R2" t="n">
-        <v>5.895446556893874e-08</v>
+        <v>5.895446556893862e-08</v>
       </c>
       <c r="S2" t="n">
         <v>5.770358471114568e-08</v>
       </c>
       <c r="T2" t="n">
-        <v>5.713463857160541e-08</v>
+        <v>5.713463857160538e-08</v>
       </c>
       <c r="U2" t="n">
-        <v>5.811559142696191e-08</v>
+        <v>5.811559142696183e-08</v>
       </c>
       <c r="V2" t="n">
-        <v>4.463844058081186e-08</v>
+        <v>4.463844058081138e-08</v>
       </c>
       <c r="W2" t="n">
-        <v>5.967281647470699e-08</v>
+        <v>5.967281647470696e-08</v>
       </c>
       <c r="X2" t="n">
-        <v>6.014135968465823e-08</v>
+        <v>6.014135968465821e-08</v>
       </c>
       <c r="Y2" t="n">
-        <v>5.754325736370344e-08</v>
+        <v>5.754325736370337e-08</v>
       </c>
       <c r="Z2" t="n">
-        <v>5.746199369845313e-08</v>
+        <v>5.746199369845323e-08</v>
       </c>
       <c r="AA2" t="n">
-        <v>5.828971117049649e-08</v>
+        <v>5.828971117049645e-08</v>
       </c>
       <c r="AB2" t="n">
-        <v>5.887646209210705e-08</v>
+        <v>5.8876462092107e-08</v>
       </c>
     </row>
     <row r="3">
@@ -1446,16 +1446,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.75636661550921e-08</v>
+        <v>5.756366615509209e-08</v>
       </c>
       <c r="C3" t="n">
         <v>5.737004568341684e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>5.75636661550921e-08</v>
+        <v>5.756366615509209e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>9.557103665363968e-08</v>
+        <v>9.557103665363958e-08</v>
       </c>
       <c r="F3" t="n">
         <v>5.74344756504244e-08</v>
@@ -1464,67 +1464,67 @@
         <v>5.717541316820373e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>5.75636661550921e-08</v>
+        <v>5.756366615509209e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>5.75636661550921e-08</v>
+        <v>5.756366615509209e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>5.742116222310528e-08</v>
+        <v>5.742116222310526e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>5.749036290502978e-08</v>
+        <v>5.749036290502977e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>5.75636661550921e-08</v>
+        <v>5.756366615509209e-08</v>
       </c>
       <c r="M3" t="n">
         <v>5.71503179173318e-08</v>
       </c>
       <c r="N3" t="n">
-        <v>5.75636661550921e-08</v>
+        <v>5.756366615509209e-08</v>
       </c>
       <c r="O3" t="n">
-        <v>5.734286245856818e-08</v>
+        <v>5.734286245856817e-08</v>
       </c>
       <c r="P3" t="n">
         <v>5.713529498497015e-08</v>
       </c>
       <c r="Q3" t="n">
-        <v>5.756149638678365e-08</v>
+        <v>5.756149638678364e-08</v>
       </c>
       <c r="R3" t="n">
-        <v>5.797820042563513e-08</v>
+        <v>5.797820042563512e-08</v>
       </c>
       <c r="S3" t="n">
-        <v>5.75636661550921e-08</v>
+        <v>5.756366615509209e-08</v>
       </c>
       <c r="T3" t="n">
-        <v>5.726642264683336e-08</v>
+        <v>5.726642264683335e-08</v>
       </c>
       <c r="U3" t="n">
         <v>5.817873669826677e-08</v>
       </c>
       <c r="V3" t="n">
-        <v>4.356457553180187e-08</v>
+        <v>4.356457553180132e-08</v>
       </c>
       <c r="W3" t="n">
-        <v>5.75636661550921e-08</v>
+        <v>5.756366615509209e-08</v>
       </c>
       <c r="X3" t="n">
         <v>5.81567508270407e-08</v>
       </c>
       <c r="Y3" t="n">
-        <v>5.670282890775634e-08</v>
+        <v>5.670282890775633e-08</v>
       </c>
       <c r="Z3" t="n">
-        <v>5.754682343278651e-08</v>
+        <v>5.75468234327865e-08</v>
       </c>
       <c r="AA3" t="n">
-        <v>5.75636661550921e-08</v>
+        <v>5.756366615509209e-08</v>
       </c>
       <c r="AB3" t="n">
-        <v>5.949507075084494e-08</v>
+        <v>5.949507075084493e-08</v>
       </c>
     </row>
     <row r="4">
@@ -1534,85 +1534,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.573703795081975e-07</v>
+        <v>1.573703795081973e-07</v>
       </c>
       <c r="C4" t="n">
-        <v>2.328807228932262e-07</v>
+        <v>2.32880722893226e-07</v>
       </c>
       <c r="D4" t="n">
         <v>1.9840023735277e-07</v>
       </c>
       <c r="E4" t="n">
-        <v>1.674817778715754e-07</v>
+        <v>1.67481777871575e-07</v>
       </c>
       <c r="F4" t="n">
-        <v>3.329029881374083e-07</v>
+        <v>3.329029881374078e-07</v>
       </c>
       <c r="G4" t="n">
-        <v>3.242193024027172e-07</v>
+        <v>3.242193024027162e-07</v>
       </c>
       <c r="H4" t="n">
-        <v>2.281551502665239e-07</v>
+        <v>2.281551502665237e-07</v>
       </c>
       <c r="I4" t="n">
-        <v>2.664916728669505e-07</v>
+        <v>2.664916728669507e-07</v>
       </c>
       <c r="J4" t="n">
-        <v>3.13745889392034e-07</v>
+        <v>3.137458893920335e-07</v>
       </c>
       <c r="K4" t="n">
-        <v>2.819850747312354e-07</v>
+        <v>2.819850747312349e-07</v>
       </c>
       <c r="L4" t="n">
-        <v>4.019884536249866e-07</v>
+        <v>4.019884536249868e-07</v>
       </c>
       <c r="M4" t="n">
-        <v>2.270228647858587e-07</v>
+        <v>2.270228647858586e-07</v>
       </c>
       <c r="N4" t="n">
-        <v>2.158581586407831e-07</v>
+        <v>2.158581586407832e-07</v>
       </c>
       <c r="O4" t="n">
-        <v>1.931197520594317e-07</v>
+        <v>1.931197520594318e-07</v>
       </c>
       <c r="P4" t="n">
-        <v>2.644445698819218e-07</v>
+        <v>2.644445698819217e-07</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.081154741091822e-07</v>
+        <v>2.081154741091821e-07</v>
       </c>
       <c r="R4" t="n">
-        <v>5.643721901864813e-07</v>
+        <v>5.643721901864809e-07</v>
       </c>
       <c r="S4" t="n">
-        <v>2.915905360675508e-07</v>
+        <v>2.915905360675505e-07</v>
       </c>
       <c r="T4" t="n">
-        <v>2.481379701174281e-07</v>
+        <v>2.481379701174279e-07</v>
       </c>
       <c r="U4" t="n">
-        <v>2.603492970772176e-07</v>
+        <v>2.603492970772151e-07</v>
       </c>
       <c r="V4" t="n">
-        <v>4.388451467131417e-07</v>
+        <v>4.388451467131413e-07</v>
       </c>
       <c r="W4" t="n">
-        <v>8.091839292168824e-07</v>
+        <v>8.091839292168822e-07</v>
       </c>
       <c r="X4" t="n">
-        <v>7.733005837157066e-07</v>
+        <v>7.73300583715707e-07</v>
       </c>
       <c r="Y4" t="n">
-        <v>4.785573944314004e-07</v>
+        <v>4.78557394431401e-07</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.344404455990231e-07</v>
+        <v>2.344404455990233e-07</v>
       </c>
       <c r="AA4" t="n">
         <v>4.663536404993801e-07</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.769836564210701e-07</v>
+        <v>1.7698365642107e-07</v>
       </c>
     </row>
     <row r="5">
@@ -1622,85 +1622,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.215177468849938e-07</v>
+        <v>1.215177468849937e-07</v>
       </c>
       <c r="C5" t="n">
-        <v>1.827533267185323e-07</v>
+        <v>1.827533267185321e-07</v>
       </c>
       <c r="D5" t="n">
-        <v>1.827533267185323e-07</v>
+        <v>1.827533267185321e-07</v>
       </c>
       <c r="E5" t="n">
-        <v>1.501471867928247e-07</v>
+        <v>1.501471867928245e-07</v>
       </c>
       <c r="F5" t="n">
-        <v>1.310575345454155e-07</v>
+        <v>1.310575345454152e-07</v>
       </c>
       <c r="G5" t="n">
-        <v>1.954509231101702e-07</v>
+        <v>1.954509231101699e-07</v>
       </c>
       <c r="H5" t="n">
-        <v>1.827533267185323e-07</v>
+        <v>1.827533267185321e-07</v>
       </c>
       <c r="I5" t="n">
-        <v>1.827533267185323e-07</v>
+        <v>1.827533267185321e-07</v>
       </c>
       <c r="J5" t="n">
-        <v>1.82507212724647e-07</v>
+        <v>1.825072127246466e-07</v>
       </c>
       <c r="K5" t="n">
-        <v>1.827533267185323e-07</v>
+        <v>1.827533267185321e-07</v>
       </c>
       <c r="L5" t="n">
-        <v>1.827533267185323e-07</v>
+        <v>1.827533267185321e-07</v>
       </c>
       <c r="M5" t="n">
-        <v>1.827533267185234e-07</v>
+        <v>1.827533267185229e-07</v>
       </c>
       <c r="N5" t="n">
-        <v>2.158581586407831e-07</v>
+        <v>1.352855078557954e-07</v>
       </c>
       <c r="O5" t="n">
-        <v>1.483300766345604e-07</v>
+        <v>1.483300766345602e-07</v>
       </c>
       <c r="P5" t="n">
-        <v>1.451325376260078e-07</v>
+        <v>1.451325376260074e-07</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.094835578114637e-07</v>
+        <v>1.094835578114638e-07</v>
       </c>
       <c r="R5" t="n">
-        <v>1.827533267185323e-07</v>
+        <v>1.827533267185321e-07</v>
       </c>
       <c r="S5" t="n">
-        <v>1.827533267185323e-07</v>
+        <v>1.827533267185321e-07</v>
       </c>
       <c r="T5" t="n">
-        <v>1.827533267185323e-07</v>
+        <v>1.827533267185321e-07</v>
       </c>
       <c r="U5" t="n">
-        <v>1.528728900897342e-07</v>
+        <v>1.528728900897341e-07</v>
       </c>
       <c r="V5" t="n">
-        <v>1.643547264282325e-07</v>
+        <v>1.643547264282319e-07</v>
       </c>
       <c r="W5" t="n">
-        <v>1.827653612611483e-07</v>
+        <v>1.827653612611479e-07</v>
       </c>
       <c r="X5" t="n">
         <v>1.150959203792523e-07</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.436518692169571e-07</v>
+        <v>2.436518692169568e-07</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.20380264548877e-07</v>
+        <v>1.203802645488771e-07</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.827533267185323e-07</v>
+        <v>1.827533267185321e-07</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.467190102919384e-07</v>
+        <v>2.467190102919381e-07</v>
       </c>
     </row>
     <row r="6">
@@ -1710,85 +1710,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.372536023966685e-07</v>
+        <v>1.372536023966684e-07</v>
       </c>
       <c r="C6" t="n">
-        <v>1.682583932833121e-07</v>
+        <v>1.682583932833119e-07</v>
       </c>
       <c r="D6" t="n">
-        <v>1.682583932833121e-07</v>
+        <v>1.682583932833119e-07</v>
       </c>
       <c r="E6" t="n">
         <v>1.611026477019786e-07</v>
       </c>
       <c r="F6" t="n">
-        <v>9.678383111188866e-08</v>
+        <v>9.678383111188867e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>1.682584370806174e-07</v>
+        <v>1.682584370806171e-07</v>
       </c>
       <c r="H6" t="n">
-        <v>1.682583932833121e-07</v>
+        <v>1.682583932833119e-07</v>
       </c>
       <c r="I6" t="n">
-        <v>1.682583932833121e-07</v>
+        <v>1.682583932833119e-07</v>
       </c>
       <c r="J6" t="n">
-        <v>1.680122792894267e-07</v>
+        <v>1.680122792894266e-07</v>
       </c>
       <c r="K6" t="n">
-        <v>1.682583932833121e-07</v>
+        <v>1.682583932833119e-07</v>
       </c>
       <c r="L6" t="n">
-        <v>1.682583932833121e-07</v>
+        <v>1.682583932833119e-07</v>
       </c>
       <c r="M6" t="n">
-        <v>1.682583932833121e-07</v>
+        <v>1.682583932833119e-07</v>
       </c>
       <c r="N6" t="n">
-        <v>2.158581586407831e-07</v>
+        <v>1.682583932833119e-07</v>
       </c>
       <c r="O6" t="n">
-        <v>1.785333986975146e-07</v>
+        <v>1.785333986975147e-07</v>
       </c>
       <c r="P6" t="n">
-        <v>1.807680265605346e-07</v>
+        <v>1.807680265605347e-07</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.682584370806174e-07</v>
+        <v>1.682584370806171e-07</v>
       </c>
       <c r="R6" t="n">
-        <v>1.682583932833121e-07</v>
+        <v>1.682583932833119e-07</v>
       </c>
       <c r="S6" t="n">
-        <v>1.682583932833121e-07</v>
+        <v>1.682583932833119e-07</v>
       </c>
       <c r="T6" t="n">
-        <v>1.682583932833121e-07</v>
+        <v>1.682583932833119e-07</v>
       </c>
       <c r="U6" t="n">
-        <v>1.682583932833121e-07</v>
+        <v>1.682583932833119e-07</v>
       </c>
       <c r="V6" t="n">
-        <v>2.023666907267822e-07</v>
+        <v>2.023666907267817e-07</v>
       </c>
       <c r="W6" t="n">
-        <v>1.682583932833121e-07</v>
+        <v>1.682583932833119e-07</v>
       </c>
       <c r="X6" t="n">
-        <v>1.682583932833121e-07</v>
+        <v>1.682583932833119e-07</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.682583932833121e-07</v>
+        <v>1.682583932833119e-07</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.495652788236689e-07</v>
+        <v>1.49565278823669e-07</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.682583932833121e-07</v>
+        <v>1.682583932833119e-07</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.682583932833121e-07</v>
+        <v>1.682583932833119e-07</v>
       </c>
     </row>
     <row r="7">
@@ -1798,85 +1798,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5.499343625795772e-08</v>
+        <v>5.499343625795768e-08</v>
       </c>
       <c r="C7" t="n">
         <v>5.327453832348601e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>5.434108759612122e-08</v>
+        <v>5.43410875961212e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>9.236961702171421e-08</v>
+        <v>9.236961702171409e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>5.118821001855978e-08</v>
+        <v>5.118821001855981e-08</v>
       </c>
       <c r="G7" t="n">
         <v>5.016537183419912e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>5.391281585967798e-08</v>
+        <v>5.391281585967795e-08</v>
       </c>
       <c r="I7" t="n">
         <v>5.287773442658737e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>5.102324970061497e-08</v>
+        <v>5.102324970061485e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>5.199213864692713e-08</v>
+        <v>5.199213864692717e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>4.876184059793341e-08</v>
+        <v>4.876184059793339e-08</v>
       </c>
       <c r="M7" t="n">
-        <v>5.33474948827673e-08</v>
+        <v>5.334749488276733e-08</v>
       </c>
       <c r="N7" t="n">
-        <v>5.390819165258291e-08</v>
+        <v>5.39081916525829e-08</v>
       </c>
       <c r="O7" t="n">
-        <v>5.381842378378932e-08</v>
+        <v>5.381842378378934e-08</v>
       </c>
       <c r="P7" t="n">
-        <v>5.170150676848493e-08</v>
+        <v>5.170150676848489e-08</v>
       </c>
       <c r="Q7" t="n">
-        <v>5.394207775514285e-08</v>
+        <v>5.394207775514286e-08</v>
       </c>
       <c r="R7" t="n">
-        <v>4.690087354979111e-08</v>
+        <v>4.690087354979106e-08</v>
       </c>
       <c r="S7" t="n">
-        <v>5.147486981834781e-08</v>
+        <v>5.147486981834776e-08</v>
       </c>
       <c r="T7" t="n">
-        <v>5.299758441845545e-08</v>
+        <v>5.299758441845546e-08</v>
       </c>
       <c r="U7" t="n">
-        <v>5.299145188068372e-08</v>
+        <v>5.299145188068378e-08</v>
       </c>
       <c r="V7" t="n">
-        <v>3.315503641766361e-08</v>
+        <v>3.315503641766303e-08</v>
       </c>
       <c r="W7" t="n">
-        <v>3.988228563631373e-08</v>
+        <v>3.988228563631368e-08</v>
       </c>
       <c r="X7" t="n">
-        <v>4.102241876795637e-08</v>
+        <v>4.102241876795655e-08</v>
       </c>
       <c r="Y7" t="n">
-        <v>4.696304804665887e-08</v>
+        <v>4.696304804665879e-08</v>
       </c>
       <c r="Z7" t="n">
-        <v>5.279007603495835e-08</v>
+        <v>5.279007603495833e-08</v>
       </c>
       <c r="AA7" t="n">
         <v>4.805310929825166e-08</v>
       </c>
       <c r="AB7" t="n">
-        <v>5.695069993333191e-08</v>
+        <v>5.69506999333319e-08</v>
       </c>
     </row>
     <row r="8">
@@ -1886,82 +1886,82 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.593949544482281e-08</v>
+        <v>5.593949544482277e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>5.533498818962957e-08</v>
+        <v>5.533498818962958e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>5.576089870055882e-08</v>
+        <v>5.576089870055878e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>9.316064151045591e-08</v>
+        <v>9.316064151045586e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>5.478851916110851e-08</v>
+        <v>5.478851916110846e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>5.431152140649104e-08</v>
+        <v>5.431152140649103e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>5.564342446985224e-08</v>
+        <v>5.564342446985222e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>5.534640449190945e-08</v>
+        <v>5.534640449190943e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>5.470555198464498e-08</v>
+        <v>5.47055519846449e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>5.504564813192264e-08</v>
+        <v>5.504564813192258e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>5.416095389870749e-08</v>
+        <v>5.416095389870744e-08</v>
       </c>
       <c r="M8" t="n">
-        <v>5.522071380211707e-08</v>
+        <v>5.522071380211703e-08</v>
       </c>
       <c r="N8" t="n">
-        <v>5.563517891596265e-08</v>
+        <v>5.563517891596262e-08</v>
       </c>
       <c r="O8" t="n">
-        <v>5.546329346224192e-08</v>
+        <v>5.5463293462242e-08</v>
       </c>
       <c r="P8" t="n">
-        <v>5.47246327248662e-08</v>
+        <v>5.472463272486629e-08</v>
       </c>
       <c r="Q8" t="n">
-        <v>5.564450902831462e-08</v>
+        <v>5.564450902831467e-08</v>
       </c>
       <c r="R8" t="n">
-        <v>5.391424653908359e-08</v>
+        <v>5.391424653908353e-08</v>
       </c>
       <c r="S8" t="n">
-        <v>5.493316297408443e-08</v>
+        <v>5.493316297408444e-08</v>
       </c>
       <c r="T8" t="n">
-        <v>5.519230357371331e-08</v>
+        <v>5.519230357371329e-08</v>
       </c>
       <c r="U8" t="n">
-        <v>5.575536030406569e-08</v>
+        <v>5.575536030406568e-08</v>
       </c>
       <c r="V8" t="n">
-        <v>3.990206711064607e-08</v>
+        <v>3.990206711064549e-08</v>
       </c>
       <c r="W8" t="n">
-        <v>5.162773199144641e-08</v>
+        <v>5.162773199144639e-08</v>
       </c>
       <c r="X8" t="n">
-        <v>5.234518399389853e-08</v>
+        <v>5.234518399389852e-08</v>
       </c>
       <c r="Y8" t="n">
-        <v>5.311162603306418e-08</v>
+        <v>5.311162603306413e-08</v>
       </c>
       <c r="Z8" t="n">
-        <v>5.529765847358681e-08</v>
+        <v>5.529765847358682e-08</v>
       </c>
       <c r="AA8" t="n">
-        <v>5.396237749228772e-08</v>
+        <v>5.396237749228764e-08</v>
       </c>
       <c r="AB8" t="n">
         <v>5.771876526170996e-08</v>
@@ -2130,85 +2130,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.186718588838977e-08</v>
+        <v>6.186718588838994e-08</v>
       </c>
       <c r="C2" t="n">
-        <v>6.179231725263507e-08</v>
+        <v>6.179231725263519e-08</v>
       </c>
       <c r="D2" t="n">
-        <v>6.242624782315811e-08</v>
+        <v>6.242624782315819e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>9.698341952865186e-08</v>
+        <v>9.698341952865211e-08</v>
       </c>
       <c r="F2" t="n">
-        <v>6.283189056832854e-08</v>
+        <v>6.283189056832864e-08</v>
       </c>
       <c r="G2" t="n">
-        <v>7.097829785765663e-08</v>
+        <v>7.097829785765668e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>6.205881555567301e-08</v>
+        <v>6.205881555567303e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>6.360344698674965e-08</v>
+        <v>6.360344698674974e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>6.535041121831263e-08</v>
+        <v>6.53504112183127e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>6.75977114329285e-08</v>
+        <v>6.759771143292856e-08</v>
       </c>
       <c r="L2" t="n">
-        <v>7.558680924751467e-08</v>
+        <v>7.558680924751491e-08</v>
       </c>
       <c r="M2" t="n">
-        <v>6.395634222746287e-08</v>
+        <v>6.395634222746295e-08</v>
       </c>
       <c r="N2" t="n">
-        <v>6.367626010698115e-08</v>
+        <v>6.367626010698125e-08</v>
       </c>
       <c r="O2" t="n">
-        <v>6.220881818469393e-08</v>
+        <v>6.220881818469402e-08</v>
       </c>
       <c r="P2" t="n">
-        <v>6.285133473510339e-08</v>
+        <v>6.285133473510346e-08</v>
       </c>
       <c r="Q2" t="n">
-        <v>6.221812310887926e-08</v>
+        <v>6.221812310887939e-08</v>
       </c>
       <c r="R2" t="n">
-        <v>6.213262688027502e-08</v>
+        <v>6.213262688027507e-08</v>
       </c>
       <c r="S2" t="n">
-        <v>6.243187231722609e-08</v>
+        <v>6.243187231722613e-08</v>
       </c>
       <c r="T2" t="n">
-        <v>6.269079489081461e-08</v>
+        <v>6.269079489081466e-08</v>
       </c>
       <c r="U2" t="n">
-        <v>6.314104842920038e-08</v>
+        <v>6.314104842920045e-08</v>
       </c>
       <c r="V2" t="n">
-        <v>4.643909827801438e-08</v>
+        <v>4.643909827801441e-08</v>
       </c>
       <c r="W2" t="n">
-        <v>6.443229722852769e-08</v>
+        <v>6.443229722852778e-08</v>
       </c>
       <c r="X2" t="n">
-        <v>6.568408493656844e-08</v>
+        <v>6.568408493656857e-08</v>
       </c>
       <c r="Y2" t="n">
-        <v>6.211465561387464e-08</v>
+        <v>6.21146556138747e-08</v>
       </c>
       <c r="Z2" t="n">
-        <v>6.266530474448947e-08</v>
+        <v>6.26653047444897e-08</v>
       </c>
       <c r="AA2" t="n">
-        <v>6.340020523073106e-08</v>
+        <v>6.340020523073115e-08</v>
       </c>
       <c r="AB2" t="n">
-        <v>6.606661963928065e-08</v>
+        <v>6.606661963928069e-08</v>
       </c>
     </row>
     <row r="3">
@@ -2218,85 +2218,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.183486022126946e-08</v>
+        <v>6.183486022126956e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>6.164977235313282e-08</v>
+        <v>6.164977235313293e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>6.183486022126946e-08</v>
+        <v>6.183486022126956e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>9.790236763428804e-08</v>
+        <v>9.790236763428815e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>6.176589784143151e-08</v>
+        <v>6.176589784143162e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>6.167456410984451e-08</v>
+        <v>6.167456410984462e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>6.183486022126946e-08</v>
+        <v>6.183486022126956e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>6.183486022126946e-08</v>
+        <v>6.183486022126956e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>6.139048396851103e-08</v>
+        <v>6.139048396851117e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>6.179454750264529e-08</v>
+        <v>6.179454750264539e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>6.183486022126946e-08</v>
+        <v>6.183486022126956e-08</v>
       </c>
       <c r="M3" t="n">
-        <v>6.177590154496867e-08</v>
+        <v>6.177590154496876e-08</v>
       </c>
       <c r="N3" t="n">
-        <v>6.183486022126946e-08</v>
+        <v>6.183486022126956e-08</v>
       </c>
       <c r="O3" t="n">
-        <v>6.166201734112678e-08</v>
+        <v>6.166201734112687e-08</v>
       </c>
       <c r="P3" t="n">
-        <v>6.179393809765245e-08</v>
+        <v>6.179393809765254e-08</v>
       </c>
       <c r="Q3" t="n">
-        <v>6.1832690452961e-08</v>
+        <v>6.183269045296109e-08</v>
       </c>
       <c r="R3" t="n">
-        <v>6.18273777912129e-08</v>
+        <v>6.182737779121301e-08</v>
       </c>
       <c r="S3" t="n">
-        <v>6.183486022126946e-08</v>
+        <v>6.183486022126956e-08</v>
       </c>
       <c r="T3" t="n">
-        <v>6.176457918506017e-08</v>
+        <v>6.176457918506027e-08</v>
       </c>
       <c r="U3" t="n">
-        <v>6.198936061703234e-08</v>
+        <v>6.198936061703245e-08</v>
       </c>
       <c r="V3" t="n">
-        <v>4.630913160772376e-08</v>
+        <v>4.630913160772383e-08</v>
       </c>
       <c r="W3" t="n">
-        <v>6.183486022126946e-08</v>
+        <v>6.183486022126956e-08</v>
       </c>
       <c r="X3" t="n">
-        <v>6.194324134431907e-08</v>
+        <v>6.194324134431917e-08</v>
       </c>
       <c r="Y3" t="n">
-        <v>6.142665799803978e-08</v>
+        <v>6.142665799803987e-08</v>
       </c>
       <c r="Z3" t="n">
-        <v>6.182468003410119e-08</v>
+        <v>6.18246800341013e-08</v>
       </c>
       <c r="AA3" t="n">
-        <v>6.183486022126946e-08</v>
+        <v>6.183486022126956e-08</v>
       </c>
       <c r="AB3" t="n">
-        <v>6.37662648170223e-08</v>
+        <v>6.376626481702241e-08</v>
       </c>
     </row>
     <row r="4">
@@ -2306,85 +2306,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.030057552924509e-07</v>
+        <v>3.03005755292458e-07</v>
       </c>
       <c r="C4" t="n">
-        <v>3.526925143126457e-07</v>
+        <v>3.52692514312646e-07</v>
       </c>
       <c r="D4" t="n">
-        <v>4.91789759209316e-07</v>
+        <v>4.917897592093158e-07</v>
       </c>
       <c r="E4" t="n">
-        <v>1.954488422574526e-07</v>
+        <v>1.95448842257463e-07</v>
       </c>
       <c r="F4" t="n">
-        <v>6.271370810410322e-07</v>
+        <v>6.271370810410342e-07</v>
       </c>
       <c r="G4" t="n">
-        <v>2.683265787572543e-06</v>
+        <v>2.683265787572541e-06</v>
       </c>
       <c r="H4" t="n">
-        <v>4.012770842330694e-07</v>
+        <v>4.012770842330698e-07</v>
       </c>
       <c r="I4" t="n">
-        <v>8.355071229239814e-07</v>
+        <v>8.355071229239819e-07</v>
       </c>
       <c r="J4" t="n">
-        <v>1.336822525675357e-06</v>
+        <v>1.336822525675352e-06</v>
       </c>
       <c r="K4" t="n">
-        <v>1.833165871161383e-06</v>
+        <v>1.833165871161385e-06</v>
       </c>
       <c r="L4" t="n">
-        <v>4.024641966379554e-06</v>
+        <v>4.024641966379613e-06</v>
       </c>
       <c r="M4" t="n">
-        <v>9.492005825918587e-07</v>
+        <v>9.492005825918514e-07</v>
       </c>
       <c r="N4" t="n">
-        <v>8.255242855591019e-07</v>
+        <v>8.255242855591034e-07</v>
       </c>
       <c r="O4" t="n">
-        <v>4.219550122533937e-07</v>
+        <v>4.219550122533939e-07</v>
       </c>
       <c r="P4" t="n">
-        <v>5.660814046227044e-07</v>
+        <v>5.660814046227174e-07</v>
       </c>
       <c r="Q4" t="n">
-        <v>4.241454039319069e-07</v>
+        <v>4.241454039319141e-07</v>
       </c>
       <c r="R4" t="n">
-        <v>4.187777295307695e-07</v>
+        <v>4.187777295307693e-07</v>
       </c>
       <c r="S4" t="n">
-        <v>4.532765773644542e-07</v>
+        <v>4.532765773644578e-07</v>
       </c>
       <c r="T4" t="n">
-        <v>5.852345430723953e-07</v>
+        <v>5.852345430724019e-07</v>
       </c>
       <c r="U4" t="n">
-        <v>6.134882728196494e-07</v>
+        <v>6.134882728196502e-07</v>
       </c>
       <c r="V4" t="n">
-        <v>2.562216929447542e-07</v>
+        <v>2.562216929447543e-07</v>
       </c>
       <c r="W4" t="n">
-        <v>1.018226493672916e-06</v>
+        <v>1.018226493672917e-06</v>
       </c>
       <c r="X4" t="n">
-        <v>1.367003245069762e-06</v>
+        <v>1.367003245069774e-06</v>
       </c>
       <c r="Y4" t="n">
-        <v>4.870540384292825e-07</v>
+        <v>4.870540384292823e-07</v>
       </c>
       <c r="Z4" t="n">
-        <v>5.14487184524367e-07</v>
+        <v>5.144871845243707e-07</v>
       </c>
       <c r="AA4" t="n">
-        <v>7.368279315217168e-07</v>
+        <v>7.368279315217247e-07</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.075380099266866e-06</v>
+        <v>1.075380099266879e-06</v>
       </c>
     </row>
     <row r="5">
@@ -2394,85 +2394,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.405480677868298e-07</v>
+        <v>1.405480677868297e-07</v>
       </c>
       <c r="C5" t="n">
-        <v>2.138531979776251e-07</v>
+        <v>2.138531979776254e-07</v>
       </c>
       <c r="D5" t="n">
-        <v>2.138531979776251e-07</v>
+        <v>2.138531979776254e-07</v>
       </c>
       <c r="E5" t="n">
-        <v>1.748203785164698e-07</v>
+        <v>1.748203785164701e-07</v>
       </c>
       <c r="F5" t="n">
         <v>1.519681503327046e-07</v>
       </c>
       <c r="G5" t="n">
-        <v>2.290534942615852e-07</v>
+        <v>2.290534942615851e-07</v>
       </c>
       <c r="H5" t="n">
-        <v>2.138531979776251e-07</v>
+        <v>2.138531979776254e-07</v>
       </c>
       <c r="I5" t="n">
-        <v>2.138531979776251e-07</v>
+        <v>2.138531979776254e-07</v>
       </c>
       <c r="J5" t="n">
-        <v>2.134926479513546e-07</v>
+        <v>2.134926479513544e-07</v>
       </c>
       <c r="K5" t="n">
-        <v>2.138531979776251e-07</v>
+        <v>2.138531979776254e-07</v>
       </c>
       <c r="L5" t="n">
-        <v>2.138531979776251e-07</v>
+        <v>2.138531979776254e-07</v>
       </c>
       <c r="M5" t="n">
-        <v>2.138531979776171e-07</v>
+        <v>2.138531979776173e-07</v>
       </c>
       <c r="N5" t="n">
-        <v>8.255242855591019e-07</v>
+        <v>1.570294583955726e-07</v>
       </c>
       <c r="O5" t="n">
         <v>1.726451154229817e-07</v>
       </c>
       <c r="P5" t="n">
-        <v>1.688173405585903e-07</v>
+        <v>1.688173405585907e-07</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.261419365944367e-07</v>
+        <v>1.261419365944366e-07</v>
       </c>
       <c r="R5" t="n">
-        <v>2.138531979776251e-07</v>
+        <v>2.138531979776254e-07</v>
       </c>
       <c r="S5" t="n">
-        <v>2.138531979776251e-07</v>
+        <v>2.138531979776254e-07</v>
       </c>
       <c r="T5" t="n">
-        <v>2.138531979776251e-07</v>
+        <v>2.138531979776254e-07</v>
       </c>
       <c r="U5" t="n">
         <v>1.78042040672797e-07</v>
       </c>
       <c r="V5" t="n">
-        <v>1.91366132834564e-07</v>
+        <v>1.913661328345641e-07</v>
       </c>
       <c r="W5" t="n">
-        <v>2.138676045304656e-07</v>
+        <v>2.138676045304655e-07</v>
       </c>
       <c r="X5" t="n">
-        <v>1.328604974337302e-07</v>
+        <v>1.3286049743373e-07</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.866842459582285e-07</v>
+        <v>2.866842459582289e-07</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.391863873563278e-07</v>
+        <v>1.391863873563281e-07</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.138531979776251e-07</v>
+        <v>2.138531979776254e-07</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.904265361367874e-07</v>
+        <v>2.904265361367878e-07</v>
       </c>
     </row>
     <row r="6">
@@ -2482,85 +2482,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.95839306290634e-07</v>
+        <v>1.958393062906335e-07</v>
       </c>
       <c r="C6" t="n">
-        <v>2.430366336398586e-07</v>
+        <v>2.430366336398584e-07</v>
       </c>
       <c r="D6" t="n">
-        <v>2.430366336398586e-07</v>
+        <v>2.430366336398584e-07</v>
       </c>
       <c r="E6" t="n">
-        <v>2.321437322622215e-07</v>
+        <v>2.321437322622216e-07</v>
       </c>
       <c r="F6" t="n">
-        <v>1.342338291368718e-07</v>
+        <v>1.342338291368716e-07</v>
       </c>
       <c r="G6" t="n">
         <v>2.430366976803049e-07</v>
       </c>
       <c r="H6" t="n">
-        <v>2.430366336398586e-07</v>
+        <v>2.430366336398584e-07</v>
       </c>
       <c r="I6" t="n">
-        <v>2.430366336398586e-07</v>
+        <v>2.430366336398584e-07</v>
       </c>
       <c r="J6" t="n">
-        <v>2.426760836135877e-07</v>
+        <v>2.426760836135874e-07</v>
       </c>
       <c r="K6" t="n">
-        <v>2.430366336398586e-07</v>
+        <v>2.430366336398584e-07</v>
       </c>
       <c r="L6" t="n">
-        <v>2.430366336398586e-07</v>
+        <v>2.430366336398584e-07</v>
       </c>
       <c r="M6" t="n">
-        <v>2.430366336398586e-07</v>
+        <v>2.430366336398584e-07</v>
       </c>
       <c r="N6" t="n">
-        <v>8.255242855591019e-07</v>
+        <v>2.430366336398584e-07</v>
       </c>
       <c r="O6" t="n">
         <v>2.586778513871342e-07</v>
       </c>
       <c r="P6" t="n">
-        <v>2.620795339613641e-07</v>
+        <v>2.620795339613639e-07</v>
       </c>
       <c r="Q6" t="n">
         <v>2.430366976803049e-07</v>
       </c>
       <c r="R6" t="n">
-        <v>2.430366336398586e-07</v>
+        <v>2.430366336398584e-07</v>
       </c>
       <c r="S6" t="n">
-        <v>2.430366336398586e-07</v>
+        <v>2.430366336398584e-07</v>
       </c>
       <c r="T6" t="n">
-        <v>2.430366336398586e-07</v>
+        <v>2.430366336398584e-07</v>
       </c>
       <c r="U6" t="n">
-        <v>2.430366336398586e-07</v>
+        <v>2.430366336398584e-07</v>
       </c>
       <c r="V6" t="n">
-        <v>2.950849343460506e-07</v>
+        <v>2.950849343460505e-07</v>
       </c>
       <c r="W6" t="n">
-        <v>2.430366336398586e-07</v>
+        <v>2.430366336398584e-07</v>
       </c>
       <c r="X6" t="n">
-        <v>2.430366336398586e-07</v>
+        <v>2.430366336398584e-07</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.430366336398586e-07</v>
+        <v>2.430366336398584e-07</v>
       </c>
       <c r="Z6" t="n">
         <v>2.145808676281295e-07</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.430366336398586e-07</v>
+        <v>2.430366336398584e-07</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.430366336398586e-07</v>
+        <v>2.430366336398584e-07</v>
       </c>
     </row>
     <row r="7">
@@ -2570,85 +2570,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5.612281657596452e-08</v>
+        <v>5.612281657596444e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>5.546693397453208e-08</v>
+        <v>5.546693397453224e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>5.293668769650561e-08</v>
+        <v>5.293668769650578e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>9.44255365249771e-08</v>
+        <v>9.44255365249767e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>5.017953374141437e-08</v>
+        <v>5.017953374141443e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>9.21301547586232e-10</v>
+        <v>9.213015475864239e-10</v>
       </c>
       <c r="H7" t="n">
-        <v>5.51347046273124e-08</v>
+        <v>5.513470462731251e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>4.607084436215442e-08</v>
+        <v>4.607084436215455e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>3.24096793869171e-08</v>
+        <v>3.24096793869172e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>2.233265946159028e-08</v>
+        <v>2.233265946159038e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>-2.494929645935855e-08</v>
+        <v>-2.494929645935824e-08</v>
       </c>
       <c r="M7" t="n">
-        <v>4.366868829524181e-08</v>
+        <v>4.366868829524183e-08</v>
       </c>
       <c r="N7" t="n">
-        <v>4.554591488467144e-08</v>
+        <v>4.55459148846716e-08</v>
       </c>
       <c r="O7" t="n">
-        <v>5.296838167697886e-08</v>
+        <v>5.296838167697901e-08</v>
       </c>
       <c r="P7" t="n">
-        <v>4.998114958114041e-08</v>
+        <v>4.998114958114052e-08</v>
       </c>
       <c r="Q7" t="n">
-        <v>5.412223345928674e-08</v>
+        <v>5.412223345928687e-08</v>
       </c>
       <c r="R7" t="n">
-        <v>5.463764644042053e-08</v>
+        <v>5.463764644042067e-08</v>
       </c>
       <c r="S7" t="n">
-        <v>5.279152792357197e-08</v>
+        <v>5.279152792357178e-08</v>
       </c>
       <c r="T7" t="n">
-        <v>5.094751436243882e-08</v>
+        <v>5.094751436243886e-08</v>
       </c>
       <c r="U7" t="n">
-        <v>4.960481953657045e-08</v>
+        <v>4.960481953657058e-08</v>
       </c>
       <c r="V7" t="n">
-        <v>4.132781505276715e-08</v>
+        <v>4.132781505276718e-08</v>
       </c>
       <c r="W7" t="n">
-        <v>4.102921901514747e-08</v>
+        <v>4.102921901514755e-08</v>
       </c>
       <c r="X7" t="n">
-        <v>3.451591902971069e-08</v>
+        <v>3.451591902971071e-08</v>
       </c>
       <c r="Y7" t="n">
-        <v>5.211322000924401e-08</v>
+        <v>5.211322000924416e-08</v>
       </c>
       <c r="Z7" t="n">
         <v>5.132083870512076e-08</v>
       </c>
       <c r="AA7" t="n">
-        <v>4.713259643358117e-08</v>
+        <v>4.713259643358124e-08</v>
       </c>
       <c r="AB7" t="n">
-        <v>4.388737843486064e-08</v>
+        <v>4.388737843486066e-08</v>
       </c>
     </row>
     <row r="8">
@@ -2658,85 +2658,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.926818782657303e-08</v>
+        <v>5.926818782657317e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>5.897910608683488e-08</v>
+        <v>5.897910608683497e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>5.837755096759728e-08</v>
+        <v>5.837755096759725e-08</v>
       </c>
       <c r="E8" t="n">
         <v>9.540145029391205e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>5.756005797926916e-08</v>
+        <v>5.756005797926923e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>4.333536978266894e-08</v>
+        <v>4.333536978266902e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>5.901022340829356e-08</v>
+        <v>5.901022340829364e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>5.643076953391453e-08</v>
+        <v>5.643076953391461e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>5.216405277734308e-08</v>
+        <v>5.216405277734321e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>4.964242661667293e-08</v>
+        <v>4.964242661667305e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>3.609974139313144e-08</v>
+        <v>3.609974139313145e-08</v>
       </c>
       <c r="M8" t="n">
-        <v>5.57175024945724e-08</v>
+        <v>5.57175024945725e-08</v>
       </c>
       <c r="N8" t="n">
-        <v>5.626473806904026e-08</v>
+        <v>5.626473806904039e-08</v>
       </c>
       <c r="O8" t="n">
-        <v>5.825318625253361e-08</v>
+        <v>5.825318625253376e-08</v>
       </c>
       <c r="P8" t="n">
-        <v>5.74764783149671e-08</v>
+        <v>5.74764783149672e-08</v>
       </c>
       <c r="Q8" t="n">
-        <v>5.870984060498902e-08</v>
+        <v>5.870984060498916e-08</v>
       </c>
       <c r="R8" t="n">
         <v>5.886127620335005e-08</v>
       </c>
       <c r="S8" t="n">
-        <v>5.831712730238366e-08</v>
+        <v>5.831712730238383e-08</v>
       </c>
       <c r="T8" t="n">
-        <v>5.776899592458171e-08</v>
+        <v>5.776899592458175e-08</v>
       </c>
       <c r="U8" t="n">
-        <v>5.750604277039954e-08</v>
+        <v>5.750604277039957e-08</v>
       </c>
       <c r="V8" t="n">
-        <v>4.417258337099519e-08</v>
+        <v>4.417258337099523e-08</v>
       </c>
       <c r="W8" t="n">
-        <v>5.496566417609778e-08</v>
+        <v>5.496566417609783e-08</v>
       </c>
       <c r="X8" t="n">
-        <v>5.320456587773157e-08</v>
+        <v>5.320456587773151e-08</v>
       </c>
       <c r="Y8" t="n">
-        <v>5.787701164880671e-08</v>
+        <v>5.787701164880679e-08</v>
       </c>
       <c r="Z8" t="n">
-        <v>5.788602346604725e-08</v>
+        <v>5.788602346604746e-08</v>
       </c>
       <c r="AA8" t="n">
-        <v>5.671062835399814e-08</v>
+        <v>5.671062835399827e-08</v>
       </c>
       <c r="AB8" t="n">
-        <v>5.702166298514498e-08</v>
+        <v>5.7021662985145e-08</v>
       </c>
     </row>
   </sheetData>
@@ -2902,37 +2902,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.041460073180102e-08</v>
+        <v>6.041460073180107e-08</v>
       </c>
       <c r="C2" t="n">
         <v>6.042689049366793e-08</v>
       </c>
       <c r="D2" t="n">
-        <v>6.168638751102326e-08</v>
+        <v>6.16863875110234e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>9.678230771063304e-08</v>
+        <v>9.678230771063318e-08</v>
       </c>
       <c r="F2" t="n">
-        <v>6.132856361632335e-08</v>
+        <v>6.13285636163234e-08</v>
       </c>
       <c r="G2" t="n">
-        <v>6.83254599199505e-08</v>
+        <v>6.832545991995055e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>6.040737709176325e-08</v>
+        <v>6.040737709176329e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>6.169102304112425e-08</v>
+        <v>6.169102304112429e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>6.356228056392203e-08</v>
+        <v>6.356228056392208e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>6.151709348435767e-08</v>
+        <v>6.151709348435773e-08</v>
       </c>
       <c r="L2" t="n">
-        <v>7.188288015063018e-08</v>
+        <v>7.18828801506302e-08</v>
       </c>
       <c r="M2" t="n">
         <v>6.230763760020281e-08</v>
@@ -2941,46 +2941,46 @@
         <v>6.104238189779254e-08</v>
       </c>
       <c r="O2" t="n">
-        <v>6.052081179464988e-08</v>
+        <v>6.052081179464987e-08</v>
       </c>
       <c r="P2" t="n">
-        <v>6.131330099379779e-08</v>
+        <v>6.131330099379783e-08</v>
       </c>
       <c r="Q2" t="n">
-        <v>6.103948595986134e-08</v>
+        <v>6.103948595986138e-08</v>
       </c>
       <c r="R2" t="n">
-        <v>6.055314239334729e-08</v>
+        <v>6.055314239334733e-08</v>
       </c>
       <c r="S2" t="n">
-        <v>6.103988039248484e-08</v>
+        <v>6.103988039248489e-08</v>
       </c>
       <c r="T2" t="n">
-        <v>6.072486324680007e-08</v>
+        <v>6.072486324680012e-08</v>
       </c>
       <c r="U2" t="n">
-        <v>6.163612952961018e-08</v>
+        <v>6.163612952961024e-08</v>
       </c>
       <c r="V2" t="n">
-        <v>4.542766044370597e-08</v>
+        <v>4.542766044370603e-08</v>
       </c>
       <c r="W2" t="n">
-        <v>6.285542516899412e-08</v>
+        <v>6.285542516899416e-08</v>
       </c>
       <c r="X2" t="n">
-        <v>6.777765674755108e-08</v>
+        <v>6.777765674755113e-08</v>
       </c>
       <c r="Y2" t="n">
-        <v>6.225055363076836e-08</v>
+        <v>6.225055363076838e-08</v>
       </c>
       <c r="Z2" t="n">
-        <v>6.148220209728086e-08</v>
+        <v>6.148220209728089e-08</v>
       </c>
       <c r="AA2" t="n">
-        <v>6.144751797072704e-08</v>
+        <v>6.144751797072706e-08</v>
       </c>
       <c r="AB2" t="n">
-        <v>6.477848250746627e-08</v>
+        <v>6.477848250746631e-08</v>
       </c>
     </row>
     <row r="3">
@@ -2990,85 +2990,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.070714674854096e-08</v>
+        <v>6.070714674854102e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>6.051276591762123e-08</v>
+        <v>6.051276591762127e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>6.070714674854096e-08</v>
+        <v>6.070714674854102e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>9.743530613724276e-08</v>
+        <v>9.743530613724273e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>6.060981220289538e-08</v>
+        <v>6.060981220289542e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>6.044706134274059e-08</v>
+        <v>6.044706134274064e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>6.070714674854096e-08</v>
+        <v>6.070714674854102e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>6.070714674854096e-08</v>
+        <v>6.070714674854102e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>6.030898095407334e-08</v>
+        <v>6.030898095407336e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>6.06499661138486e-08</v>
+        <v>6.064996611384864e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>6.070714674854096e-08</v>
+        <v>6.070714674854102e-08</v>
       </c>
       <c r="M3" t="n">
-        <v>6.054767051316364e-08</v>
+        <v>6.054767051316368e-08</v>
       </c>
       <c r="N3" t="n">
-        <v>6.070714674854096e-08</v>
+        <v>6.070714674854102e-08</v>
       </c>
       <c r="O3" t="n">
-        <v>6.051413432864405e-08</v>
+        <v>6.05141343286441e-08</v>
       </c>
       <c r="P3" t="n">
-        <v>6.068650905753607e-08</v>
+        <v>6.068650905753611e-08</v>
       </c>
       <c r="Q3" t="n">
-        <v>6.070497698023251e-08</v>
+        <v>6.070497698023255e-08</v>
       </c>
       <c r="R3" t="n">
-        <v>6.092218945037027e-08</v>
+        <v>6.092218945037031e-08</v>
       </c>
       <c r="S3" t="n">
-        <v>6.070714674854096e-08</v>
+        <v>6.070714674854102e-08</v>
       </c>
       <c r="T3" t="n">
-        <v>6.05001695497079e-08</v>
+        <v>6.050016954970796e-08</v>
       </c>
       <c r="U3" t="n">
-        <v>6.089698609045782e-08</v>
+        <v>6.089698609045786e-08</v>
       </c>
       <c r="V3" t="n">
         <v>4.532043445817599e-08</v>
       </c>
       <c r="W3" t="n">
-        <v>6.070714674854096e-08</v>
+        <v>6.070714674854102e-08</v>
       </c>
       <c r="X3" t="n">
-        <v>6.200082125239623e-08</v>
+        <v>6.200082125239628e-08</v>
       </c>
       <c r="Y3" t="n">
-        <v>6.021650395826613e-08</v>
+        <v>6.021650395826617e-08</v>
       </c>
       <c r="Z3" t="n">
-        <v>6.0690029119616e-08</v>
+        <v>6.069002911961604e-08</v>
       </c>
       <c r="AA3" t="n">
-        <v>6.070714674854096e-08</v>
+        <v>6.070714674854102e-08</v>
       </c>
       <c r="AB3" t="n">
-        <v>6.263855134429381e-08</v>
+        <v>6.263855134429385e-08</v>
       </c>
     </row>
     <row r="4">
@@ -3078,85 +3078,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.051281992843485e-07</v>
+        <v>2.051281992843494e-07</v>
       </c>
       <c r="C4" t="n">
-        <v>2.65368931797048e-07</v>
+        <v>2.653689317970482e-07</v>
       </c>
       <c r="D4" t="n">
-        <v>5.55178382667067e-07</v>
+        <v>5.551783826670674e-07</v>
       </c>
       <c r="E4" t="n">
-        <v>2.497614913536241e-07</v>
+        <v>2.497614913536239e-07</v>
       </c>
       <c r="F4" t="n">
-        <v>4.839410678432631e-07</v>
+        <v>4.839410678432634e-07</v>
       </c>
       <c r="G4" t="n">
-        <v>2.12051356344768e-06</v>
+        <v>2.120513563447685e-06</v>
       </c>
       <c r="H4" t="n">
-        <v>2.279994284974727e-07</v>
+        <v>2.279994284974729e-07</v>
       </c>
       <c r="I4" t="n">
-        <v>5.642344987425291e-07</v>
+        <v>5.642344987425289e-07</v>
       </c>
       <c r="J4" t="n">
-        <v>1.060354062833744e-06</v>
+        <v>1.060354062833746e-06</v>
       </c>
       <c r="K4" t="n">
-        <v>4.851898156903497e-07</v>
+        <v>4.851898156903499e-07</v>
       </c>
       <c r="L4" t="n">
-        <v>3.083313903430099e-06</v>
+        <v>3.083313903430094e-06</v>
       </c>
       <c r="M4" t="n">
-        <v>7.688434376867446e-07</v>
+        <v>7.688434376867448e-07</v>
       </c>
       <c r="N4" t="n">
-        <v>3.793172318309571e-07</v>
+        <v>3.793172318309574e-07</v>
       </c>
       <c r="O4" t="n">
-        <v>2.670685849295795e-07</v>
+        <v>2.670685849295802e-07</v>
       </c>
       <c r="P4" t="n">
-        <v>4.198767540722972e-07</v>
+        <v>4.198767540722983e-07</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.744441627685855e-07</v>
+        <v>3.744441627685859e-07</v>
       </c>
       <c r="R4" t="n">
-        <v>2.101655040225515e-07</v>
+        <v>2.101655040225517e-07</v>
       </c>
       <c r="S4" t="n">
-        <v>3.549554024831609e-07</v>
+        <v>3.549554024831615e-07</v>
       </c>
       <c r="T4" t="n">
-        <v>3.54707271249708e-07</v>
+        <v>3.547072712497092e-07</v>
       </c>
       <c r="U4" t="n">
-        <v>4.650884545468976e-07</v>
+        <v>4.650884545468978e-07</v>
       </c>
       <c r="V4" t="n">
-        <v>2.308804759409868e-07</v>
+        <v>2.308804759409908e-07</v>
       </c>
       <c r="W4" t="n">
-        <v>8.331093764243225e-07</v>
+        <v>8.331093764243216e-07</v>
       </c>
       <c r="X4" t="n">
-        <v>1.819040770516287e-06</v>
+        <v>1.819040770516286e-06</v>
       </c>
       <c r="Y4" t="n">
-        <v>7.882461316131358e-07</v>
+        <v>7.882461316131384e-07</v>
       </c>
       <c r="Z4" t="n">
-        <v>4.449989414653656e-07</v>
+        <v>4.449989414653653e-07</v>
       </c>
       <c r="AA4" t="n">
-        <v>4.76615039685164e-07</v>
+        <v>4.766150396851645e-07</v>
       </c>
       <c r="AB4" t="n">
-        <v>9.580756408591484e-07</v>
+        <v>9.580756408591495e-07</v>
       </c>
     </row>
     <row r="5">
@@ -3166,85 +3166,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.290836452820296e-07</v>
+        <v>1.290836452820299e-07</v>
       </c>
       <c r="C5" t="n">
-        <v>1.952410735721797e-07</v>
+        <v>1.952410735721799e-07</v>
       </c>
       <c r="D5" t="n">
-        <v>1.952410735721797e-07</v>
+        <v>1.952410735721799e-07</v>
       </c>
       <c r="E5" t="n">
-        <v>1.600141945291694e-07</v>
+        <v>1.600141945291696e-07</v>
       </c>
       <c r="F5" t="n">
-        <v>1.393901994089572e-07</v>
+        <v>1.393901994089574e-07</v>
       </c>
       <c r="G5" t="n">
-        <v>2.08959247304074e-07</v>
+        <v>2.089592473040747e-07</v>
       </c>
       <c r="H5" t="n">
-        <v>1.952410735721797e-07</v>
+        <v>1.952410735721799e-07</v>
       </c>
       <c r="I5" t="n">
-        <v>1.952410735721797e-07</v>
+        <v>1.952410735721799e-07</v>
       </c>
       <c r="J5" t="n">
-        <v>1.949247242777291e-07</v>
+        <v>1.949247242777293e-07</v>
       </c>
       <c r="K5" t="n">
-        <v>1.952410735721797e-07</v>
+        <v>1.952410735721799e-07</v>
       </c>
       <c r="L5" t="n">
-        <v>1.952410735721798e-07</v>
+        <v>1.9524107357218e-07</v>
       </c>
       <c r="M5" t="n">
-        <v>1.952410735721693e-07</v>
+        <v>1.952410735721696e-07</v>
       </c>
       <c r="N5" t="n">
-        <v>3.793172318309571e-07</v>
+        <v>1.439579987478341e-07</v>
       </c>
       <c r="O5" t="n">
-        <v>1.580510329912128e-07</v>
+        <v>1.580510329912132e-07</v>
       </c>
       <c r="P5" t="n">
-        <v>1.545964897629094e-07</v>
+        <v>1.545964897629096e-07</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.160822006516191e-07</v>
+        <v>1.160822006516195e-07</v>
       </c>
       <c r="R5" t="n">
-        <v>1.952410735721797e-07</v>
+        <v>1.952410735721799e-07</v>
       </c>
       <c r="S5" t="n">
-        <v>1.952410735721797e-07</v>
+        <v>1.952410735721799e-07</v>
       </c>
       <c r="T5" t="n">
-        <v>1.952410735721797e-07</v>
+        <v>1.952410735721799e-07</v>
       </c>
       <c r="U5" t="n">
-        <v>1.629220581623097e-07</v>
+        <v>1.6292205816231e-07</v>
       </c>
       <c r="V5" t="n">
-        <v>1.750034370638808e-07</v>
+        <v>1.75003437063881e-07</v>
       </c>
       <c r="W5" t="n">
-        <v>1.952540753972391e-07</v>
+        <v>1.952540753972394e-07</v>
       </c>
       <c r="X5" t="n">
-        <v>1.221456604091961e-07</v>
+        <v>1.221456604091963e-07</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.609712159206077e-07</v>
+        <v>2.609712159206083e-07</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.278547370841563e-07</v>
+        <v>1.278547370841564e-07</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.952410735721797e-07</v>
+        <v>1.952410735721799e-07</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.643480394150364e-07</v>
+        <v>2.643480394150368e-07</v>
       </c>
     </row>
     <row r="6">
@@ -3254,85 +3254,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.661809457425433e-07</v>
+        <v>1.661809457425434e-07</v>
       </c>
       <c r="C6" t="n">
-        <v>2.05235591600836e-07</v>
+        <v>2.052355916008364e-07</v>
       </c>
       <c r="D6" t="n">
-        <v>2.05235591600836e-07</v>
+        <v>2.052355916008364e-07</v>
       </c>
       <c r="E6" t="n">
-        <v>1.962219824218042e-07</v>
+        <v>1.962219824218044e-07</v>
       </c>
       <c r="F6" t="n">
-        <v>1.152038995755561e-07</v>
+        <v>1.152038995755563e-07</v>
       </c>
       <c r="G6" t="n">
-        <v>2.052356485220934e-07</v>
+        <v>2.052356485220937e-07</v>
       </c>
       <c r="H6" t="n">
-        <v>2.05235591600836e-07</v>
+        <v>2.052355916008364e-07</v>
       </c>
       <c r="I6" t="n">
-        <v>2.05235591600836e-07</v>
+        <v>2.052355916008364e-07</v>
       </c>
       <c r="J6" t="n">
         <v>2.049192423063858e-07</v>
       </c>
       <c r="K6" t="n">
-        <v>2.05235591600836e-07</v>
+        <v>2.052355916008364e-07</v>
       </c>
       <c r="L6" t="n">
-        <v>2.052355916008361e-07</v>
+        <v>2.052355916008364e-07</v>
       </c>
       <c r="M6" t="n">
-        <v>2.05235591600836e-07</v>
+        <v>2.052355916008364e-07</v>
       </c>
       <c r="N6" t="n">
-        <v>3.793172318309571e-07</v>
+        <v>2.052355916008364e-07</v>
       </c>
       <c r="O6" t="n">
-        <v>2.181783258854709e-07</v>
+        <v>2.181783258854711e-07</v>
       </c>
       <c r="P6" t="n">
-        <v>2.209931361530562e-07</v>
+        <v>2.209931361530565e-07</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.052356485220934e-07</v>
+        <v>2.052356485220937e-07</v>
       </c>
       <c r="R6" t="n">
-        <v>2.05235591600836e-07</v>
+        <v>2.052355916008364e-07</v>
       </c>
       <c r="S6" t="n">
-        <v>2.05235591600836e-07</v>
+        <v>2.052355916008364e-07</v>
       </c>
       <c r="T6" t="n">
-        <v>2.05235591600836e-07</v>
+        <v>2.052355916008364e-07</v>
       </c>
       <c r="U6" t="n">
-        <v>2.05235591600836e-07</v>
+        <v>2.052355916008364e-07</v>
       </c>
       <c r="V6" t="n">
-        <v>2.481794599531115e-07</v>
+        <v>2.481794599531118e-07</v>
       </c>
       <c r="W6" t="n">
-        <v>2.05235591600836e-07</v>
+        <v>2.052355916008364e-07</v>
       </c>
       <c r="X6" t="n">
-        <v>2.052355916008361e-07</v>
+        <v>2.052355916008364e-07</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.05235591600836e-07</v>
+        <v>2.052355916008364e-07</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.816891356256984e-07</v>
+        <v>1.816891356256986e-07</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.05235591600836e-07</v>
+        <v>2.052355916008364e-07</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.05235591600836e-07</v>
+        <v>2.052355916008364e-07</v>
       </c>
     </row>
     <row r="7">
@@ -3342,82 +3342,82 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5.699909740770715e-08</v>
+        <v>5.699909740770723e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>5.574439997197263e-08</v>
+        <v>5.574439997197273e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>4.960727590272314e-08</v>
+        <v>4.960727590272322e-08</v>
       </c>
       <c r="E7" t="n">
         <v>9.239816373850411e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>5.113156817547673e-08</v>
+        <v>5.113156817547679e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>8.291017854424774e-09</v>
+        <v>8.291017854424794e-09</v>
       </c>
       <c r="H7" t="n">
-        <v>5.712372328146518e-08</v>
+        <v>5.712372328146517e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>4.960102367335304e-08</v>
+        <v>4.9601023673353e-08</v>
       </c>
       <c r="J7" t="n">
         <v>3.559758657893398e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>5.022084952322018e-08</v>
+        <v>5.022084952322019e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.077601471262206e-08</v>
+        <v>-1.077601471262198e-08</v>
       </c>
       <c r="M7" t="n">
-        <v>4.501448750034774e-08</v>
+        <v>4.501448750034779e-08</v>
       </c>
       <c r="N7" t="n">
-        <v>5.334839822359935e-08</v>
+        <v>5.334839822359942e-08</v>
       </c>
       <c r="O7" t="n">
-        <v>5.511899184906425e-08</v>
+        <v>5.511899184906426e-08</v>
       </c>
       <c r="P7" t="n">
-        <v>5.150152956269871e-08</v>
+        <v>5.150152956269872e-08</v>
       </c>
       <c r="Q7" t="n">
-        <v>5.336391540313978e-08</v>
+        <v>5.336391540313981e-08</v>
       </c>
       <c r="R7" t="n">
-        <v>5.762460808724315e-08</v>
+        <v>5.762460808724322e-08</v>
       </c>
       <c r="S7" t="n">
-        <v>5.330225192897939e-08</v>
+        <v>5.330225192897941e-08</v>
       </c>
       <c r="T7" t="n">
-        <v>5.392875850791548e-08</v>
+        <v>5.392875850791552e-08</v>
       </c>
       <c r="U7" t="n">
-        <v>5.100664966191126e-08</v>
+        <v>5.100664966191129e-08</v>
       </c>
       <c r="V7" t="n">
-        <v>4.051893759267545e-08</v>
+        <v>4.051893759267537e-08</v>
       </c>
       <c r="W7" t="n">
-        <v>4.262313174654301e-08</v>
+        <v>4.262313174654307e-08</v>
       </c>
       <c r="X7" t="n">
-        <v>2.21074923888695e-08</v>
+        <v>2.210749238886946e-08</v>
       </c>
       <c r="Y7" t="n">
-        <v>4.308397876355893e-08</v>
+        <v>4.308397876355903e-08</v>
       </c>
       <c r="Z7" t="n">
-        <v>5.05488647259507e-08</v>
+        <v>5.054886472595071e-08</v>
       </c>
       <c r="AA7" t="n">
-        <v>5.094054573751947e-08</v>
+        <v>5.094054573751951e-08</v>
       </c>
       <c r="AB7" t="n">
         <v>4.376928484933355e-08</v>
@@ -3430,85 +3430,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.872742646486948e-08</v>
+        <v>5.872742646486956e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>5.825726879251719e-08</v>
+        <v>5.825726879251727e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>5.663591090298662e-08</v>
+        <v>5.66359109029867e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>9.449039186678667e-08</v>
+        <v>9.44903918667868e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>5.701593237847635e-08</v>
+        <v>5.701593237847637e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>4.459429392131823e-08</v>
+        <v>4.459429392131827e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>5.87769079945508e-08</v>
+        <v>5.877690799455079e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>5.663770164879944e-08</v>
+        <v>5.663770164879949e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>5.231851737269225e-08</v>
+        <v>5.231851737269235e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>5.67718121999992e-08</v>
+        <v>5.677181219999924e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>3.935781388248199e-08</v>
+        <v>3.935781388248205e-08</v>
       </c>
       <c r="M8" t="n">
-        <v>5.523998982805442e-08</v>
+        <v>5.523998982805443e-08</v>
       </c>
       <c r="N8" t="n">
-        <v>5.769412786800397e-08</v>
+        <v>5.769412786800404e-08</v>
       </c>
       <c r="O8" t="n">
-        <v>5.806600477314203e-08</v>
+        <v>5.806600477314209e-08</v>
       </c>
       <c r="P8" t="n">
         <v>5.71341060528539e-08</v>
       </c>
       <c r="Q8" t="n">
-        <v>5.769927954770895e-08</v>
+        <v>5.769927954770903e-08</v>
       </c>
       <c r="R8" t="n">
-        <v>5.905273236435617e-08</v>
+        <v>5.905273236435624e-08</v>
       </c>
       <c r="S8" t="n">
         <v>5.767062965158469e-08</v>
       </c>
       <c r="T8" t="n">
-        <v>5.773485028094e-08</v>
+        <v>5.773485028094009e-08</v>
       </c>
       <c r="U8" t="n">
-        <v>5.713599493598945e-08</v>
+        <v>5.713599493598943e-08</v>
       </c>
       <c r="V8" t="n">
-        <v>4.324296406844064e-08</v>
+        <v>4.324296406844063e-08</v>
       </c>
       <c r="W8" t="n">
-        <v>5.462714071274871e-08</v>
+        <v>5.462714071274878e-08</v>
       </c>
       <c r="X8" t="n">
-        <v>4.962606498215051e-08</v>
+        <v>4.962606498215062e-08</v>
       </c>
       <c r="Y8" t="n">
-        <v>5.445520006905832e-08</v>
+        <v>5.445520006905839e-08</v>
       </c>
       <c r="Z8" t="n">
-        <v>5.686793998018979e-08</v>
+        <v>5.686793998018982e-08</v>
       </c>
       <c r="AA8" t="n">
-        <v>5.700368338640149e-08</v>
+        <v>5.700368338640155e-08</v>
       </c>
       <c r="AB8" t="n">
-        <v>5.619290611947486e-08</v>
+        <v>5.619290611947496e-08</v>
       </c>
     </row>
   </sheetData>
@@ -3674,85 +3674,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.93884683317194e-08</v>
+        <v>5.938846833171937e-08</v>
       </c>
       <c r="C2" t="n">
-        <v>5.930096098305826e-08</v>
+        <v>5.93009609830584e-08</v>
       </c>
       <c r="D2" t="n">
-        <v>5.984526530615181e-08</v>
+        <v>5.984526530615195e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>9.610413712348222e-08</v>
+        <v>9.610413712348219e-08</v>
       </c>
       <c r="F2" t="n">
-        <v>6.03611370436752e-08</v>
+        <v>6.036113704367542e-08</v>
       </c>
       <c r="G2" t="n">
-        <v>6.604203403967414e-08</v>
+        <v>6.604203403967422e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>5.947359343971201e-08</v>
+        <v>5.947359343971203e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>6.034173874371994e-08</v>
+        <v>6.034173874372002e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>6.193043467030591e-08</v>
+        <v>6.19304346703059e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>6.0641331474898e-08</v>
+        <v>6.064133147489813e-08</v>
       </c>
       <c r="L2" t="n">
-        <v>6.840435140119212e-08</v>
+        <v>6.840435140119202e-08</v>
       </c>
       <c r="M2" t="n">
-        <v>6.068518375960605e-08</v>
+        <v>6.068518375960609e-08</v>
       </c>
       <c r="N2" t="n">
-        <v>5.935547953763835e-08</v>
+        <v>5.935547953763857e-08</v>
       </c>
       <c r="O2" t="n">
-        <v>5.958074068505739e-08</v>
+        <v>5.958074068505771e-08</v>
       </c>
       <c r="P2" t="n">
-        <v>5.957099824416254e-08</v>
+        <v>5.957099824416274e-08</v>
       </c>
       <c r="Q2" t="n">
-        <v>5.997922623379021e-08</v>
+        <v>5.997922623379025e-08</v>
       </c>
       <c r="R2" t="n">
-        <v>6.01162891796528e-08</v>
+        <v>6.011628917965301e-08</v>
       </c>
       <c r="S2" t="n">
-        <v>6.011265548847839e-08</v>
+        <v>6.011265548847874e-08</v>
       </c>
       <c r="T2" t="n">
-        <v>5.985084262562573e-08</v>
+        <v>5.985084262562593e-08</v>
       </c>
       <c r="U2" t="n">
-        <v>6.126837140713586e-08</v>
+        <v>6.126837140713603e-08</v>
       </c>
       <c r="V2" t="n">
-        <v>4.459332823468525e-08</v>
+        <v>4.459332823468528e-08</v>
       </c>
       <c r="W2" t="n">
-        <v>6.083746410132867e-08</v>
+        <v>6.083746410132881e-08</v>
       </c>
       <c r="X2" t="n">
-        <v>6.676010022273395e-08</v>
+        <v>6.676010022273429e-08</v>
       </c>
       <c r="Y2" t="n">
-        <v>6.214030948160575e-08</v>
+        <v>6.214030948160566e-08</v>
       </c>
       <c r="Z2" t="n">
-        <v>6.031737441113927e-08</v>
+        <v>6.031737441113923e-08</v>
       </c>
       <c r="AA2" t="n">
-        <v>6.052389638446804e-08</v>
+        <v>6.052389638446836e-08</v>
       </c>
       <c r="AB2" t="n">
-        <v>6.342982070549257e-08</v>
+        <v>6.342982070549263e-08</v>
       </c>
     </row>
     <row r="3">
@@ -3762,85 +3762,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.974165783764193e-08</v>
+        <v>5.974165783764203e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>5.954803736596667e-08</v>
+        <v>5.954803736596678e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>5.974165783764193e-08</v>
+        <v>5.974165783764203e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>9.697328361798527e-08</v>
+        <v>9.697328361798547e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>5.961246733297423e-08</v>
+        <v>5.961246733297433e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>5.935340485075356e-08</v>
+        <v>5.935340485075368e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>5.974165783764193e-08</v>
+        <v>5.974165783764203e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>5.974165783764193e-08</v>
+        <v>5.974165783764203e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>5.938723322706437e-08</v>
+        <v>5.938723322706443e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>5.96683545875796e-08</v>
+        <v>5.966835458757972e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>5.974165783764193e-08</v>
+        <v>5.974165783764203e-08</v>
       </c>
       <c r="M3" t="n">
-        <v>5.932830959988163e-08</v>
+        <v>5.932830959988174e-08</v>
       </c>
       <c r="N3" t="n">
-        <v>5.974165783764193e-08</v>
+        <v>5.974165783764203e-08</v>
       </c>
       <c r="O3" t="n">
-        <v>5.952085414111801e-08</v>
+        <v>5.952085414111812e-08</v>
       </c>
       <c r="P3" t="n">
-        <v>5.931328666751998e-08</v>
+        <v>5.931328666752009e-08</v>
       </c>
       <c r="Q3" t="n">
-        <v>5.973948806933347e-08</v>
+        <v>5.973948806933358e-08</v>
       </c>
       <c r="R3" t="n">
-        <v>6.015619210818495e-08</v>
+        <v>6.015619210818505e-08</v>
       </c>
       <c r="S3" t="n">
-        <v>5.974165783764193e-08</v>
+        <v>5.974165783764203e-08</v>
       </c>
       <c r="T3" t="n">
-        <v>5.944441432938319e-08</v>
+        <v>5.944441432938329e-08</v>
       </c>
       <c r="U3" t="n">
-        <v>6.03567283808166e-08</v>
+        <v>6.035672838081672e-08</v>
       </c>
       <c r="V3" t="n">
-        <v>4.435474133265331e-08</v>
+        <v>4.435474133265333e-08</v>
       </c>
       <c r="W3" t="n">
-        <v>5.974165783764193e-08</v>
+        <v>5.974165783764203e-08</v>
       </c>
       <c r="X3" t="n">
-        <v>6.033474250959053e-08</v>
+        <v>6.033474250959063e-08</v>
       </c>
       <c r="Y3" t="n">
-        <v>5.888082059030617e-08</v>
+        <v>5.888082059030628e-08</v>
       </c>
       <c r="Z3" t="n">
-        <v>5.972481511533633e-08</v>
+        <v>5.972481511533644e-08</v>
       </c>
       <c r="AA3" t="n">
-        <v>5.974165783764193e-08</v>
+        <v>5.974165783764203e-08</v>
       </c>
       <c r="AB3" t="n">
-        <v>6.167306243339476e-08</v>
+        <v>6.167306243339486e-08</v>
       </c>
     </row>
     <row r="4">
@@ -3850,85 +3850,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.86353811597228e-07</v>
+        <v>1.863538115972278e-07</v>
       </c>
       <c r="C4" t="n">
-        <v>2.215320545739493e-07</v>
+        <v>2.215320545739495e-07</v>
       </c>
       <c r="D4" t="n">
-        <v>3.157325290316851e-07</v>
+        <v>3.157325290316867e-07</v>
       </c>
       <c r="E4" t="n">
-        <v>1.910643850736431e-07</v>
+        <v>1.910643850736432e-07</v>
       </c>
       <c r="F4" t="n">
-        <v>4.84125832847671e-07</v>
+        <v>4.841258328476717e-07</v>
       </c>
       <c r="G4" t="n">
-        <v>1.774183762748787e-06</v>
+        <v>1.774183762748785e-06</v>
       </c>
       <c r="H4" t="n">
-        <v>2.33377138867259e-07</v>
+        <v>2.333771388672599e-07</v>
       </c>
       <c r="I4" t="n">
-        <v>4.529523305570276e-07</v>
+        <v>4.529523305570278e-07</v>
       </c>
       <c r="J4" t="n">
-        <v>8.638245557907839e-07</v>
+        <v>8.638245557907842e-07</v>
       </c>
       <c r="K4" t="n">
-        <v>5.054753385807427e-07</v>
+        <v>5.054753385807442e-07</v>
       </c>
       <c r="L4" t="n">
-        <v>2.354757086765477e-06</v>
+        <v>2.354757086765478e-06</v>
       </c>
       <c r="M4" t="n">
-        <v>6.309123274257615e-07</v>
+        <v>6.309123274257613e-07</v>
       </c>
       <c r="N4" t="n">
-        <v>1.898413458756113e-07</v>
+        <v>1.898413458756117e-07</v>
       </c>
       <c r="O4" t="n">
-        <v>2.748881179692091e-07</v>
+        <v>2.748881179692096e-07</v>
       </c>
       <c r="P4" t="n">
-        <v>3.156452709270252e-07</v>
+        <v>3.156452709270246e-07</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.412521513353915e-07</v>
+        <v>3.412521513353916e-07</v>
       </c>
       <c r="R4" t="n">
-        <v>3.007516536547512e-07</v>
+        <v>3.007516536547514e-07</v>
       </c>
       <c r="S4" t="n">
-        <v>3.574444086294008e-07</v>
+        <v>3.57444408629401e-07</v>
       </c>
       <c r="T4" t="n">
-        <v>3.977573791153213e-07</v>
+        <v>3.97757379115322e-07</v>
       </c>
       <c r="U4" t="n">
-        <v>4.995677684804544e-07</v>
+        <v>4.995677684804542e-07</v>
       </c>
       <c r="V4" t="n">
-        <v>2.543172608393403e-07</v>
+        <v>2.543172608393422e-07</v>
       </c>
       <c r="W4" t="n">
-        <v>5.635640626585411e-07</v>
+        <v>5.635640626585419e-07</v>
       </c>
       <c r="X4" t="n">
         <v>1.907524916064122e-06</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.104117098641405e-06</v>
+        <v>1.104117098641402e-06</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.818694750702649e-07</v>
+        <v>3.818694750702656e-07</v>
       </c>
       <c r="AA4" t="n">
-        <v>4.858595546330121e-07</v>
+        <v>4.858595546330129e-07</v>
       </c>
       <c r="AB4" t="n">
-        <v>8.366467315103159e-07</v>
+        <v>8.36646731510316e-07</v>
       </c>
     </row>
     <row r="5">
@@ -3938,85 +3938,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.273895140393009e-07</v>
+        <v>1.273895140393008e-07</v>
       </c>
       <c r="C5" t="n">
-        <v>1.924367102011793e-07</v>
+        <v>1.924367102011794e-07</v>
       </c>
       <c r="D5" t="n">
-        <v>1.924367102011793e-07</v>
+        <v>1.924367102011794e-07</v>
       </c>
       <c r="E5" t="n">
-        <v>1.578009970166189e-07</v>
+        <v>1.578009970166193e-07</v>
       </c>
       <c r="F5" t="n">
-        <v>1.375231069762114e-07</v>
+        <v>1.375231069762118e-07</v>
       </c>
       <c r="G5" t="n">
-        <v>2.059246700688017e-07</v>
+        <v>2.05924670068802e-07</v>
       </c>
       <c r="H5" t="n">
-        <v>1.924367102011793e-07</v>
+        <v>1.924367102011794e-07</v>
       </c>
       <c r="I5" t="n">
-        <v>1.924367102011793e-07</v>
+        <v>1.924367102011794e-07</v>
       </c>
       <c r="J5" t="n">
-        <v>1.921464825224548e-07</v>
+        <v>1.921464825224552e-07</v>
       </c>
       <c r="K5" t="n">
-        <v>1.924367102011793e-07</v>
+        <v>1.924367102011794e-07</v>
       </c>
       <c r="L5" t="n">
-        <v>1.924367102011794e-07</v>
+        <v>1.924367102011795e-07</v>
       </c>
       <c r="M5" t="n">
         <v>1.924367102011745e-07</v>
       </c>
       <c r="N5" t="n">
-        <v>1.898413458756113e-07</v>
+        <v>1.420142510140676e-07</v>
       </c>
       <c r="O5" t="n">
-        <v>1.558707806078499e-07</v>
+        <v>1.558707806078501e-07</v>
       </c>
       <c r="P5" t="n">
         <v>1.524742103839013e-07</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.146062553618255e-07</v>
+        <v>1.146062553618262e-07</v>
       </c>
       <c r="R5" t="n">
-        <v>1.924367102011793e-07</v>
+        <v>1.924367102011794e-07</v>
       </c>
       <c r="S5" t="n">
-        <v>1.924367102011793e-07</v>
+        <v>1.924367102011794e-07</v>
       </c>
       <c r="T5" t="n">
-        <v>1.924367102011793e-07</v>
+        <v>1.924367102011794e-07</v>
       </c>
       <c r="U5" t="n">
-        <v>1.606631799301993e-07</v>
+        <v>1.606631799301995e-07</v>
       </c>
       <c r="V5" t="n">
-        <v>1.726782900390507e-07</v>
+        <v>1.726782900390508e-07</v>
       </c>
       <c r="W5" t="n">
-        <v>1.924494938340239e-07</v>
+        <v>1.92449493834024e-07</v>
       </c>
       <c r="X5" t="n">
-        <v>1.205679601389174e-07</v>
+        <v>1.205679601389177e-07</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.570691251347596e-07</v>
+        <v>2.570691251347595e-07</v>
       </c>
       <c r="Z5" t="n">
         <v>1.261812289731669e-07</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.924367102011793e-07</v>
+        <v>1.924367102011794e-07</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.603839457501862e-07</v>
+        <v>2.603839457501859e-07</v>
       </c>
     </row>
     <row r="6">
@@ -4026,7 +4026,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.545858787604027e-07</v>
+        <v>1.545858787604031e-07</v>
       </c>
       <c r="C6" t="n">
         <v>1.904191408422628e-07</v>
@@ -4035,13 +4035,13 @@
         <v>1.904191408422628e-07</v>
       </c>
       <c r="E6" t="n">
-        <v>1.821490117838972e-07</v>
+        <v>1.821490117838977e-07</v>
       </c>
       <c r="F6" t="n">
-        <v>1.078136212099329e-07</v>
+        <v>1.078136212099332e-07</v>
       </c>
       <c r="G6" t="n">
-        <v>1.904191950137311e-07</v>
+        <v>1.90419195013731e-07</v>
       </c>
       <c r="H6" t="n">
         <v>1.904191408422628e-07</v>
@@ -4050,28 +4050,28 @@
         <v>1.904191408422628e-07</v>
       </c>
       <c r="J6" t="n">
-        <v>1.901289131635385e-07</v>
+        <v>1.901289131635387e-07</v>
       </c>
       <c r="K6" t="n">
         <v>1.904191408422628e-07</v>
       </c>
       <c r="L6" t="n">
-        <v>1.904191408422628e-07</v>
+        <v>1.904191408422629e-07</v>
       </c>
       <c r="M6" t="n">
         <v>1.904191408422628e-07</v>
       </c>
       <c r="N6" t="n">
-        <v>1.898413458756113e-07</v>
+        <v>1.904191408422628e-07</v>
       </c>
       <c r="O6" t="n">
-        <v>2.02294309100364e-07</v>
+        <v>2.022943091003645e-07</v>
       </c>
       <c r="P6" t="n">
-        <v>2.048769426715589e-07</v>
+        <v>2.048769426715593e-07</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.904191950137311e-07</v>
+        <v>1.90419195013731e-07</v>
       </c>
       <c r="R6" t="n">
         <v>1.904191408422628e-07</v>
@@ -4086,25 +4086,25 @@
         <v>1.904191408422628e-07</v>
       </c>
       <c r="V6" t="n">
-        <v>2.298174068610291e-07</v>
+        <v>2.298174068610293e-07</v>
       </c>
       <c r="W6" t="n">
         <v>1.904191408422628e-07</v>
       </c>
       <c r="X6" t="n">
-        <v>1.904191408422628e-07</v>
+        <v>1.904191408422629e-07</v>
       </c>
       <c r="Y6" t="n">
         <v>1.904191408422628e-07</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.688148917357811e-07</v>
+        <v>1.688148917357813e-07</v>
       </c>
       <c r="AA6" t="n">
         <v>1.904191408422628e-07</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.904191408422628e-07</v>
+        <v>1.904191408422629e-07</v>
       </c>
     </row>
     <row r="7">
@@ -4114,85 +4114,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5.646469992552459e-08</v>
+        <v>5.646469992552491e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>5.579392518358066e-08</v>
+        <v>5.579392518358068e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>5.384005921824757e-08</v>
+        <v>5.384005921824758e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>9.323802572628717e-08</v>
+        <v>9.323802572628738e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>5.004471509864018e-08</v>
+        <v>5.004471509864031e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>1.440751484525092e-08</v>
+        <v>1.44075148452512e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>5.604252474729199e-08</v>
+        <v>5.604252474729207e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>5.094851227476327e-08</v>
+        <v>5.094851227476356e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>3.896640345408892e-08</v>
+        <v>3.896640345408887e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>4.869581326258407e-08</v>
+        <v>4.869581326258394e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>3.185052088109034e-09</v>
+        <v>3.185052088109064e-09</v>
       </c>
       <c r="M7" t="n">
-        <v>4.634391455913696e-08</v>
+        <v>4.634391455913702e-08</v>
       </c>
       <c r="N7" t="n">
-        <v>5.669600633638323e-08</v>
+        <v>5.669600633638345e-08</v>
       </c>
       <c r="O7" t="n">
-        <v>5.389346950888374e-08</v>
+        <v>5.389346950888399e-08</v>
       </c>
       <c r="P7" t="n">
-        <v>5.260827210895418e-08</v>
+        <v>5.260827210895424e-08</v>
       </c>
       <c r="Q7" t="n">
-        <v>5.302436979309004e-08</v>
+        <v>5.302436979309009e-08</v>
       </c>
       <c r="R7" t="n">
-        <v>5.490688221067873e-08</v>
+        <v>5.490688221067888e-08</v>
       </c>
       <c r="S7" t="n">
-        <v>5.217992092900607e-08</v>
+        <v>5.217992092900603e-08</v>
       </c>
       <c r="T7" t="n">
-        <v>5.192387628716515e-08</v>
+        <v>5.1923876287165e-08</v>
       </c>
       <c r="U7" t="n">
-        <v>4.929867251764384e-08</v>
+        <v>4.929867251764393e-08</v>
       </c>
       <c r="V7" t="n">
-        <v>3.887239002959762e-08</v>
+        <v>3.887239002959764e-08</v>
       </c>
       <c r="W7" t="n">
-        <v>4.793905865460247e-08</v>
+        <v>4.793905865460253e-08</v>
       </c>
       <c r="X7" t="n">
-        <v>1.706228759838581e-08</v>
+        <v>1.706228759838604e-08</v>
       </c>
       <c r="Y7" t="n">
-        <v>3.478507768941832e-08</v>
+        <v>3.478507768941835e-08</v>
       </c>
       <c r="Z7" t="n">
-        <v>5.083996527125522e-08</v>
+        <v>5.083996527125532e-08</v>
       </c>
       <c r="AA7" t="n">
-        <v>4.979785196828533e-08</v>
+        <v>4.979785196828529e-08</v>
       </c>
       <c r="AB7" t="n">
-        <v>4.511693714909601e-08</v>
+        <v>4.511693714909614e-08</v>
       </c>
     </row>
     <row r="8">
@@ -4202,85 +4202,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.789744203866038e-08</v>
+        <v>5.789744203866081e-08</v>
       </c>
       <c r="C8" t="n">
         <v>5.759282797642706e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>5.716001912704846e-08</v>
+        <v>5.716001912704856e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>9.440458287919903e-08</v>
+        <v>9.440458287919887e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>5.600777928643596e-08</v>
+        <v>5.600777928643612e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>4.559151085311759e-08</v>
+        <v>4.559151085311775e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>5.779047609516505e-08</v>
+        <v>5.779047609516506e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>5.634082949051791e-08</v>
+        <v>5.634082949051802e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>5.263889204627889e-08</v>
+        <v>5.263889204627883e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>5.564879020461039e-08</v>
+        <v>5.564879020461053e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>4.267091554994618e-08</v>
+        <v>4.267091554994604e-08</v>
       </c>
       <c r="M8" t="n">
-        <v>5.477724263725529e-08</v>
+        <v>5.477724263725542e-08</v>
       </c>
       <c r="N8" t="n">
-        <v>5.796969839865061e-08</v>
+        <v>5.796969839865038e-08</v>
       </c>
       <c r="O8" t="n">
-        <v>5.702026274398034e-08</v>
+        <v>5.702026274398047e-08</v>
       </c>
       <c r="P8" t="n">
-        <v>5.65201952524016e-08</v>
+        <v>5.652019525240173e-08</v>
       </c>
       <c r="Q8" t="n">
-        <v>5.692382601828731e-08</v>
+        <v>5.692382601828715e-08</v>
       </c>
       <c r="R8" t="n">
-        <v>5.772783644772961e-08</v>
+        <v>5.772783644772966e-08</v>
       </c>
       <c r="S8" t="n">
-        <v>5.667204109722349e-08</v>
+        <v>5.667204109722362e-08</v>
       </c>
       <c r="T8" t="n">
-        <v>5.642897384988367e-08</v>
+        <v>5.642897384988391e-08</v>
       </c>
       <c r="U8" t="n">
-        <v>5.623692074945915e-08</v>
+        <v>5.62369207494593e-08</v>
       </c>
       <c r="V8" t="n">
-        <v>4.209884092057796e-08</v>
+        <v>4.209884092057797e-08</v>
       </c>
       <c r="W8" t="n">
-        <v>5.546724386039381e-08</v>
+        <v>5.546724386039392e-08</v>
       </c>
       <c r="X8" t="n">
-        <v>4.707099533700466e-08</v>
+        <v>4.707099533700464e-08</v>
       </c>
       <c r="Y8" t="n">
         <v>5.117666967312518e-08</v>
       </c>
       <c r="Z8" t="n">
-        <v>5.627473941774593e-08</v>
+        <v>5.62747394177459e-08</v>
       </c>
       <c r="AA8" t="n">
-        <v>5.599943302488214e-08</v>
+        <v>5.599943302488204e-08</v>
       </c>
       <c r="AB8" t="n">
-        <v>5.589673093989581e-08</v>
+        <v>5.589673093989597e-08</v>
       </c>
     </row>
   </sheetData>
@@ -4446,85 +4446,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.816710762397708e-08</v>
+        <v>5.816710762397706e-08</v>
       </c>
       <c r="C2" t="n">
-        <v>5.772428919891858e-08</v>
+        <v>5.772428919891856e-08</v>
       </c>
       <c r="D2" t="n">
-        <v>5.984323813418174e-08</v>
+        <v>5.984323813418178e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>9.581691395063882e-08</v>
+        <v>9.581691395063889e-08</v>
       </c>
       <c r="F2" t="n">
-        <v>5.835715293356691e-08</v>
+        <v>5.835715293356695e-08</v>
       </c>
       <c r="G2" t="n">
-        <v>6.024469979638026e-08</v>
+        <v>6.024469979638023e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>5.872399112027065e-08</v>
+        <v>5.872399112027062e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>5.909735338994585e-08</v>
+        <v>5.909735338994582e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>5.915478932831925e-08</v>
+        <v>5.91547893283193e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>6.105338212434364e-08</v>
+        <v>6.105338212434356e-08</v>
       </c>
       <c r="L2" t="n">
-        <v>6.199821118497285e-08</v>
+        <v>6.199821118497281e-08</v>
       </c>
       <c r="M2" t="n">
-        <v>5.890137668601089e-08</v>
+        <v>5.890137668601086e-08</v>
       </c>
       <c r="N2" t="n">
-        <v>6.007086256459522e-08</v>
+        <v>6.00708625645952e-08</v>
       </c>
       <c r="O2" t="n">
-        <v>5.81170703034219e-08</v>
+        <v>5.811707030342189e-08</v>
       </c>
       <c r="P2" t="n">
-        <v>5.919113156668273e-08</v>
+        <v>5.91911315666827e-08</v>
       </c>
       <c r="Q2" t="n">
-        <v>5.898174228558788e-08</v>
+        <v>5.898174228558786e-08</v>
       </c>
       <c r="R2" t="n">
-        <v>5.889742205735824e-08</v>
+        <v>5.889742205735821e-08</v>
       </c>
       <c r="S2" t="n">
-        <v>5.876695159952875e-08</v>
+        <v>5.876695159952874e-08</v>
       </c>
       <c r="T2" t="n">
-        <v>5.848803130942116e-08</v>
+        <v>5.848803130942112e-08</v>
       </c>
       <c r="U2" t="n">
         <v>5.867373017157591e-08</v>
       </c>
       <c r="V2" t="n">
-        <v>4.35475637217783e-08</v>
+        <v>4.354756372177824e-08</v>
       </c>
       <c r="W2" t="n">
-        <v>5.892003762687767e-08</v>
+        <v>5.892003762687772e-08</v>
       </c>
       <c r="X2" t="n">
-        <v>5.920322273509401e-08</v>
+        <v>5.9203222735094e-08</v>
       </c>
       <c r="Y2" t="n">
-        <v>5.784906818784414e-08</v>
+        <v>5.784906818784411e-08</v>
       </c>
       <c r="Z2" t="n">
-        <v>5.879641491733051e-08</v>
+        <v>5.879641491733048e-08</v>
       </c>
       <c r="AA2" t="n">
         <v>5.900261113099527e-08</v>
       </c>
       <c r="AB2" t="n">
-        <v>7.043651509505933e-08</v>
+        <v>7.04365150950593e-08</v>
       </c>
     </row>
     <row r="3">
@@ -4534,85 +4534,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.841842792296174e-08</v>
+        <v>5.841842792296168e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>5.823334005482511e-08</v>
+        <v>5.823334005482504e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>5.841842792296174e-08</v>
+        <v>5.841842792296168e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>9.629770924360896e-08</v>
+        <v>9.629770924360912e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>5.834946554312379e-08</v>
+        <v>5.834946554312372e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>5.82581318115368e-08</v>
+        <v>5.825813181153673e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>5.841842792296174e-08</v>
+        <v>5.841842792296168e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>5.841842792296174e-08</v>
+        <v>5.841842792296168e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>5.816302748293473e-08</v>
+        <v>5.816302748293468e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>5.837811520433758e-08</v>
+        <v>5.837811520433751e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>5.841842792296174e-08</v>
+        <v>5.841842792296168e-08</v>
       </c>
       <c r="M3" t="n">
-        <v>5.835946924666094e-08</v>
+        <v>5.835946924666088e-08</v>
       </c>
       <c r="N3" t="n">
-        <v>5.841842792296174e-08</v>
+        <v>5.841842792296168e-08</v>
       </c>
       <c r="O3" t="n">
-        <v>5.824558504281906e-08</v>
+        <v>5.8245585042819e-08</v>
       </c>
       <c r="P3" t="n">
-        <v>5.837750579934473e-08</v>
+        <v>5.837750579934465e-08</v>
       </c>
       <c r="Q3" t="n">
-        <v>5.841625815465329e-08</v>
+        <v>5.841625815465322e-08</v>
       </c>
       <c r="R3" t="n">
-        <v>5.841094549290519e-08</v>
+        <v>5.841094549290512e-08</v>
       </c>
       <c r="S3" t="n">
-        <v>5.841842792296174e-08</v>
+        <v>5.841842792296168e-08</v>
       </c>
       <c r="T3" t="n">
-        <v>5.834814688675245e-08</v>
+        <v>5.834814688675238e-08</v>
       </c>
       <c r="U3" t="n">
-        <v>5.857292831872462e-08</v>
+        <v>5.857292831872455e-08</v>
       </c>
       <c r="V3" t="n">
-        <v>4.359507120889413e-08</v>
+        <v>4.35950712088941e-08</v>
       </c>
       <c r="W3" t="n">
-        <v>5.841842792296174e-08</v>
+        <v>5.841842792296168e-08</v>
       </c>
       <c r="X3" t="n">
-        <v>5.852680904601135e-08</v>
+        <v>5.852680904601129e-08</v>
       </c>
       <c r="Y3" t="n">
-        <v>5.801022569973206e-08</v>
+        <v>5.801022569973199e-08</v>
       </c>
       <c r="Z3" t="n">
-        <v>5.840824773579347e-08</v>
+        <v>5.84082477357934e-08</v>
       </c>
       <c r="AA3" t="n">
-        <v>5.841842792296174e-08</v>
+        <v>5.841842792296168e-08</v>
       </c>
       <c r="AB3" t="n">
-        <v>6.034983251871457e-08</v>
+        <v>6.03498325187145e-08</v>
       </c>
     </row>
     <row r="4">
@@ -4622,31 +4622,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.208608696055141e-07</v>
+        <v>2.208608696055142e-07</v>
       </c>
       <c r="C4" t="n">
-        <v>1.640146208891012e-07</v>
+        <v>1.640146208891009e-07</v>
       </c>
       <c r="D4" t="n">
-        <v>7.094842816369863e-07</v>
+        <v>7.094842816369868e-07</v>
       </c>
       <c r="E4" t="n">
-        <v>3.11677650419013e-07</v>
+        <v>3.116776504190126e-07</v>
       </c>
       <c r="F4" t="n">
-        <v>3.118956563856571e-07</v>
+        <v>3.11895656385657e-07</v>
       </c>
       <c r="G4" t="n">
-        <v>7.331722157624177e-07</v>
+        <v>7.331722157624169e-07</v>
       </c>
       <c r="H4" t="n">
         <v>4.132314596836886e-07</v>
       </c>
       <c r="I4" t="n">
-        <v>5.070270365167598e-07</v>
+        <v>5.070270365167596e-07</v>
       </c>
       <c r="J4" t="n">
-        <v>5.267298852467762e-07</v>
+        <v>5.26729885246776e-07</v>
       </c>
       <c r="K4" t="n">
         <v>9.719004316086706e-07</v>
@@ -4655,52 +4655,52 @@
         <v>1.1279900448095e-06</v>
       </c>
       <c r="M4" t="n">
-        <v>4.406923917756196e-07</v>
+        <v>4.406923917756194e-07</v>
       </c>
       <c r="N4" t="n">
-        <v>7.41591442101223e-07</v>
+        <v>7.415914421012228e-07</v>
       </c>
       <c r="O4" t="n">
-        <v>2.457579401976759e-07</v>
+        <v>2.457579401976763e-07</v>
       </c>
       <c r="P4" t="n">
-        <v>4.901925022836218e-07</v>
+        <v>4.901925022836223e-07</v>
       </c>
       <c r="Q4" t="n">
-        <v>4.467366340679329e-07</v>
+        <v>4.467366340679324e-07</v>
       </c>
       <c r="R4" t="n">
-        <v>4.609951092876371e-07</v>
+        <v>4.609951092876368e-07</v>
       </c>
       <c r="S4" t="n">
-        <v>3.469712207990077e-07</v>
+        <v>3.469712207990078e-07</v>
       </c>
       <c r="T4" t="n">
-        <v>3.422252380379937e-07</v>
+        <v>3.422252380379933e-07</v>
       </c>
       <c r="U4" t="n">
-        <v>3.215523352997706e-07</v>
+        <v>3.21552335299771e-07</v>
       </c>
       <c r="V4" t="n">
-        <v>2.017955677275807e-07</v>
+        <v>2.0179556772758e-07</v>
       </c>
       <c r="W4" t="n">
-        <v>4.37619934814639e-07</v>
+        <v>4.376199348146393e-07</v>
       </c>
       <c r="X4" t="n">
-        <v>4.967997887401456e-07</v>
+        <v>4.967997887401471e-07</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.481508128029009e-07</v>
+        <v>2.481508128029005e-07</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.718214673433049e-07</v>
+        <v>3.718214673433045e-07</v>
       </c>
       <c r="AA4" t="n">
-        <v>4.597978563527644e-07</v>
+        <v>4.59797856352764e-07</v>
       </c>
       <c r="AB4" t="n">
-        <v>3.248509549001457e-06</v>
+        <v>3.248509549001453e-06</v>
       </c>
     </row>
     <row r="5">
@@ -4713,31 +4713,31 @@
         <v>1.307152608512474e-07</v>
       </c>
       <c r="C5" t="n">
-        <v>1.983407768500775e-07</v>
+        <v>1.983407768500776e-07</v>
       </c>
       <c r="D5" t="n">
-        <v>1.983407768500775e-07</v>
+        <v>1.983407768500776e-07</v>
       </c>
       <c r="E5" t="n">
-        <v>1.623321844076991e-07</v>
+        <v>1.62332184407699e-07</v>
       </c>
       <c r="F5" t="n">
-        <v>1.412505258852223e-07</v>
+        <v>1.412505258852224e-07</v>
       </c>
       <c r="G5" t="n">
-        <v>2.123633681321463e-07</v>
+        <v>2.123633681321462e-07</v>
       </c>
       <c r="H5" t="n">
-        <v>1.983407768500775e-07</v>
+        <v>1.983407768500776e-07</v>
       </c>
       <c r="I5" t="n">
-        <v>1.983407768500775e-07</v>
+        <v>1.983407768500776e-07</v>
       </c>
       <c r="J5" t="n">
-        <v>1.980198619005136e-07</v>
+        <v>1.980198619005135e-07</v>
       </c>
       <c r="K5" t="n">
-        <v>1.983407768500775e-07</v>
+        <v>1.983407768500776e-07</v>
       </c>
       <c r="L5" t="n">
         <v>1.983407768500775e-07</v>
@@ -4746,49 +4746,49 @@
         <v>1.983407768500698e-07</v>
       </c>
       <c r="N5" t="n">
-        <v>7.41591442101223e-07</v>
+        <v>1.459196884459238e-07</v>
       </c>
       <c r="O5" t="n">
-        <v>1.603254587028527e-07</v>
+        <v>1.603254587028526e-07</v>
       </c>
       <c r="P5" t="n">
-        <v>1.567942563207854e-07</v>
+        <v>1.567942563207853e-07</v>
       </c>
       <c r="Q5" t="n">
         <v>1.174253034779971e-07</v>
       </c>
       <c r="R5" t="n">
-        <v>1.983407768500775e-07</v>
+        <v>1.983407768500776e-07</v>
       </c>
       <c r="S5" t="n">
-        <v>1.983407768500775e-07</v>
+        <v>1.983407768500776e-07</v>
       </c>
       <c r="T5" t="n">
-        <v>1.983407768500775e-07</v>
+        <v>1.983407768500776e-07</v>
       </c>
       <c r="U5" t="n">
-        <v>1.65324495038851e-07</v>
+        <v>1.653244950388508e-07</v>
       </c>
       <c r="V5" t="n">
-        <v>1.776845015674563e-07</v>
+        <v>1.776845015674562e-07</v>
       </c>
       <c r="W5" t="n">
-        <v>1.983540671975013e-07</v>
+        <v>1.983540671975014e-07</v>
       </c>
       <c r="X5" t="n">
-        <v>1.236233163919688e-07</v>
+        <v>1.236233163919687e-07</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.655636008884641e-07</v>
+        <v>2.65563600888464e-07</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.2945908217012e-07</v>
+        <v>1.294590821701198e-07</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.983407768500775e-07</v>
+        <v>1.983407768500776e-07</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.689812830656008e-07</v>
+        <v>2.689812830656004e-07</v>
       </c>
     </row>
     <row r="6">
@@ -4807,7 +4807,7 @@
         <v>2.057083497965209e-07</v>
       </c>
       <c r="E6" t="n">
-        <v>1.96637150163186e-07</v>
+        <v>1.966371501631861e-07</v>
       </c>
       <c r="F6" t="n">
         <v>1.151014851060004e-07</v>
@@ -4822,7 +4822,7 @@
         <v>2.057083497965209e-07</v>
       </c>
       <c r="J6" t="n">
-        <v>2.053874348469565e-07</v>
+        <v>2.053874348469566e-07</v>
       </c>
       <c r="K6" t="n">
         <v>2.057083497965209e-07</v>
@@ -4834,13 +4834,13 @@
         <v>2.057083497965209e-07</v>
       </c>
       <c r="N6" t="n">
-        <v>7.41591442101223e-07</v>
+        <v>2.057083497965209e-07</v>
       </c>
       <c r="O6" t="n">
-        <v>2.187337612361905e-07</v>
+        <v>2.187337612361909e-07</v>
       </c>
       <c r="P6" t="n">
-        <v>2.215665538562401e-07</v>
+        <v>2.215665538562403e-07</v>
       </c>
       <c r="Q6" t="n">
         <v>2.057083998678385e-07</v>
@@ -4870,7 +4870,7 @@
         <v>2.057083497965209e-07</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.820114606002343e-07</v>
+        <v>1.820114606002344e-07</v>
       </c>
       <c r="AA6" t="n">
         <v>2.057083497965209e-07</v>
@@ -4886,85 +4886,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5.45655753040479e-08</v>
+        <v>5.456557530404786e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>5.604092552369866e-08</v>
+        <v>5.60409255236986e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>4.480751286680954e-08</v>
+        <v>4.480751286680958e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>9.023857934394932e-08</v>
+        <v>9.023857934394953e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>5.310013066010532e-08</v>
+        <v>5.310013066010525e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>4.118339328603703e-08</v>
+        <v>4.118339328603698e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>5.141137802240599e-08</v>
+        <v>5.141137802240604e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>4.91939260739781e-08</v>
+        <v>4.919392607397815e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>4.696917014733253e-08</v>
+        <v>4.696917014733255e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>3.743325708975272e-08</v>
+        <v>3.743325708975274e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>3.194112007770221e-08</v>
+        <v>3.194112007770214e-08</v>
       </c>
       <c r="M7" t="n">
-        <v>4.998200097328031e-08</v>
+        <v>4.998200097328025e-08</v>
       </c>
       <c r="N7" t="n">
-        <v>4.341081528377175e-08</v>
+        <v>4.341081528377164e-08</v>
       </c>
       <c r="O7" t="n">
-        <v>5.374581479789816e-08</v>
+        <v>5.374581479789814e-08</v>
       </c>
       <c r="P7" t="n">
-        <v>4.818989691831964e-08</v>
+        <v>4.818989691831969e-08</v>
       </c>
       <c r="Q7" t="n">
-        <v>4.981794122357296e-08</v>
+        <v>4.98179412235729e-08</v>
       </c>
       <c r="R7" t="n">
-        <v>5.033223406540538e-08</v>
+        <v>5.033223406540551e-08</v>
       </c>
       <c r="S7" t="n">
-        <v>5.102002792477576e-08</v>
+        <v>5.10200279247757e-08</v>
       </c>
       <c r="T7" t="n">
-        <v>5.230306595597102e-08</v>
+        <v>5.230306595597099e-08</v>
       </c>
       <c r="U7" t="n">
-        <v>5.257807258466415e-08</v>
+        <v>5.257807258466422e-08</v>
       </c>
       <c r="V7" t="n">
-        <v>3.982782435718851e-08</v>
+        <v>3.982782435718843e-08</v>
       </c>
       <c r="W7" t="n">
-        <v>5.015266152756038e-08</v>
+        <v>5.015266152756032e-08</v>
       </c>
       <c r="X7" t="n">
-        <v>4.923597307331445e-08</v>
+        <v>4.923597307331444e-08</v>
       </c>
       <c r="Y7" t="n">
-        <v>5.387046310113174e-08</v>
+        <v>5.387046310113177e-08</v>
       </c>
       <c r="Z7" t="n">
-        <v>5.076471242738393e-08</v>
+        <v>5.076471242738383e-08</v>
       </c>
       <c r="AA7" t="n">
-        <v>4.967246442489943e-08</v>
+        <v>4.967246442489941e-08</v>
       </c>
       <c r="AB7" t="n">
-        <v>-4.958270621619359e-09</v>
+        <v>-4.958270621619432e-09</v>
       </c>
     </row>
     <row r="8">
@@ -4977,82 +4977,82 @@
         <v>5.64140474040585e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>5.67267336004454e-08</v>
+        <v>5.672673360044539e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>5.365022840822003e-08</v>
+        <v>5.365022840821997e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>9.305999053699242e-08</v>
+        <v>9.30599905369925e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>5.596868883315584e-08</v>
+        <v>5.59686888331558e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>5.247563935331479e-08</v>
+        <v>5.247563935331477e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>5.553576108537478e-08</v>
+        <v>5.553576108537476e-08</v>
       </c>
       <c r="I8" t="n">
         <v>5.49001756519152e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>5.406154856791352e-08</v>
+        <v>5.406154856791351e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>5.152340493490501e-08</v>
+        <v>5.152340493490509e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>4.995095173720616e-08</v>
+        <v>4.995095173720615e-08</v>
       </c>
       <c r="M8" t="n">
-        <v>5.508960192421538e-08</v>
+        <v>5.508960192421532e-08</v>
       </c>
       <c r="N8" t="n">
-        <v>5.324235098734012e-08</v>
+        <v>5.324235098734009e-08</v>
       </c>
       <c r="O8" t="n">
-        <v>5.6069660502066e-08</v>
+        <v>5.606966050206602e-08</v>
       </c>
       <c r="P8" t="n">
-        <v>5.455573705983316e-08</v>
+        <v>5.455573705983318e-08</v>
       </c>
       <c r="Q8" t="n">
-        <v>5.506948068073602e-08</v>
+        <v>5.506948068073608e-08</v>
       </c>
       <c r="R8" t="n">
-        <v>5.522158261252024e-08</v>
+        <v>5.52215826125202e-08</v>
       </c>
       <c r="S8" t="n">
-        <v>5.540065602305228e-08</v>
+        <v>5.540065602305225e-08</v>
       </c>
       <c r="T8" t="n">
-        <v>5.573750022138582e-08</v>
+        <v>5.573750022138565e-08</v>
       </c>
       <c r="U8" t="n">
-        <v>5.594605170810673e-08</v>
+        <v>5.594605170810678e-08</v>
       </c>
       <c r="V8" t="n">
-        <v>4.183345439874883e-08</v>
+        <v>4.18334543987488e-08</v>
       </c>
       <c r="W8" t="n">
-        <v>5.51590875755355e-08</v>
+        <v>5.515908757553552e-08</v>
       </c>
       <c r="X8" t="n">
-        <v>5.49758627593796e-08</v>
+        <v>5.497586275937951e-08</v>
       </c>
       <c r="Y8" t="n">
-        <v>5.596546301284039e-08</v>
+        <v>5.596546301284037e-08</v>
       </c>
       <c r="Z8" t="n">
         <v>5.53185819935023e-08</v>
       </c>
       <c r="AA8" t="n">
-        <v>5.502316986764501e-08</v>
+        <v>5.502316986764494e-08</v>
       </c>
       <c r="AB8" t="n">
-        <v>4.072112004163153e-08</v>
+        <v>4.072112004163152e-08</v>
       </c>
     </row>
   </sheetData>
@@ -5218,85 +5218,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.757049401472819e-08</v>
+        <v>5.757049401472814e-08</v>
       </c>
       <c r="C2" t="n">
-        <v>5.740520951801784e-08</v>
+        <v>5.740520951801778e-08</v>
       </c>
       <c r="D2" t="n">
-        <v>5.770394280997597e-08</v>
+        <v>5.770394280997594e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>9.519100631309238e-08</v>
+        <v>9.519100631309227e-08</v>
       </c>
       <c r="F2" t="n">
-        <v>5.811621575363142e-08</v>
+        <v>5.811621575363136e-08</v>
       </c>
       <c r="G2" t="n">
-        <v>5.776994686256794e-08</v>
+        <v>5.776994686256788e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>5.76890924429304e-08</v>
+        <v>5.768909244293035e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>5.789829727989445e-08</v>
+        <v>5.789829727989444e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>5.775413101316944e-08</v>
+        <v>5.775413101316931e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>5.755164672344532e-08</v>
+        <v>5.755164672344527e-08</v>
       </c>
       <c r="L2" t="n">
-        <v>5.793259021841183e-08</v>
+        <v>5.793259021841181e-08</v>
       </c>
       <c r="M2" t="n">
-        <v>5.72106152818725e-08</v>
+        <v>5.721061528187247e-08</v>
       </c>
       <c r="N2" t="n">
-        <v>5.828716004880556e-08</v>
+        <v>5.828716004880551e-08</v>
       </c>
       <c r="O2" t="n">
-        <v>5.845582662052362e-08</v>
+        <v>5.845582662052359e-08</v>
       </c>
       <c r="P2" t="n">
-        <v>5.763803609184134e-08</v>
+        <v>5.763803609184132e-08</v>
       </c>
       <c r="Q2" t="n">
-        <v>5.739851003614926e-08</v>
+        <v>5.739851003614922e-08</v>
       </c>
       <c r="R2" t="n">
-        <v>5.899212259499724e-08</v>
+        <v>5.899212259499721e-08</v>
       </c>
       <c r="S2" t="n">
-        <v>5.781310172117246e-08</v>
+        <v>5.781310172117249e-08</v>
       </c>
       <c r="T2" t="n">
-        <v>5.718492526073667e-08</v>
+        <v>5.718492526073659e-08</v>
       </c>
       <c r="U2" t="n">
-        <v>5.733726089171598e-08</v>
+        <v>5.733726089171595e-08</v>
       </c>
       <c r="V2" t="n">
-        <v>4.334335753910108e-08</v>
+        <v>4.334335753910116e-08</v>
       </c>
       <c r="W2" t="n">
-        <v>5.878912323350527e-08</v>
+        <v>5.878912323350523e-08</v>
       </c>
       <c r="X2" t="n">
-        <v>5.982403558312905e-08</v>
+        <v>5.982403558312907e-08</v>
       </c>
       <c r="Y2" t="n">
-        <v>5.713601576070122e-08</v>
+        <v>5.713601576070118e-08</v>
       </c>
       <c r="Z2" t="n">
-        <v>5.837007451642959e-08</v>
+        <v>5.837007451642953e-08</v>
       </c>
       <c r="AA2" t="n">
-        <v>5.780632951299733e-08</v>
+        <v>5.78063295129973e-08</v>
       </c>
       <c r="AB2" t="n">
-        <v>5.887065684658858e-08</v>
+        <v>5.887065684658855e-08</v>
       </c>
     </row>
     <row r="3">
@@ -5306,85 +5306,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.76555004599434e-08</v>
+        <v>5.765550045994337e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>5.746111962902367e-08</v>
+        <v>5.746111962902364e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>5.76555004599434e-08</v>
+        <v>5.765550045994337e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>9.571844395289333e-08</v>
+        <v>9.571844395289326e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>5.755816591429781e-08</v>
+        <v>5.755816591429779e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>5.739541505414302e-08</v>
+        <v>5.7395415054143e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>5.76555004599434e-08</v>
+        <v>5.765550045994337e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>5.76555004599434e-08</v>
+        <v>5.765550045994337e-08</v>
       </c>
       <c r="J3" t="n">
         <v>5.746050543882015e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>5.759831982525103e-08</v>
+        <v>5.759831982525101e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>5.76555004599434e-08</v>
+        <v>5.765550045994337e-08</v>
       </c>
       <c r="M3" t="n">
-        <v>5.749602422456606e-08</v>
+        <v>5.749602422456603e-08</v>
       </c>
       <c r="N3" t="n">
-        <v>5.76555004599434e-08</v>
+        <v>5.765550045994337e-08</v>
       </c>
       <c r="O3" t="n">
-        <v>5.746248804004649e-08</v>
+        <v>5.746248804004646e-08</v>
       </c>
       <c r="P3" t="n">
-        <v>5.76348627689385e-08</v>
+        <v>5.763486276893847e-08</v>
       </c>
       <c r="Q3" t="n">
-        <v>5.765333069163495e-08</v>
+        <v>5.765333069163492e-08</v>
       </c>
       <c r="R3" t="n">
-        <v>5.78705431617727e-08</v>
+        <v>5.787054316177268e-08</v>
       </c>
       <c r="S3" t="n">
-        <v>5.76555004599434e-08</v>
+        <v>5.765550045994337e-08</v>
       </c>
       <c r="T3" t="n">
-        <v>5.744852326111034e-08</v>
+        <v>5.744852326111031e-08</v>
       </c>
       <c r="U3" t="n">
-        <v>5.784533980186024e-08</v>
+        <v>5.784533980186022e-08</v>
       </c>
       <c r="V3" t="n">
-        <v>4.308379991893197e-08</v>
+        <v>4.308379991893144e-08</v>
       </c>
       <c r="W3" t="n">
-        <v>5.76555004599434e-08</v>
+        <v>5.765550045994337e-08</v>
       </c>
       <c r="X3" t="n">
-        <v>5.894917496379867e-08</v>
+        <v>5.894917496379864e-08</v>
       </c>
       <c r="Y3" t="n">
-        <v>5.716485766966856e-08</v>
+        <v>5.716485766966853e-08</v>
       </c>
       <c r="Z3" t="n">
-        <v>5.763838283101843e-08</v>
+        <v>5.76383828310184e-08</v>
       </c>
       <c r="AA3" t="n">
-        <v>5.76555004599434e-08</v>
+        <v>5.765550045994337e-08</v>
       </c>
       <c r="AB3" t="n">
-        <v>5.958690505569623e-08</v>
+        <v>5.95869050556962e-08</v>
       </c>
     </row>
     <row r="4">
@@ -5394,85 +5394,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.447791417050493e-07</v>
+        <v>2.447791417050495e-07</v>
       </c>
       <c r="C4" t="n">
-        <v>2.618361213275669e-07</v>
+        <v>2.618361213275666e-07</v>
       </c>
       <c r="D4" t="n">
-        <v>2.920152833031102e-07</v>
+        <v>2.920152833031098e-07</v>
       </c>
       <c r="E4" t="n">
-        <v>2.777243160189626e-07</v>
+        <v>2.777243160189628e-07</v>
       </c>
       <c r="F4" t="n">
-        <v>4.219795682304843e-07</v>
+        <v>4.21979568230484e-07</v>
       </c>
       <c r="G4" t="n">
-        <v>3.272510842110778e-07</v>
+        <v>3.272510842110785e-07</v>
       </c>
       <c r="H4" t="n">
-        <v>3.075686826124457e-07</v>
+        <v>3.075686826124456e-07</v>
       </c>
       <c r="I4" t="n">
-        <v>3.499579160985994e-07</v>
+        <v>3.499579160985988e-07</v>
       </c>
       <c r="J4" t="n">
-        <v>3.285718967778356e-07</v>
+        <v>3.285718967778357e-07</v>
       </c>
       <c r="K4" t="n">
-        <v>2.604942683139026e-07</v>
+        <v>2.604942683139024e-07</v>
       </c>
       <c r="L4" t="n">
-        <v>3.061329863221983e-07</v>
+        <v>3.061329863221977e-07</v>
       </c>
       <c r="M4" t="n">
-        <v>2.061244716684081e-07</v>
+        <v>2.061244716684078e-07</v>
       </c>
       <c r="N4" t="n">
-        <v>4.28754094115147e-07</v>
+        <v>4.287540941151465e-07</v>
       </c>
       <c r="O4" t="n">
-        <v>4.741769843359324e-07</v>
+        <v>4.741769843359329e-07</v>
       </c>
       <c r="P4" t="n">
-        <v>2.62999197248968e-07</v>
+        <v>2.629991972489681e-07</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.057499439492571e-07</v>
+        <v>2.057499439492569e-07</v>
       </c>
       <c r="R4" t="n">
-        <v>5.911207771139285e-07</v>
+        <v>5.911207771139277e-07</v>
       </c>
       <c r="S4" t="n">
         <v>2.839045803182599e-07</v>
       </c>
       <c r="T4" t="n">
-        <v>2.122106723310587e-07</v>
+        <v>2.122106723310586e-07</v>
       </c>
       <c r="U4" t="n">
-        <v>1.546418673020869e-07</v>
+        <v>1.546418673020868e-07</v>
       </c>
       <c r="V4" t="n">
-        <v>2.536180050890064e-07</v>
+        <v>2.536180050890076e-07</v>
       </c>
       <c r="W4" t="n">
-        <v>5.407287763786381e-07</v>
+        <v>5.407287763786377e-07</v>
       </c>
       <c r="X4" t="n">
-        <v>5.13864090160363e-07</v>
+        <v>5.138640901603649e-07</v>
       </c>
       <c r="Y4" t="n">
         <v>2.627735058590343e-07</v>
       </c>
       <c r="Z4" t="n">
-        <v>4.173081550521595e-07</v>
+        <v>4.173081550521587e-07</v>
       </c>
       <c r="AA4" t="n">
-        <v>3.180983006401124e-07</v>
+        <v>3.180983006401129e-07</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.496462746880597e-07</v>
+        <v>1.496462746880596e-07</v>
       </c>
     </row>
     <row r="5">
@@ -5482,85 +5482,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.203631768054186e-07</v>
+        <v>1.203631768054182e-07</v>
       </c>
       <c r="C5" t="n">
-        <v>1.813850437020288e-07</v>
+        <v>1.813850437020281e-07</v>
       </c>
       <c r="D5" t="n">
-        <v>1.813850437020288e-07</v>
+        <v>1.813850437020281e-07</v>
       </c>
       <c r="E5" t="n">
-        <v>1.488926996111732e-07</v>
+        <v>1.488926996111727e-07</v>
       </c>
       <c r="F5" t="n">
-        <v>1.298696704879626e-07</v>
+        <v>1.298696704879623e-07</v>
       </c>
       <c r="G5" t="n">
-        <v>1.940383253239596e-07</v>
+        <v>1.940383253239591e-07</v>
       </c>
       <c r="H5" t="n">
-        <v>1.813850437020288e-07</v>
+        <v>1.813850437020281e-07</v>
       </c>
       <c r="I5" t="n">
-        <v>1.813850437020288e-07</v>
+        <v>1.813850437020281e-07</v>
       </c>
       <c r="J5" t="n">
-        <v>1.811112151833405e-07</v>
+        <v>1.811112151833399e-07</v>
       </c>
       <c r="K5" t="n">
-        <v>1.813850437020288e-07</v>
+        <v>1.813850437020281e-07</v>
       </c>
       <c r="L5" t="n">
-        <v>1.813850437020288e-07</v>
+        <v>1.813850437020281e-07</v>
       </c>
       <c r="M5" t="n">
-        <v>1.813850437020206e-07</v>
+        <v>1.813850437020199e-07</v>
       </c>
       <c r="N5" t="n">
-        <v>4.28754094115147e-07</v>
+        <v>1.340828881187512e-07</v>
       </c>
       <c r="O5" t="n">
-        <v>1.47081931189735e-07</v>
+        <v>1.470819311897344e-07</v>
       </c>
       <c r="P5" t="n">
-        <v>1.438955516322291e-07</v>
+        <v>1.438955516322287e-07</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.083709872018548e-07</v>
+        <v>1.083709872018546e-07</v>
       </c>
       <c r="R5" t="n">
-        <v>1.813850437020288e-07</v>
+        <v>1.813850437020281e-07</v>
       </c>
       <c r="S5" t="n">
-        <v>1.813850437020288e-07</v>
+        <v>1.813850437020281e-07</v>
       </c>
       <c r="T5" t="n">
-        <v>1.813850437020288e-07</v>
+        <v>1.813850437020281e-07</v>
       </c>
       <c r="U5" t="n">
-        <v>1.515992258450623e-07</v>
+        <v>1.515992258450618e-07</v>
       </c>
       <c r="V5" t="n">
-        <v>1.628521933165498e-07</v>
+        <v>1.628521933165493e-07</v>
       </c>
       <c r="W5" t="n">
-        <v>1.813970362436402e-07</v>
+        <v>1.813970362436399e-07</v>
       </c>
       <c r="X5" t="n">
-        <v>1.139637625541359e-07</v>
+        <v>1.139637625541356e-07</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.420545166808477e-07</v>
+        <v>2.42054516680847e-07</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.192296642968697e-07</v>
+        <v>1.192296642968694e-07</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.813850437020288e-07</v>
+        <v>1.813850437020281e-07</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.451274862421275e-07</v>
+        <v>2.451274862421266e-07</v>
       </c>
     </row>
     <row r="6">
@@ -5570,85 +5570,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.421733198678484e-07</v>
+        <v>1.421733198678483e-07</v>
       </c>
       <c r="C6" t="n">
-        <v>1.747649608827056e-07</v>
+        <v>1.747649608827057e-07</v>
       </c>
       <c r="D6" t="n">
-        <v>1.747649608827056e-07</v>
+        <v>1.747649608827057e-07</v>
       </c>
       <c r="E6" t="n">
-        <v>1.672429810837654e-07</v>
+        <v>1.672429810837652e-07</v>
       </c>
       <c r="F6" t="n">
-        <v>9.963226874371119e-08</v>
+        <v>9.963226874371108e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>1.747650102953489e-07</v>
+        <v>1.747650102953488e-07</v>
       </c>
       <c r="H6" t="n">
-        <v>1.747649608827056e-07</v>
+        <v>1.747649608827057e-07</v>
       </c>
       <c r="I6" t="n">
-        <v>1.747649608827056e-07</v>
+        <v>1.747649608827057e-07</v>
       </c>
       <c r="J6" t="n">
-        <v>1.744911323640178e-07</v>
+        <v>1.744911323640171e-07</v>
       </c>
       <c r="K6" t="n">
-        <v>1.747649608827056e-07</v>
+        <v>1.747649608827057e-07</v>
       </c>
       <c r="L6" t="n">
-        <v>1.747649608827056e-07</v>
+        <v>1.747649608827057e-07</v>
       </c>
       <c r="M6" t="n">
-        <v>1.747649608827056e-07</v>
+        <v>1.747649608827057e-07</v>
       </c>
       <c r="N6" t="n">
-        <v>4.28754094115147e-07</v>
+        <v>1.747649608827057e-07</v>
       </c>
       <c r="O6" t="n">
-        <v>1.855658538278489e-07</v>
+        <v>1.855658538278488e-07</v>
       </c>
       <c r="P6" t="n">
-        <v>1.879148519848987e-07</v>
+        <v>1.879148519848984e-07</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.747650102953489e-07</v>
+        <v>1.747650102953488e-07</v>
       </c>
       <c r="R6" t="n">
-        <v>1.747649608827056e-07</v>
+        <v>1.747649608827057e-07</v>
       </c>
       <c r="S6" t="n">
-        <v>1.747649608827056e-07</v>
+        <v>1.747649608827057e-07</v>
       </c>
       <c r="T6" t="n">
-        <v>1.747649608827056e-07</v>
+        <v>1.747649608827057e-07</v>
       </c>
       <c r="U6" t="n">
-        <v>1.747649608827056e-07</v>
+        <v>1.747649608827057e-07</v>
       </c>
       <c r="V6" t="n">
-        <v>2.105224822222954e-07</v>
+        <v>2.105224822222949e-07</v>
       </c>
       <c r="W6" t="n">
-        <v>1.747649608827056e-07</v>
+        <v>1.747649608827057e-07</v>
       </c>
       <c r="X6" t="n">
-        <v>1.747649608827056e-07</v>
+        <v>1.747649608827057e-07</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.747649608827056e-07</v>
+        <v>1.747649608827057e-07</v>
       </c>
       <c r="Z6" t="n">
         <v>1.551151191337574e-07</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.747649608827056e-07</v>
+        <v>1.747649608827057e-07</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.747649608827056e-07</v>
+        <v>1.747649608827057e-07</v>
       </c>
     </row>
     <row r="7">
@@ -5658,85 +5658,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5.28577395237846e-08</v>
+        <v>5.285773952378454e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>5.265991005364814e-08</v>
+        <v>5.265991005364812e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>5.215052581281094e-08</v>
+        <v>5.215052581281088e-08</v>
       </c>
       <c r="E7" t="n">
         <v>8.996398537615469e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>4.915865247631271e-08</v>
+        <v>4.91586524763127e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>5.000125500909272e-08</v>
+        <v>5.000125500909276e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>5.227430807344496e-08</v>
+        <v>5.227430807344494e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>5.10245924694699e-08</v>
+        <v>5.102459246946985e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>5.044779391133561e-08</v>
+        <v>5.044779391133574e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>5.267232700942421e-08</v>
+        <v>5.267232700942419e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>5.074742176060171e-08</v>
+        <v>5.074742176060168e-08</v>
       </c>
       <c r="M7" t="n">
-        <v>5.404039570613535e-08</v>
+        <v>5.404039570613531e-08</v>
       </c>
       <c r="N7" t="n">
-        <v>4.869641742741026e-08</v>
+        <v>4.869641742741024e-08</v>
       </c>
       <c r="O7" t="n">
         <v>4.633627322222428e-08</v>
       </c>
       <c r="P7" t="n">
-        <v>5.231250557651382e-08</v>
+        <v>5.231250557651384e-08</v>
       </c>
       <c r="Q7" t="n">
-        <v>5.391619776780529e-08</v>
+        <v>5.391619776780527e-08</v>
       </c>
       <c r="R7" t="n">
-        <v>4.60181196246592e-08</v>
+        <v>4.601811962465914e-08</v>
       </c>
       <c r="S7" t="n">
-        <v>5.143380565738346e-08</v>
+        <v>5.143380565738348e-08</v>
       </c>
       <c r="T7" t="n">
-        <v>5.387810356692379e-08</v>
+        <v>5.387810356692383e-08</v>
       </c>
       <c r="U7" t="n">
-        <v>5.54799436565968e-08</v>
+        <v>5.547994365659678e-08</v>
       </c>
       <c r="V7" t="n">
-        <v>3.750429443951293e-08</v>
+        <v>3.750429443951234e-08</v>
       </c>
       <c r="W7" t="n">
-        <v>4.57037701886368e-08</v>
+        <v>4.570377018863671e-08</v>
       </c>
       <c r="X7" t="n">
-        <v>4.793979899218698e-08</v>
+        <v>4.793979899218699e-08</v>
       </c>
       <c r="Y7" t="n">
-        <v>5.233138350654256e-08</v>
+        <v>5.233138350654251e-08</v>
       </c>
       <c r="Z7" t="n">
         <v>4.800144806656855e-08</v>
       </c>
       <c r="AA7" t="n">
-        <v>5.150922858434805e-08</v>
+        <v>5.150922858434803e-08</v>
       </c>
       <c r="AB7" t="n">
-        <v>5.758665833274423e-08</v>
+        <v>5.758665833274424e-08</v>
       </c>
     </row>
     <row r="8">
@@ -5746,85 +5746,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.538749749921904e-08</v>
+        <v>5.538749749921901e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>5.522064386067489e-08</v>
+        <v>5.522064386067487e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>5.519916180221741e-08</v>
+        <v>5.519916180221735e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>9.257270932230477e-08</v>
+        <v>9.257270932230475e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>5.429441037168706e-08</v>
+        <v>5.429441037168703e-08</v>
       </c>
       <c r="G8" t="n">
         <v>5.440558047828012e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>5.524063275823098e-08</v>
+        <v>5.524063275823093e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>5.488121301277907e-08</v>
+        <v>5.488121301277903e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>5.456332491997823e-08</v>
+        <v>5.456332491997814e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>5.531030429403639e-08</v>
+        <v>5.531030429403638e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>5.478939239547077e-08</v>
+        <v>5.478939239547076e-08</v>
       </c>
       <c r="M8" t="n">
-        <v>5.563829329355188e-08</v>
+        <v>5.563829329355186e-08</v>
       </c>
       <c r="N8" t="n">
-        <v>5.421074871809942e-08</v>
+        <v>5.421074871809932e-08</v>
       </c>
       <c r="O8" t="n">
-        <v>5.339336342127163e-08</v>
+        <v>5.339336342127162e-08</v>
       </c>
       <c r="P8" t="n">
-        <v>5.52163466079421e-08</v>
+        <v>5.521634660794212e-08</v>
       </c>
       <c r="Q8" t="n">
-        <v>5.569810264627081e-08</v>
+        <v>5.569810264627083e-08</v>
       </c>
       <c r="R8" t="n">
-        <v>5.359923211417784e-08</v>
+        <v>5.359923211417782e-08</v>
       </c>
       <c r="S8" t="n">
-        <v>5.498221075864279e-08</v>
+        <v>5.498221075864281e-08</v>
       </c>
       <c r="T8" t="n">
-        <v>5.556037292162929e-08</v>
+        <v>5.556037292162931e-08</v>
       </c>
       <c r="U8" t="n">
-        <v>5.626099810755081e-08</v>
+        <v>5.626099810755079e-08</v>
       </c>
       <c r="V8" t="n">
-        <v>4.080466476513639e-08</v>
+        <v>4.080466476513653e-08</v>
       </c>
       <c r="W8" t="n">
-        <v>5.335104787215628e-08</v>
+        <v>5.335104787215625e-08</v>
       </c>
       <c r="X8" t="n">
-        <v>5.48147344312463e-08</v>
+        <v>5.481473443124627e-08</v>
       </c>
       <c r="Y8" t="n">
-        <v>5.49367696131106e-08</v>
+        <v>5.493676961311062e-08</v>
       </c>
       <c r="Z8" t="n">
-        <v>5.398523848751601e-08</v>
+        <v>5.398523848751597e-08</v>
       </c>
       <c r="AA8" t="n">
-        <v>5.50097562225952e-08</v>
+        <v>5.500975622259514e-08</v>
       </c>
       <c r="AB8" t="n">
-        <v>5.796053821323738e-08</v>
+        <v>5.796053821323734e-08</v>
       </c>
     </row>
   </sheetData>
@@ -5990,85 +5990,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.791394904890071e-08</v>
+        <v>5.791394904890066e-08</v>
       </c>
       <c r="C2" t="n">
-        <v>5.740389521306036e-08</v>
+        <v>5.740389521306028e-08</v>
       </c>
       <c r="D2" t="n">
-        <v>5.768249408948497e-08</v>
+        <v>5.768249408948489e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>9.602510218124733e-08</v>
+        <v>9.602510218124725e-08</v>
       </c>
       <c r="F2" t="n">
-        <v>5.774575852630351e-08</v>
+        <v>5.774575852630341e-08</v>
       </c>
       <c r="G2" t="n">
-        <v>5.71752394439072e-08</v>
+        <v>5.717523944390713e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>5.736444664127019e-08</v>
+        <v>5.736444664127013e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>5.742989554879688e-08</v>
+        <v>5.74298955487968e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>5.761913521150192e-08</v>
+        <v>5.761913521150185e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>5.723906209035427e-08</v>
+        <v>5.723906209035424e-08</v>
       </c>
       <c r="L2" t="n">
-        <v>5.787492377813887e-08</v>
+        <v>5.787492377813883e-08</v>
       </c>
       <c r="M2" t="n">
-        <v>5.684364938223169e-08</v>
+        <v>5.684364938223162e-08</v>
       </c>
       <c r="N2" t="n">
-        <v>5.7524762577288e-08</v>
+        <v>5.75247625772879e-08</v>
       </c>
       <c r="O2" t="n">
-        <v>5.845191127266171e-08</v>
+        <v>5.845191127266167e-08</v>
       </c>
       <c r="P2" t="n">
-        <v>5.743613289450539e-08</v>
+        <v>5.743613289450533e-08</v>
       </c>
       <c r="Q2" t="n">
-        <v>5.722866798943879e-08</v>
+        <v>5.722866798943875e-08</v>
       </c>
       <c r="R2" t="n">
-        <v>5.935617110504881e-08</v>
+        <v>5.935617110504875e-08</v>
       </c>
       <c r="S2" t="n">
-        <v>5.768220335727676e-08</v>
+        <v>5.768220335727668e-08</v>
       </c>
       <c r="T2" t="n">
-        <v>5.693742990585485e-08</v>
+        <v>5.693742990585483e-08</v>
       </c>
       <c r="U2" t="n">
-        <v>5.78066672167899e-08</v>
+        <v>5.780666721678986e-08</v>
       </c>
       <c r="V2" t="n">
-        <v>4.473611043151545e-08</v>
+        <v>4.473611043151543e-08</v>
       </c>
       <c r="W2" t="n">
-        <v>5.911080463520712e-08</v>
+        <v>5.911080463520708e-08</v>
       </c>
       <c r="X2" t="n">
-        <v>5.940619707021361e-08</v>
+        <v>5.940619707021353e-08</v>
       </c>
       <c r="Y2" t="n">
-        <v>5.677132773408826e-08</v>
+        <v>5.677132773408819e-08</v>
       </c>
       <c r="Z2" t="n">
-        <v>5.790736155194925e-08</v>
+        <v>5.790736155194921e-08</v>
       </c>
       <c r="AA2" t="n">
         <v>5.772907976434007e-08</v>
       </c>
       <c r="AB2" t="n">
-        <v>5.89734620427867e-08</v>
+        <v>5.897346204278665e-08</v>
       </c>
     </row>
     <row r="3">
@@ -6078,85 +6078,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.757158744446114e-08</v>
+        <v>5.75715874444611e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>5.737796697278589e-08</v>
+        <v>5.737796697278583e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>5.757158744446114e-08</v>
+        <v>5.75715874444611e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>9.602387380585532e-08</v>
+        <v>9.602387380585525e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>5.744239693979344e-08</v>
+        <v>5.74423969397934e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>5.718333445757278e-08</v>
+        <v>5.718333445757272e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>5.757158744446114e-08</v>
+        <v>5.75715874444611e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>5.757158744446114e-08</v>
+        <v>5.75715874444611e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>5.743836614552334e-08</v>
+        <v>5.743836614552328e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>5.749828419439883e-08</v>
+        <v>5.749828419439877e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>5.757158744446114e-08</v>
+        <v>5.75715874444611e-08</v>
       </c>
       <c r="M3" t="n">
-        <v>5.715823920670085e-08</v>
+        <v>5.715823920670079e-08</v>
       </c>
       <c r="N3" t="n">
-        <v>5.757158744446114e-08</v>
+        <v>5.75715874444611e-08</v>
       </c>
       <c r="O3" t="n">
-        <v>5.735078374793723e-08</v>
+        <v>5.735078374793717e-08</v>
       </c>
       <c r="P3" t="n">
-        <v>5.71432162743392e-08</v>
+        <v>5.714321627433914e-08</v>
       </c>
       <c r="Q3" t="n">
-        <v>5.756941767615269e-08</v>
+        <v>5.756941767615264e-08</v>
       </c>
       <c r="R3" t="n">
-        <v>5.798612171500418e-08</v>
+        <v>5.798612171500412e-08</v>
       </c>
       <c r="S3" t="n">
-        <v>5.757158744446114e-08</v>
+        <v>5.75715874444611e-08</v>
       </c>
       <c r="T3" t="n">
-        <v>5.72743439362024e-08</v>
+        <v>5.727434393620235e-08</v>
       </c>
       <c r="U3" t="n">
-        <v>5.818665798763583e-08</v>
+        <v>5.818665798763577e-08</v>
       </c>
       <c r="V3" t="n">
-        <v>4.348510822045316e-08</v>
+        <v>4.348510822045314e-08</v>
       </c>
       <c r="W3" t="n">
-        <v>5.757158744446114e-08</v>
+        <v>5.75715874444611e-08</v>
       </c>
       <c r="X3" t="n">
-        <v>5.816467211640975e-08</v>
+        <v>5.81646721164097e-08</v>
       </c>
       <c r="Y3" t="n">
-        <v>5.671075019712538e-08</v>
+        <v>5.671075019712533e-08</v>
       </c>
       <c r="Z3" t="n">
-        <v>5.755474472215555e-08</v>
+        <v>5.755474472215549e-08</v>
       </c>
       <c r="AA3" t="n">
-        <v>5.757158744446114e-08</v>
+        <v>5.75715874444611e-08</v>
       </c>
       <c r="AB3" t="n">
-        <v>5.950299204021399e-08</v>
+        <v>5.950299204021393e-08</v>
       </c>
     </row>
     <row r="4">
@@ -6166,55 +6166,55 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.420601457799154e-07</v>
+        <v>3.420601457799152e-07</v>
       </c>
       <c r="C4" t="n">
-        <v>2.827200006414872e-07</v>
+        <v>2.827200006414875e-07</v>
       </c>
       <c r="D4" t="n">
-        <v>3.101469968339931e-07</v>
+        <v>3.101469968339929e-07</v>
       </c>
       <c r="E4" t="n">
-        <v>3.920360637627822e-07</v>
+        <v>3.920360637627819e-07</v>
       </c>
       <c r="F4" t="n">
-        <v>3.636835932674081e-07</v>
+        <v>3.636835932674086e-07</v>
       </c>
       <c r="G4" t="n">
-        <v>2.500691139174478e-07</v>
+        <v>2.500691139174481e-07</v>
       </c>
       <c r="H4" t="n">
         <v>2.414673708194303e-07</v>
       </c>
       <c r="I4" t="n">
-        <v>2.522677098503017e-07</v>
+        <v>2.522677098503014e-07</v>
       </c>
       <c r="J4" t="n">
-        <v>3.086414902918068e-07</v>
+        <v>3.086414902918074e-07</v>
       </c>
       <c r="K4" t="n">
         <v>2.133505823553476e-07</v>
       </c>
       <c r="L4" t="n">
-        <v>3.228927747339967e-07</v>
+        <v>3.228927747339968e-07</v>
       </c>
       <c r="M4" t="n">
-        <v>1.972136324549675e-07</v>
+        <v>1.972136324549677e-07</v>
       </c>
       <c r="N4" t="n">
         <v>2.669090081682991e-07</v>
       </c>
       <c r="O4" t="n">
-        <v>4.992998613095495e-07</v>
+        <v>4.992998613095494e-07</v>
       </c>
       <c r="P4" t="n">
-        <v>3.162089436531064e-07</v>
+        <v>3.162089436531062e-07</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.906056975431831e-07</v>
+        <v>1.906056975431833e-07</v>
       </c>
       <c r="R4" t="n">
-        <v>6.669517362067838e-07</v>
+        <v>6.669517362067834e-07</v>
       </c>
       <c r="S4" t="n">
         <v>2.840438781845636e-07</v>
@@ -6226,25 +6226,25 @@
         <v>1.895303866958199e-07</v>
       </c>
       <c r="V4" t="n">
-        <v>4.798794982539403e-07</v>
+        <v>4.798794982539411e-07</v>
       </c>
       <c r="W4" t="n">
-        <v>6.465997192625313e-07</v>
+        <v>6.465997192625322e-07</v>
       </c>
       <c r="X4" t="n">
-        <v>5.797537632204728e-07</v>
+        <v>5.797537632204734e-07</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.786809311963221e-07</v>
+        <v>2.786809311963228e-07</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.285843777965027e-07</v>
+        <v>3.285843777965024e-07</v>
       </c>
       <c r="AA4" t="n">
         <v>3.20123776311649e-07</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.998272117043173e-07</v>
+        <v>1.998272117043172e-07</v>
       </c>
     </row>
     <row r="5">
@@ -6254,16 +6254,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.211890180862381e-07</v>
+        <v>1.211890180862382e-07</v>
       </c>
       <c r="C5" t="n">
-        <v>1.821145014422902e-07</v>
+        <v>1.821145014422901e-07</v>
       </c>
       <c r="D5" t="n">
-        <v>1.821145014422902e-07</v>
+        <v>1.821145014422901e-07</v>
       </c>
       <c r="E5" t="n">
-        <v>1.496734787436447e-07</v>
+        <v>1.496734787436446e-07</v>
       </c>
       <c r="F5" t="n">
         <v>1.306804963396002e-07</v>
@@ -6272,67 +6272,67 @@
         <v>1.947477973092035e-07</v>
       </c>
       <c r="H5" t="n">
-        <v>1.821145014422902e-07</v>
+        <v>1.821145014422901e-07</v>
       </c>
       <c r="I5" t="n">
-        <v>1.821145014422902e-07</v>
+        <v>1.821145014422901e-07</v>
       </c>
       <c r="J5" t="n">
-        <v>1.818700170776178e-07</v>
+        <v>1.818700170776179e-07</v>
       </c>
       <c r="K5" t="n">
-        <v>1.821145014422902e-07</v>
+        <v>1.821145014422901e-07</v>
       </c>
       <c r="L5" t="n">
-        <v>1.821145014422902e-07</v>
+        <v>1.821145014422901e-07</v>
       </c>
       <c r="M5" t="n">
         <v>1.821145014422851e-07</v>
       </c>
       <c r="N5" t="n">
-        <v>2.669090081682993e-07</v>
+        <v>1.348870592275259e-07</v>
       </c>
       <c r="O5" t="n">
-        <v>1.478655704160972e-07</v>
+        <v>1.478655704160971e-07</v>
       </c>
       <c r="P5" t="n">
-        <v>1.446842237190921e-07</v>
+        <v>1.446842237190919e-07</v>
       </c>
       <c r="Q5" t="n">
         <v>1.092157700482288e-07</v>
       </c>
       <c r="R5" t="n">
-        <v>1.821145014422902e-07</v>
+        <v>1.821145014422901e-07</v>
       </c>
       <c r="S5" t="n">
-        <v>1.821145014422902e-07</v>
+        <v>1.821145014422901e-07</v>
       </c>
       <c r="T5" t="n">
-        <v>1.821145014422902e-07</v>
+        <v>1.821145014422901e-07</v>
       </c>
       <c r="U5" t="n">
         <v>1.52386882695548e-07</v>
       </c>
       <c r="V5" t="n">
-        <v>1.638127022088049e-07</v>
+        <v>1.63812702208805e-07</v>
       </c>
       <c r="W5" t="n">
         <v>1.821264750417198e-07</v>
       </c>
       <c r="X5" t="n">
-        <v>1.147997116574732e-07</v>
+        <v>1.147997116574731e-07</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.427072264303155e-07</v>
+        <v>2.427072264303154e-07</v>
       </c>
       <c r="Z5" t="n">
         <v>1.200572959514213e-07</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.821145014422902e-07</v>
+        <v>1.821145014422901e-07</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.457562633147962e-07</v>
+        <v>2.457562633147963e-07</v>
       </c>
     </row>
     <row r="6">
@@ -6345,82 +6345,82 @@
         <v>1.372154263339327e-07</v>
       </c>
       <c r="C6" t="n">
-        <v>1.681655985673093e-07</v>
+        <v>1.681655985673091e-07</v>
       </c>
       <c r="D6" t="n">
-        <v>1.681655985673093e-07</v>
+        <v>1.681655985673091e-07</v>
       </c>
       <c r="E6" t="n">
-        <v>1.610224602040926e-07</v>
+        <v>1.610224602040923e-07</v>
       </c>
       <c r="F6" t="n">
-        <v>9.681694482826559e-08</v>
+        <v>9.681694482826556e-08</v>
       </c>
       <c r="G6" t="n">
         <v>1.681656442571265e-07</v>
       </c>
       <c r="H6" t="n">
-        <v>1.681655985673093e-07</v>
+        <v>1.681655985673091e-07</v>
       </c>
       <c r="I6" t="n">
-        <v>1.681655985673093e-07</v>
+        <v>1.681655985673091e-07</v>
       </c>
       <c r="J6" t="n">
-        <v>1.679211142026371e-07</v>
+        <v>1.679211142026368e-07</v>
       </c>
       <c r="K6" t="n">
-        <v>1.681655985673093e-07</v>
+        <v>1.681655985673091e-07</v>
       </c>
       <c r="L6" t="n">
-        <v>1.681655985673093e-07</v>
+        <v>1.681655985673091e-07</v>
       </c>
       <c r="M6" t="n">
-        <v>1.681655985673093e-07</v>
+        <v>1.681655985673091e-07</v>
       </c>
       <c r="N6" t="n">
-        <v>2.669090081682991e-07</v>
+        <v>1.681655985673091e-07</v>
       </c>
       <c r="O6" t="n">
-        <v>1.784225059510246e-07</v>
+        <v>1.784225059510245e-07</v>
       </c>
       <c r="P6" t="n">
-        <v>1.806531973913347e-07</v>
+        <v>1.806531973913343e-07</v>
       </c>
       <c r="Q6" t="n">
         <v>1.681656442571265e-07</v>
       </c>
       <c r="R6" t="n">
-        <v>1.681655985673093e-07</v>
+        <v>1.681655985673091e-07</v>
       </c>
       <c r="S6" t="n">
-        <v>1.681655985673093e-07</v>
+        <v>1.681655985673091e-07</v>
       </c>
       <c r="T6" t="n">
-        <v>1.681655985673093e-07</v>
+        <v>1.681655985673091e-07</v>
       </c>
       <c r="U6" t="n">
-        <v>1.681655985673093e-07</v>
+        <v>1.681655985673091e-07</v>
       </c>
       <c r="V6" t="n">
-        <v>2.022213021307687e-07</v>
+        <v>2.022213021307685e-07</v>
       </c>
       <c r="W6" t="n">
-        <v>1.681655985673093e-07</v>
+        <v>1.681655985673091e-07</v>
       </c>
       <c r="X6" t="n">
-        <v>1.681655985673093e-07</v>
+        <v>1.681655985673091e-07</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.681655985673093e-07</v>
+        <v>1.681655985673091e-07</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.495054150502018e-07</v>
+        <v>1.495054150502017e-07</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.681655985673093e-07</v>
+        <v>1.681655985673091e-07</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.681655985673093e-07</v>
+        <v>1.681655985673091e-07</v>
       </c>
     </row>
     <row r="7">
@@ -6430,85 +6430,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5.026011113457902e-08</v>
+        <v>5.026011113457898e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>5.212480577448176e-08</v>
+        <v>5.212480577448183e-08</v>
       </c>
       <c r="D7" t="n">
         <v>5.172905268992501e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>8.713742803814372e-08</v>
+        <v>8.713742803814367e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>5.057163738857564e-08</v>
+        <v>5.057163738857557e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>5.215864793067883e-08</v>
+        <v>5.215864793067878e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>5.361912059650059e-08</v>
+        <v>5.361912059650056e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>5.321689162505182e-08</v>
+        <v>5.321689162505177e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>5.112773448332725e-08</v>
+        <v>5.112773448332716e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>5.385558552705514e-08</v>
+        <v>5.385558552705509e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>5.053693325855039e-08</v>
+        <v>5.053693325855035e-08</v>
       </c>
       <c r="M7" t="n">
-        <v>5.402876913099321e-08</v>
+        <v>5.402876913099317e-08</v>
       </c>
       <c r="N7" t="n">
-        <v>5.263200899918162e-08</v>
+        <v>5.263200899918159e-08</v>
       </c>
       <c r="O7" t="n">
-        <v>4.562568091404541e-08</v>
+        <v>4.562568091404539e-08</v>
       </c>
       <c r="P7" t="n">
-        <v>5.033198982017863e-08</v>
+        <v>5.033198982017862e-08</v>
       </c>
       <c r="Q7" t="n">
-        <v>5.436530293852791e-08</v>
+        <v>5.436530293852789e-08</v>
       </c>
       <c r="R7" t="n">
-        <v>4.461192556666739e-08</v>
+        <v>4.461192556666736e-08</v>
       </c>
       <c r="S7" t="n">
-        <v>5.165723570017157e-08</v>
+        <v>5.165723570017153e-08</v>
       </c>
       <c r="T7" t="n">
         <v>5.420694583765884e-08</v>
       </c>
       <c r="U7" t="n">
-        <v>5.487503766271953e-08</v>
+        <v>5.487503766271949e-08</v>
       </c>
       <c r="V7" t="n">
-        <v>3.203482205495747e-08</v>
+        <v>3.203482205495746e-08</v>
       </c>
       <c r="W7" t="n">
-        <v>4.325459119839116e-08</v>
+        <v>4.325459119839109e-08</v>
       </c>
       <c r="X7" t="n">
-        <v>4.538781411358269e-08</v>
+        <v>4.538781411358265e-08</v>
       </c>
       <c r="Y7" t="n">
-        <v>5.156684959792406e-08</v>
+        <v>5.156684959792403e-08</v>
       </c>
       <c r="Z7" t="n">
-        <v>5.019909233026703e-08</v>
+        <v>5.019909233026699e-08</v>
       </c>
       <c r="AA7" t="n">
-        <v>5.141453997426014e-08</v>
+        <v>5.141453997426006e-08</v>
       </c>
       <c r="AB7" t="n">
-        <v>5.643760752287457e-08</v>
+        <v>5.643760752287455e-08</v>
       </c>
     </row>
     <row r="8">
@@ -6518,85 +6518,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.458720402761182e-08</v>
+        <v>5.458720402761176e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>5.501369012700053e-08</v>
+        <v>5.501369012700051e-08</v>
       </c>
       <c r="D8" t="n">
         <v>5.502412215711749e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>9.198174103751616e-08</v>
+        <v>9.198174103751612e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>5.461954103468786e-08</v>
+        <v>5.461954103468779e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>5.488899106144457e-08</v>
+        <v>5.488899106144453e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>5.556606162968366e-08</v>
+        <v>5.556606162968364e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>5.544849507337345e-08</v>
+        <v>5.544849507337342e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>5.474777769441285e-08</v>
+        <v>5.47477776944128e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>5.558162258812107e-08</v>
+        <v>5.558162258812112e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>5.467413370543674e-08</v>
+        <v>5.467413370543669e-08</v>
       </c>
       <c r="M8" t="n">
-        <v>5.541973052475532e-08</v>
+        <v>5.541973052475528e-08</v>
       </c>
       <c r="N8" t="n">
-        <v>5.527723864318335e-08</v>
+        <v>5.527723864318328e-08</v>
       </c>
       <c r="O8" t="n">
-        <v>5.311695211755525e-08</v>
+        <v>5.311695211755527e-08</v>
       </c>
       <c r="P8" t="n">
-        <v>5.433700315177149e-08</v>
+        <v>5.433700315177147e-08</v>
       </c>
       <c r="Q8" t="n">
-        <v>5.577078557291176e-08</v>
+        <v>5.577078557291173e-08</v>
       </c>
       <c r="R8" t="n">
-        <v>5.327086923652135e-08</v>
+        <v>5.327086923652133e-08</v>
       </c>
       <c r="S8" t="n">
-        <v>5.499115446570433e-08</v>
+        <v>5.499115446570428e-08</v>
       </c>
       <c r="T8" t="n">
-        <v>5.554175399579982e-08</v>
+        <v>5.554175399579977e-08</v>
       </c>
       <c r="U8" t="n">
-        <v>5.629986941544519e-08</v>
+        <v>5.629986941544517e-08</v>
       </c>
       <c r="V8" t="n">
         <v>3.952619373631798e-08</v>
       </c>
       <c r="W8" t="n">
-        <v>5.259652571768534e-08</v>
+        <v>5.25965257176853e-08</v>
       </c>
       <c r="X8" t="n">
-        <v>5.359268596149678e-08</v>
+        <v>5.35926859614967e-08</v>
       </c>
       <c r="Y8" t="n">
-        <v>5.443083656881307e-08</v>
+        <v>5.443083656881302e-08</v>
       </c>
       <c r="Z8" t="n">
-        <v>5.456051627256667e-08</v>
+        <v>5.456051627256663e-08</v>
       </c>
       <c r="AA8" t="n">
-        <v>5.492760354405251e-08</v>
+        <v>5.49276035440524e-08</v>
       </c>
       <c r="AB8" t="n">
-        <v>5.757870231859645e-08</v>
+        <v>5.757870231859638e-08</v>
       </c>
     </row>
   </sheetData>
@@ -6762,28 +6762,28 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.103642101611766e-08</v>
+        <v>6.103642101611768e-08</v>
       </c>
       <c r="C2" t="n">
-        <v>6.062491550482436e-08</v>
+        <v>6.062491550482438e-08</v>
       </c>
       <c r="D2" t="n">
-        <v>6.221321476845588e-08</v>
+        <v>6.221321476845591e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>9.668023769506842e-08</v>
+        <v>9.668023769506854e-08</v>
       </c>
       <c r="F2" t="n">
-        <v>6.166797751236794e-08</v>
+        <v>6.166797751236792e-08</v>
       </c>
       <c r="G2" t="n">
-        <v>6.975190825668942e-08</v>
+        <v>6.975190825668943e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>6.133933169588489e-08</v>
+        <v>6.133933169588485e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>6.327616531420509e-08</v>
+        <v>6.327616531420508e-08</v>
       </c>
       <c r="J2" t="n">
         <v>6.430691627874189e-08</v>
@@ -6792,55 +6792,55 @@
         <v>6.525384282874133e-08</v>
       </c>
       <c r="L2" t="n">
-        <v>7.307302940519272e-08</v>
+        <v>7.307302940519279e-08</v>
       </c>
       <c r="M2" t="n">
         <v>6.326235457832359e-08</v>
       </c>
       <c r="N2" t="n">
-        <v>6.442565866535566e-08</v>
+        <v>6.44256586653557e-08</v>
       </c>
       <c r="O2" t="n">
-        <v>6.138650320864066e-08</v>
+        <v>6.138650320864068e-08</v>
       </c>
       <c r="P2" t="n">
-        <v>6.220244847925045e-08</v>
+        <v>6.220244847925046e-08</v>
       </c>
       <c r="Q2" t="n">
-        <v>6.151361947496466e-08</v>
+        <v>6.151361947496475e-08</v>
       </c>
       <c r="R2" t="n">
-        <v>6.178690854019334e-08</v>
+        <v>6.178690854019335e-08</v>
       </c>
       <c r="S2" t="n">
-        <v>6.153553624257187e-08</v>
+        <v>6.15355362425718e-08</v>
       </c>
       <c r="T2" t="n">
-        <v>6.229411206069228e-08</v>
+        <v>6.229411206069225e-08</v>
       </c>
       <c r="U2" t="n">
-        <v>6.209622874434097e-08</v>
+        <v>6.2096228744341e-08</v>
       </c>
       <c r="V2" t="n">
-        <v>4.553813642493044e-08</v>
+        <v>4.553813642493051e-08</v>
       </c>
       <c r="W2" t="n">
-        <v>6.163338583180236e-08</v>
+        <v>6.16333858318024e-08</v>
       </c>
       <c r="X2" t="n">
-        <v>6.535473458194317e-08</v>
+        <v>6.535473458194311e-08</v>
       </c>
       <c r="Y2" t="n">
-        <v>6.124170488402441e-08</v>
+        <v>6.124170488402442e-08</v>
       </c>
       <c r="Z2" t="n">
-        <v>6.183043143335098e-08</v>
+        <v>6.183043143335101e-08</v>
       </c>
       <c r="AA2" t="n">
-        <v>6.238228663462692e-08</v>
+        <v>6.238228663462696e-08</v>
       </c>
       <c r="AB2" t="n">
-        <v>6.486010525051538e-08</v>
+        <v>6.486010525051536e-08</v>
       </c>
     </row>
     <row r="3">
@@ -6850,85 +6850,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.105366334589261e-08</v>
+        <v>6.105366334589267e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>6.086857547775597e-08</v>
+        <v>6.086857547775604e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>6.105366334589261e-08</v>
+        <v>6.105366334589267e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>9.757984181564471e-08</v>
+        <v>9.757984181564485e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>6.098470096605467e-08</v>
+        <v>6.098470096605472e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>6.089336723446766e-08</v>
+        <v>6.089336723446773e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>6.105366334589261e-08</v>
+        <v>6.105366334589267e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>6.105366334589261e-08</v>
+        <v>6.105366334589267e-08</v>
       </c>
       <c r="J3" t="n">
         <v>6.061961452588559e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>6.101335062726844e-08</v>
+        <v>6.101335062726851e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>6.105366334589261e-08</v>
+        <v>6.105366334589267e-08</v>
       </c>
       <c r="M3" t="n">
-        <v>6.099470466959182e-08</v>
+        <v>6.099470466959189e-08</v>
       </c>
       <c r="N3" t="n">
-        <v>6.105366334589261e-08</v>
+        <v>6.105366334589267e-08</v>
       </c>
       <c r="O3" t="n">
-        <v>6.088082046574993e-08</v>
+        <v>6.088082046575e-08</v>
       </c>
       <c r="P3" t="n">
-        <v>6.10127412222756e-08</v>
+        <v>6.101274122227566e-08</v>
       </c>
       <c r="Q3" t="n">
-        <v>6.105149357758415e-08</v>
+        <v>6.105149357758422e-08</v>
       </c>
       <c r="R3" t="n">
-        <v>6.104618091583605e-08</v>
+        <v>6.104618091583612e-08</v>
       </c>
       <c r="S3" t="n">
-        <v>6.105366334589261e-08</v>
+        <v>6.105366334589267e-08</v>
       </c>
       <c r="T3" t="n">
-        <v>6.098338230968333e-08</v>
+        <v>6.098338230968339e-08</v>
       </c>
       <c r="U3" t="n">
-        <v>6.120816374165549e-08</v>
+        <v>6.120816374165555e-08</v>
       </c>
       <c r="V3" t="n">
-        <v>4.546081647623434e-08</v>
+        <v>4.54608164762344e-08</v>
       </c>
       <c r="W3" t="n">
-        <v>6.105366334589261e-08</v>
+        <v>6.105366334589267e-08</v>
       </c>
       <c r="X3" t="n">
-        <v>6.116204446894222e-08</v>
+        <v>6.116204446894228e-08</v>
       </c>
       <c r="Y3" t="n">
-        <v>6.064546112266293e-08</v>
+        <v>6.0645461122663e-08</v>
       </c>
       <c r="Z3" t="n">
-        <v>6.104348315872434e-08</v>
+        <v>6.10434831587244e-08</v>
       </c>
       <c r="AA3" t="n">
-        <v>6.105366334589261e-08</v>
+        <v>6.105366334589267e-08</v>
       </c>
       <c r="AB3" t="n">
-        <v>6.298506794164545e-08</v>
+        <v>6.29850679416455e-08</v>
       </c>
     </row>
     <row r="4">
@@ -6938,85 +6938,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.871099347291984e-07</v>
+        <v>2.871099347292103e-07</v>
       </c>
       <c r="C4" t="n">
-        <v>2.444370822941023e-07</v>
+        <v>2.444370822941024e-07</v>
       </c>
       <c r="D4" t="n">
-        <v>6.505313818451655e-07</v>
+        <v>6.505313818451664e-07</v>
       </c>
       <c r="E4" t="n">
-        <v>1.998569665547514e-07</v>
+        <v>1.99856966554754e-07</v>
       </c>
       <c r="F4" t="n">
-        <v>5.107458361953692e-07</v>
+        <v>5.107458361953688e-07</v>
       </c>
       <c r="G4" t="n">
-        <v>2.453383166128272e-06</v>
+        <v>2.453383166128273e-06</v>
       </c>
       <c r="H4" t="n">
-        <v>4.159546897250891e-07</v>
+        <v>4.159546897250886e-07</v>
       </c>
       <c r="I4" t="n">
-        <v>9.533318899239927e-07</v>
+        <v>9.533318899239914e-07</v>
       </c>
       <c r="J4" t="n">
-        <v>1.217069918733007e-06</v>
+        <v>1.217069918733011e-06</v>
       </c>
       <c r="K4" t="n">
-        <v>1.37266464901369e-06</v>
+        <v>1.372664649013691e-06</v>
       </c>
       <c r="L4" t="n">
-        <v>3.421941134506928e-06</v>
+        <v>3.421941134506955e-06</v>
       </c>
       <c r="M4" t="n">
-        <v>9.076589213941605e-07</v>
+        <v>9.076589213941618e-07</v>
       </c>
       <c r="N4" t="n">
-        <v>1.244827939993539e-06</v>
+        <v>1.244827939993538e-06</v>
       </c>
       <c r="O4" t="n">
-        <v>4.075121491412356e-07</v>
+        <v>4.075121491412358e-07</v>
       </c>
       <c r="P4" t="n">
-        <v>5.966950718276003e-07</v>
+        <v>5.96695071827602e-07</v>
       </c>
       <c r="Q4" t="n">
-        <v>4.349066210072925e-07</v>
+        <v>4.349066210072932e-07</v>
       </c>
       <c r="R4" t="n">
-        <v>5.425520030631e-07</v>
+        <v>5.425520030630989e-07</v>
       </c>
       <c r="S4" t="n">
-        <v>4.039158048017848e-07</v>
+        <v>4.039158048017902e-07</v>
       </c>
       <c r="T4" t="n">
-        <v>6.908529967342313e-07</v>
+        <v>6.908529967342318e-07</v>
       </c>
       <c r="U4" t="n">
-        <v>5.386061281963643e-07</v>
+        <v>5.386061281963787e-07</v>
       </c>
       <c r="V4" t="n">
-        <v>2.401175744260907e-07</v>
+        <v>2.401175744260939e-07</v>
       </c>
       <c r="W4" t="n">
-        <v>4.660555748577225e-07</v>
+        <v>4.660555748577219e-07</v>
       </c>
       <c r="X4" t="n">
-        <v>1.488805108120503e-06</v>
+        <v>1.488805108120522e-06</v>
       </c>
       <c r="Y4" t="n">
-        <v>4.586482585082328e-07</v>
+        <v>4.586482585082335e-07</v>
       </c>
       <c r="Z4" t="n">
-        <v>4.891740534292638e-07</v>
+        <v>4.891740534292649e-07</v>
       </c>
       <c r="AA4" t="n">
-        <v>6.689628454762586e-07</v>
+        <v>6.689628454762593e-07</v>
       </c>
       <c r="AB4" t="n">
-        <v>9.420439902047159e-07</v>
+        <v>9.420439902047154e-07</v>
       </c>
     </row>
     <row r="5">
@@ -7026,64 +7026,64 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.383756029273112e-07</v>
+        <v>1.383756029273113e-07</v>
       </c>
       <c r="C5" t="n">
-        <v>2.103950218426503e-07</v>
+        <v>2.103950218426506e-07</v>
       </c>
       <c r="D5" t="n">
-        <v>2.103950218426503e-07</v>
+        <v>2.103950218426506e-07</v>
       </c>
       <c r="E5" t="n">
-        <v>1.720468057096236e-07</v>
+        <v>1.720468057096237e-07</v>
       </c>
       <c r="F5" t="n">
-        <v>1.495953866828703e-07</v>
+        <v>1.495953866828704e-07</v>
       </c>
       <c r="G5" t="n">
-        <v>2.25328717517989e-07</v>
+        <v>2.253287175179891e-07</v>
       </c>
       <c r="H5" t="n">
-        <v>2.103950218426503e-07</v>
+        <v>2.103950218426505e-07</v>
       </c>
       <c r="I5" t="n">
-        <v>2.103950218426503e-07</v>
+        <v>2.103950218426506e-07</v>
       </c>
       <c r="J5" t="n">
-        <v>2.100367911091746e-07</v>
+        <v>2.100367911091747e-07</v>
       </c>
       <c r="K5" t="n">
-        <v>2.103950218426503e-07</v>
+        <v>2.103950218426506e-07</v>
       </c>
       <c r="L5" t="n">
-        <v>2.103950218426503e-07</v>
+        <v>2.103950218426506e-07</v>
       </c>
       <c r="M5" t="n">
-        <v>2.103950218426433e-07</v>
+        <v>2.103950218426435e-07</v>
       </c>
       <c r="N5" t="n">
-        <v>1.244827939993539e-06</v>
+        <v>1.545679235938368e-07</v>
       </c>
       <c r="O5" t="n">
-        <v>1.699096949290652e-07</v>
+        <v>1.699096949290654e-07</v>
       </c>
       <c r="P5" t="n">
         <v>1.661490560658453e-07</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.242221433455305e-07</v>
+        <v>1.242221433455307e-07</v>
       </c>
       <c r="R5" t="n">
-        <v>2.103950218426503e-07</v>
+        <v>2.103950218426505e-07</v>
       </c>
       <c r="S5" t="n">
-        <v>2.103950218426503e-07</v>
+        <v>2.103950218426505e-07</v>
       </c>
       <c r="T5" t="n">
-        <v>2.103950218426503e-07</v>
+        <v>2.103950218426506e-07</v>
       </c>
       <c r="U5" t="n">
-        <v>1.752114268388613e-07</v>
+        <v>1.752114268388617e-07</v>
       </c>
       <c r="V5" t="n">
         <v>1.882741937157374e-07</v>
@@ -7095,16 +7095,16 @@
         <v>1.308228661915527e-07</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.81947757060713e-07</v>
+        <v>2.819477570607133e-07</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.370378052438553e-07</v>
+        <v>1.370378052438555e-07</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.103950218426503e-07</v>
+        <v>2.103950218426505e-07</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.856253270649674e-07</v>
+        <v>2.85625327064967e-07</v>
       </c>
     </row>
     <row r="6">
@@ -7114,7 +7114,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.929080074265471e-07</v>
+        <v>1.92908007426547e-07</v>
       </c>
       <c r="C6" t="n">
         <v>2.393358667132409e-07</v>
@@ -7123,7 +7123,7 @@
         <v>2.393358667132409e-07</v>
       </c>
       <c r="E6" t="n">
-        <v>2.286205540873298e-07</v>
+        <v>2.286205540873295e-07</v>
       </c>
       <c r="F6" t="n">
         <v>1.323068983734711e-07</v>
@@ -7138,7 +7138,7 @@
         <v>2.393358667132409e-07</v>
       </c>
       <c r="J6" t="n">
-        <v>2.389776359797655e-07</v>
+        <v>2.389776359797652e-07</v>
       </c>
       <c r="K6" t="n">
         <v>2.393358667132409e-07</v>
@@ -7150,10 +7150,10 @@
         <v>2.393358667132409e-07</v>
       </c>
       <c r="N6" t="n">
-        <v>1.244827939993539e-06</v>
+        <v>2.393358667132409e-07</v>
       </c>
       <c r="O6" t="n">
-        <v>2.547220814353402e-07</v>
+        <v>2.547220814353401e-07</v>
       </c>
       <c r="P6" t="n">
         <v>2.580683056051541e-07</v>
@@ -7174,7 +7174,7 @@
         <v>2.393358667132409e-07</v>
       </c>
       <c r="V6" t="n">
-        <v>2.905110222279005e-07</v>
+        <v>2.905110222279008e-07</v>
       </c>
       <c r="W6" t="n">
         <v>2.393358667132409e-07</v>
@@ -7205,82 +7205,82 @@
         <v>5.569194143158621e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>5.700520638112077e-08</v>
+        <v>5.700520638112075e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>4.88820282826118e-08</v>
+        <v>4.888202828261178e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>9.400197518602134e-08</v>
+        <v>9.400197518602154e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>5.168347698488585e-08</v>
+        <v>5.168347698488588e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>2.842563194944697e-09</v>
+        <v>2.842563194944577e-09</v>
       </c>
       <c r="H7" t="n">
-        <v>5.40486644414929e-08</v>
+        <v>5.404866444149297e-08</v>
       </c>
       <c r="I7" t="n">
         <v>4.269027423757034e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>3.331120419082914e-08</v>
+        <v>3.331120419082913e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>3.077249139436284e-08</v>
+        <v>3.077249139436282e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.543265819560486e-08</v>
+        <v>-1.5432658195605e-08</v>
       </c>
       <c r="M7" t="n">
-        <v>4.243296597350054e-08</v>
+        <v>4.243296597350058e-08</v>
       </c>
       <c r="N7" t="n">
-        <v>3.581608376990106e-08</v>
+        <v>3.581608376990119e-08</v>
       </c>
       <c r="O7" t="n">
         <v>5.24875636795899e-08</v>
       </c>
       <c r="P7" t="n">
-        <v>4.846680008093224e-08</v>
+        <v>4.846680008093222e-08</v>
       </c>
       <c r="Q7" t="n">
-        <v>5.294537003184391e-08</v>
+        <v>5.294537003184389e-08</v>
       </c>
       <c r="R7" t="n">
-        <v>5.137003007764365e-08</v>
+        <v>5.137003007764361e-08</v>
       </c>
       <c r="S7" t="n">
-        <v>5.274846037552112e-08</v>
+        <v>5.274846037552104e-08</v>
       </c>
       <c r="T7" t="n">
-        <v>4.796998447930736e-08</v>
+        <v>4.796998447930739e-08</v>
       </c>
       <c r="U7" t="n">
-        <v>5.043881295424823e-08</v>
+        <v>5.043881295424787e-08</v>
       </c>
       <c r="V7" t="n">
-        <v>4.08568418365601e-08</v>
+        <v>4.085684183656016e-08</v>
       </c>
       <c r="W7" t="n">
-        <v>5.221151414809803e-08</v>
+        <v>5.221151414809804e-08</v>
       </c>
       <c r="X7" t="n">
-        <v>3.114009818952767e-08</v>
+        <v>3.11400981895275e-08</v>
       </c>
       <c r="Y7" t="n">
-        <v>5.192757952060313e-08</v>
+        <v>5.192757952060319e-08</v>
       </c>
       <c r="Z7" t="n">
-        <v>5.091398991133172e-08</v>
+        <v>5.091398991133165e-08</v>
       </c>
       <c r="AA7" t="n">
-        <v>4.780233601097317e-08</v>
+        <v>4.780233601097329e-08</v>
       </c>
       <c r="AB7" t="n">
-        <v>4.565148540289247e-08</v>
+        <v>4.565148540289259e-08</v>
       </c>
     </row>
     <row r="8">
@@ -7290,82 +7290,82 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.859682045831436e-08</v>
+        <v>5.859682045831427e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>5.886707025402851e-08</v>
+        <v>5.886707025402853e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>5.667508202596364e-08</v>
+        <v>5.66750820259637e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>9.505229697660536e-08</v>
+        <v>9.505229697660545e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>5.743589095969408e-08</v>
+        <v>5.743589095969409e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>4.333860742177048e-08</v>
+        <v>4.333860742177045e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>5.815203487077602e-08</v>
+        <v>5.815203487077607e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>5.492076474926963e-08</v>
+        <v>5.492076474926966e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>5.188150254955107e-08</v>
+        <v>5.188150254955106e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>5.149415550586902e-08</v>
+        <v>5.149415550586904e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>3.827150935636712e-08</v>
+        <v>3.827150935636717e-08</v>
       </c>
       <c r="M8" t="n">
-        <v>5.481670431885057e-08</v>
+        <v>5.481670431885056e-08</v>
       </c>
       <c r="N8" t="n">
-        <v>5.294247953088548e-08</v>
+        <v>5.294247953088552e-08</v>
       </c>
       <c r="O8" t="n">
-        <v>5.756754462321549e-08</v>
+        <v>5.756754462321555e-08</v>
       </c>
       <c r="P8" t="n">
-        <v>5.649400527839703e-08</v>
+        <v>5.649400527839705e-08</v>
       </c>
       <c r="Q8" t="n">
-        <v>5.782530742896993e-08</v>
+        <v>5.782530742896998e-08</v>
       </c>
       <c r="R8" t="n">
         <v>5.738422907275266e-08</v>
       </c>
       <c r="S8" t="n">
-        <v>5.775664242394128e-08</v>
+        <v>5.775664242394126e-08</v>
       </c>
       <c r="T8" t="n">
-        <v>5.637297457663292e-08</v>
+        <v>5.637297457663301e-08</v>
       </c>
       <c r="U8" t="n">
         <v>5.719613981618603e-08</v>
       </c>
       <c r="V8" t="n">
-        <v>4.344331329188196e-08</v>
+        <v>4.344331329188198e-08</v>
       </c>
       <c r="W8" t="n">
-        <v>5.76101797685482e-08</v>
+        <v>5.761017976854814e-08</v>
       </c>
       <c r="X8" t="n">
-        <v>5.169465335054333e-08</v>
+        <v>5.169465335054337e-08</v>
       </c>
       <c r="Y8" t="n">
-        <v>5.727504097284689e-08</v>
+        <v>5.727504097284691e-08</v>
       </c>
       <c r="Z8" t="n">
-        <v>5.722147972500781e-08</v>
+        <v>5.722147972500783e-08</v>
       </c>
       <c r="AA8" t="n">
-        <v>5.6352890467764e-08</v>
+        <v>5.635289046776399e-08</v>
       </c>
       <c r="AB8" t="n">
         <v>5.697326995653279e-08</v>
@@ -7534,85 +7534,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.929575491050022e-08</v>
+        <v>5.929575491050024e-08</v>
       </c>
       <c r="C2" t="n">
-        <v>5.939685621024869e-08</v>
+        <v>5.939685621024868e-08</v>
       </c>
       <c r="D2" t="n">
-        <v>5.961405254078153e-08</v>
+        <v>5.961405254078156e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>9.634168805989988e-08</v>
+        <v>9.634168805989996e-08</v>
       </c>
       <c r="F2" t="n">
         <v>5.978061901912752e-08</v>
       </c>
       <c r="G2" t="n">
-        <v>6.60218902095162e-08</v>
+        <v>6.602189020951621e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>5.942451485926297e-08</v>
+        <v>5.942451485926299e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>5.979059100094867e-08</v>
+        <v>5.97905910009487e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>6.194030067412085e-08</v>
+        <v>6.194030067412083e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>6.014934588182062e-08</v>
+        <v>6.014934588182063e-08</v>
       </c>
       <c r="L2" t="n">
-        <v>6.38955228471112e-08</v>
+        <v>6.389552284711121e-08</v>
       </c>
       <c r="M2" t="n">
-        <v>5.957577215334274e-08</v>
+        <v>5.957577215334269e-08</v>
       </c>
       <c r="N2" t="n">
-        <v>5.965386928878448e-08</v>
+        <v>5.965386928878446e-08</v>
       </c>
       <c r="O2" t="n">
-        <v>5.926801517350337e-08</v>
+        <v>5.926801517350341e-08</v>
       </c>
       <c r="P2" t="n">
-        <v>6.090086099090759e-08</v>
+        <v>6.09008609909076e-08</v>
       </c>
       <c r="Q2" t="n">
-        <v>5.988241913210453e-08</v>
+        <v>5.988241913210455e-08</v>
       </c>
       <c r="R2" t="n">
-        <v>6.080386842604134e-08</v>
+        <v>6.080386842604136e-08</v>
       </c>
       <c r="S2" t="n">
-        <v>6.007990255513716e-08</v>
+        <v>6.00799025551372e-08</v>
       </c>
       <c r="T2" t="n">
-        <v>5.946014781791956e-08</v>
+        <v>5.94601478179195e-08</v>
       </c>
       <c r="U2" t="n">
-        <v>5.970175291174002e-08</v>
+        <v>5.970175291173998e-08</v>
       </c>
       <c r="V2" t="n">
-        <v>4.47777863777858e-08</v>
+        <v>4.477778637778578e-08</v>
       </c>
       <c r="W2" t="n">
-        <v>6.065775911512565e-08</v>
+        <v>6.065775911512567e-08</v>
       </c>
       <c r="X2" t="n">
-        <v>6.340473979210634e-08</v>
+        <v>6.340473979210637e-08</v>
       </c>
       <c r="Y2" t="n">
-        <v>6.081463913303673e-08</v>
+        <v>6.081463913303672e-08</v>
       </c>
       <c r="Z2" t="n">
-        <v>5.957722329303627e-08</v>
+        <v>5.957722329303626e-08</v>
       </c>
       <c r="AA2" t="n">
-        <v>5.976223571194662e-08</v>
+        <v>5.976223571194665e-08</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.269005371624254e-07</v>
+        <v>1.269005371624255e-07</v>
       </c>
     </row>
     <row r="3">
@@ -7622,85 +7622,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.971357327740729e-08</v>
+        <v>5.971357327740726e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>5.951919244648756e-08</v>
+        <v>5.951919244648753e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>5.971357327740729e-08</v>
+        <v>5.971357327740726e-08</v>
       </c>
       <c r="E3" t="n">
         <v>9.702880326473033e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>5.96162387317617e-08</v>
+        <v>5.961623873176168e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>5.945348787160692e-08</v>
+        <v>5.945348787160688e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>5.971357327740729e-08</v>
+        <v>5.971357327740726e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>5.971357327740729e-08</v>
+        <v>5.971357327740726e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>5.936620837506003e-08</v>
+        <v>5.936620837506001e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>5.965639264271494e-08</v>
+        <v>5.96563926427149e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>5.971357327740729e-08</v>
+        <v>5.971357327740726e-08</v>
       </c>
       <c r="M3" t="n">
-        <v>5.955409704202995e-08</v>
+        <v>5.955409704202992e-08</v>
       </c>
       <c r="N3" t="n">
-        <v>5.971357327740729e-08</v>
+        <v>5.971357327740726e-08</v>
       </c>
       <c r="O3" t="n">
-        <v>5.952056085751038e-08</v>
+        <v>5.952056085751035e-08</v>
       </c>
       <c r="P3" t="n">
-        <v>5.969293558640238e-08</v>
+        <v>5.969293558640236e-08</v>
       </c>
       <c r="Q3" t="n">
-        <v>5.971140350909885e-08</v>
+        <v>5.971140350909881e-08</v>
       </c>
       <c r="R3" t="n">
-        <v>5.992861597923661e-08</v>
+        <v>5.992861597923657e-08</v>
       </c>
       <c r="S3" t="n">
-        <v>5.971357327740729e-08</v>
+        <v>5.971357327740726e-08</v>
       </c>
       <c r="T3" t="n">
-        <v>5.950659607857423e-08</v>
+        <v>5.95065960785742e-08</v>
       </c>
       <c r="U3" t="n">
-        <v>5.990341261932414e-08</v>
+        <v>5.990341261932412e-08</v>
       </c>
       <c r="V3" t="n">
-        <v>4.461755539189631e-08</v>
+        <v>4.461755539189633e-08</v>
       </c>
       <c r="W3" t="n">
-        <v>5.971357327740729e-08</v>
+        <v>5.971357327740726e-08</v>
       </c>
       <c r="X3" t="n">
-        <v>6.100724778126255e-08</v>
+        <v>6.100724778126253e-08</v>
       </c>
       <c r="Y3" t="n">
-        <v>5.922293048713245e-08</v>
+        <v>5.922293048713242e-08</v>
       </c>
       <c r="Z3" t="n">
-        <v>5.969645564848231e-08</v>
+        <v>5.969645564848229e-08</v>
       </c>
       <c r="AA3" t="n">
-        <v>5.971357327740729e-08</v>
+        <v>5.971357327740726e-08</v>
       </c>
       <c r="AB3" t="n">
-        <v>6.164497787316013e-08</v>
+        <v>6.164497787316009e-08</v>
       </c>
     </row>
     <row r="4">
@@ -7713,58 +7713,58 @@
         <v>1.722684195624353e-07</v>
       </c>
       <c r="C4" t="n">
-        <v>2.527397499402088e-07</v>
+        <v>2.52739749940209e-07</v>
       </c>
       <c r="D4" t="n">
-        <v>2.666029738342287e-07</v>
+        <v>2.666029738342289e-07</v>
       </c>
       <c r="E4" t="n">
-        <v>2.401537702644887e-07</v>
+        <v>2.40153770264489e-07</v>
       </c>
       <c r="F4" t="n">
-        <v>3.321015435087235e-07</v>
+        <v>3.321015435087237e-07</v>
       </c>
       <c r="G4" t="n">
         <v>1.689345408894036e-06</v>
       </c>
       <c r="H4" t="n">
-        <v>2.274081758806909e-07</v>
+        <v>2.27408175880691e-07</v>
       </c>
       <c r="I4" t="n">
-        <v>3.180379715685617e-07</v>
+        <v>3.180379715685619e-07</v>
       </c>
       <c r="J4" t="n">
-        <v>8.637802030028131e-07</v>
+        <v>8.637802030028136e-07</v>
       </c>
       <c r="K4" t="n">
-        <v>3.909801137961882e-07</v>
+        <v>3.909801137961884e-07</v>
       </c>
       <c r="L4" t="n">
-        <v>1.218137754774293e-06</v>
+        <v>1.218137754774294e-06</v>
       </c>
       <c r="M4" t="n">
-        <v>2.907261276887825e-07</v>
+        <v>2.907261276887824e-07</v>
       </c>
       <c r="N4" t="n">
-        <v>2.738916618144413e-07</v>
+        <v>2.738916618144417e-07</v>
       </c>
       <c r="O4" t="n">
-        <v>2.05923971611707e-07</v>
+        <v>2.059239716117075e-07</v>
       </c>
       <c r="P4" t="n">
-        <v>5.476517416831417e-07</v>
+        <v>5.47651741683141e-07</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.148954454899426e-07</v>
+        <v>3.148954454899425e-07</v>
       </c>
       <c r="R4" t="n">
-        <v>5.425434067095637e-07</v>
+        <v>5.425434067095645e-07</v>
       </c>
       <c r="S4" t="n">
-        <v>3.455109682945835e-07</v>
+        <v>3.455109682945834e-07</v>
       </c>
       <c r="T4" t="n">
-        <v>2.779218694218569e-07</v>
+        <v>2.779218694218565e-07</v>
       </c>
       <c r="U4" t="n">
         <v>2.311748808657767e-07</v>
@@ -7773,22 +7773,22 @@
         <v>2.398026514500312e-07</v>
       </c>
       <c r="W4" t="n">
-        <v>5.243283981974674e-07</v>
+        <v>5.243283981974673e-07</v>
       </c>
       <c r="X4" t="n">
-        <v>9.167627549454577e-07</v>
+        <v>9.167627549454573e-07</v>
       </c>
       <c r="Y4" t="n">
-        <v>6.721353703523625e-07</v>
+        <v>6.72135370352361e-07</v>
       </c>
       <c r="Z4" t="n">
         <v>2.370638483723889e-07</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.977532380729098e-07</v>
+        <v>2.977532380729099e-07</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.796502902947058e-05</v>
+        <v>1.796502902947059e-05</v>
       </c>
     </row>
     <row r="5">
@@ -7798,85 +7798,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.272864410492036e-07</v>
+        <v>1.272864410492038e-07</v>
       </c>
       <c r="C5" t="n">
-        <v>1.921533994444734e-07</v>
+        <v>1.921533994444736e-07</v>
       </c>
       <c r="D5" t="n">
-        <v>1.921533994444734e-07</v>
+        <v>1.921533994444736e-07</v>
       </c>
       <c r="E5" t="n">
         <v>1.576136575539818e-07</v>
       </c>
       <c r="F5" t="n">
-        <v>1.373919550485537e-07</v>
+        <v>1.373919550485538e-07</v>
       </c>
       <c r="G5" t="n">
         <v>2.056039858370281e-07</v>
       </c>
       <c r="H5" t="n">
-        <v>1.921533994444734e-07</v>
+        <v>1.921533994444736e-07</v>
       </c>
       <c r="I5" t="n">
-        <v>1.921533994444734e-07</v>
+        <v>1.921533994444736e-07</v>
       </c>
       <c r="J5" t="n">
-        <v>1.918470079067206e-07</v>
+        <v>1.918470079067207e-07</v>
       </c>
       <c r="K5" t="n">
-        <v>1.921533994444734e-07</v>
+        <v>1.921533994444736e-07</v>
       </c>
       <c r="L5" t="n">
-        <v>1.921533994444735e-07</v>
+        <v>1.921533994444736e-07</v>
       </c>
       <c r="M5" t="n">
-        <v>1.921533994444615e-07</v>
+        <v>1.921533994444618e-07</v>
       </c>
       <c r="N5" t="n">
-        <v>2.738916618144413e-07</v>
+        <v>1.418706546795911e-07</v>
       </c>
       <c r="O5" t="n">
-        <v>1.556887895369655e-07</v>
+        <v>1.556887895369657e-07</v>
       </c>
       <c r="P5" t="n">
-        <v>1.523016307906683e-07</v>
+        <v>1.523016307906686e-07</v>
       </c>
       <c r="Q5" t="n">
         <v>1.145386032066332e-07</v>
       </c>
       <c r="R5" t="n">
-        <v>1.921533994444734e-07</v>
+        <v>1.921533994444736e-07</v>
       </c>
       <c r="S5" t="n">
-        <v>1.921533994444734e-07</v>
+        <v>1.921533994444736e-07</v>
       </c>
       <c r="T5" t="n">
-        <v>1.921533994444734e-07</v>
+        <v>1.921533994444736e-07</v>
       </c>
       <c r="U5" t="n">
         <v>1.604702067520181e-07</v>
       </c>
       <c r="V5" t="n">
-        <v>1.723387383947375e-07</v>
+        <v>1.723387383947377e-07</v>
       </c>
       <c r="W5" t="n">
-        <v>1.921661476553274e-07</v>
+        <v>1.921661476553277e-07</v>
       </c>
       <c r="X5" t="n">
         <v>1.20483788834205e-07</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.566106554875346e-07</v>
+        <v>2.566106554875348e-07</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.260815039921362e-07</v>
+        <v>1.260815039921363e-07</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.921533994444734e-07</v>
+        <v>1.921533994444736e-07</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.599123615752412e-07</v>
+        <v>2.599123615752417e-07</v>
       </c>
     </row>
     <row r="6">
@@ -7898,10 +7898,10 @@
         <v>1.894974970845311e-07</v>
       </c>
       <c r="F6" t="n">
-        <v>1.117711781802363e-07</v>
+        <v>1.117711781802364e-07</v>
       </c>
       <c r="G6" t="n">
-        <v>1.981449380161747e-07</v>
+        <v>1.981449380161749e-07</v>
       </c>
       <c r="H6" t="n">
         <v>1.98144903519111e-07</v>
@@ -7910,7 +7910,7 @@
         <v>1.98144903519111e-07</v>
       </c>
       <c r="J6" t="n">
-        <v>1.978385119813579e-07</v>
+        <v>1.978385119813581e-07</v>
       </c>
       <c r="K6" t="n">
         <v>1.98144903519111e-07</v>
@@ -7922,16 +7922,16 @@
         <v>1.98144903519111e-07</v>
       </c>
       <c r="N6" t="n">
-        <v>2.738916618144413e-07</v>
+        <v>1.98144903519111e-07</v>
       </c>
       <c r="O6" t="n">
         <v>2.105617545203412e-07</v>
       </c>
       <c r="P6" t="n">
-        <v>2.132621990733014e-07</v>
+        <v>2.132621990733016e-07</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.981449380161747e-07</v>
+        <v>1.981449380161749e-07</v>
       </c>
       <c r="R6" t="n">
         <v>1.98144903519111e-07</v>
@@ -7946,7 +7946,7 @@
         <v>1.98144903519111e-07</v>
       </c>
       <c r="V6" t="n">
-        <v>2.393213291002842e-07</v>
+        <v>2.393213291002843e-07</v>
       </c>
       <c r="W6" t="n">
         <v>1.98144903519111e-07</v>
@@ -7958,7 +7958,7 @@
         <v>1.98144903519111e-07</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.755551197166901e-07</v>
+        <v>1.755551197166902e-07</v>
       </c>
       <c r="AA6" t="n">
         <v>1.98144903519111e-07</v>
@@ -7974,28 +7974,28 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5.682559687295124e-08</v>
+        <v>5.682559687295127e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>5.503837778339754e-08</v>
+        <v>5.503837778339752e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>5.500622928640205e-08</v>
+        <v>5.500622928640206e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>9.221427606176972e-08</v>
+        <v>9.221427606176964e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>5.344268138700525e-08</v>
+        <v>5.344268138700523e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>1.516127093672277e-08</v>
+        <v>1.516127093672266e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>5.614097933430582e-08</v>
+        <v>5.614097933430579e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>5.39829680753292e-08</v>
+        <v>5.398296807532913e-08</v>
       </c>
       <c r="J7" t="n">
         <v>3.877425873506232e-08</v>
@@ -8004,55 +8004,55 @@
         <v>5.149587251136753e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>2.965087014027339e-08</v>
+        <v>2.965087014027338e-08</v>
       </c>
       <c r="M7" t="n">
-        <v>5.423774002280543e-08</v>
+        <v>5.423774002280546e-08</v>
       </c>
       <c r="N7" t="n">
-        <v>5.475194100924913e-08</v>
+        <v>5.475194100924911e-08</v>
       </c>
       <c r="O7" t="n">
-        <v>5.574414902499896e-08</v>
+        <v>5.5744149024999e-08</v>
       </c>
       <c r="P7" t="n">
-        <v>4.711880786382115e-08</v>
+        <v>4.711880786382118e-08</v>
       </c>
       <c r="Q7" t="n">
-        <v>5.340429493839581e-08</v>
+        <v>5.340429493839586e-08</v>
       </c>
       <c r="R7" t="n">
-        <v>4.944458541815534e-08</v>
+        <v>4.944458541815536e-08</v>
       </c>
       <c r="S7" t="n">
-        <v>5.218400307486351e-08</v>
+        <v>5.21840030748635e-08</v>
       </c>
       <c r="T7" t="n">
-        <v>5.459599957134097e-08</v>
+        <v>5.459599957134092e-08</v>
       </c>
       <c r="U7" t="n">
-        <v>5.565491420112336e-08</v>
+        <v>5.565491420112334e-08</v>
       </c>
       <c r="V7" t="n">
-        <v>3.956339919465621e-08</v>
+        <v>3.95633991946562e-08</v>
       </c>
       <c r="W7" t="n">
-        <v>4.881029202973819e-08</v>
+        <v>4.881029202973808e-08</v>
       </c>
       <c r="X7" t="n">
-        <v>4.100129354520744e-08</v>
+        <v>4.100129354520741e-08</v>
       </c>
       <c r="Y7" t="n">
-        <v>4.477096401405048e-08</v>
+        <v>4.477096401405049e-08</v>
       </c>
       <c r="Z7" t="n">
-        <v>5.504611594332893e-08</v>
+        <v>5.504611594332894e-08</v>
       </c>
       <c r="AA7" t="n">
-        <v>5.410025112185182e-08</v>
+        <v>5.410025112185186e-08</v>
       </c>
       <c r="AB7" t="n">
-        <v>-3.267679354452393e-07</v>
+        <v>-3.267679354452395e-07</v>
       </c>
     </row>
     <row r="8">
@@ -8062,85 +8062,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.798171644303798e-08</v>
+        <v>5.798171644303794e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>5.73580712590337e-08</v>
+        <v>5.735807125903376e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>5.747219602345896e-08</v>
+        <v>5.747219602345898e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>9.415106283956492e-08</v>
+        <v>9.415106283956501e-08</v>
       </c>
       <c r="F8" t="n">
         <v>5.697163075330336e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>4.586879035322349e-08</v>
+        <v>4.586879035322348e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>5.779897322997052e-08</v>
+        <v>5.779897322997045e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>5.718314737164797e-08</v>
+        <v>5.718314737164795e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>5.257089796527194e-08</v>
+        <v>5.2570897965272e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>5.643628321602297e-08</v>
+        <v>5.643628321602295e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>5.021689711556482e-08</v>
+        <v>5.02168971155648e-08</v>
       </c>
       <c r="M8" t="n">
-        <v>5.715681276737101e-08</v>
+        <v>5.7156812767371e-08</v>
       </c>
       <c r="N8" t="n">
-        <v>5.739631079498866e-08</v>
+        <v>5.739631079498862e-08</v>
       </c>
       <c r="O8" t="n">
-        <v>5.754973575500022e-08</v>
+        <v>5.754973575500031e-08</v>
       </c>
       <c r="P8" t="n">
-        <v>5.517959280576576e-08</v>
+        <v>5.51795928057657e-08</v>
       </c>
       <c r="Q8" t="n">
-        <v>5.701266463287216e-08</v>
+        <v>5.701266463287228e-08</v>
       </c>
       <c r="R8" t="n">
-        <v>5.60336011101264e-08</v>
+        <v>5.603360111012637e-08</v>
       </c>
       <c r="S8" t="n">
-        <v>5.665392411766327e-08</v>
+        <v>5.665392411766324e-08</v>
       </c>
       <c r="T8" t="n">
-        <v>5.722581075798593e-08</v>
+        <v>5.722581075798585e-08</v>
       </c>
       <c r="U8" t="n">
-        <v>5.776867259229751e-08</v>
+        <v>5.776867259229743e-08</v>
       </c>
       <c r="V8" t="n">
-        <v>4.247812920140139e-08</v>
+        <v>4.247812920140138e-08</v>
       </c>
       <c r="W8" t="n">
-        <v>5.569673140074043e-08</v>
+        <v>5.569673140074051e-08</v>
       </c>
       <c r="X8" t="n">
-        <v>5.4301966859508e-08</v>
+        <v>5.430196685950789e-08</v>
       </c>
       <c r="Y8" t="n">
-        <v>5.423894833210004e-08</v>
+        <v>5.423894833209994e-08</v>
       </c>
       <c r="Z8" t="n">
-        <v>5.746130390743825e-08</v>
+        <v>5.746130390743817e-08</v>
       </c>
       <c r="AA8" t="n">
-        <v>5.72081562425726e-08</v>
+        <v>5.720815624257264e-08</v>
       </c>
       <c r="AB8" t="n">
-        <v>-4.982857619595715e-08</v>
+        <v>-4.982857619595724e-08</v>
       </c>
     </row>
   </sheetData>
